--- a/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRMG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C30D77-1122-4863-A219-71224A407983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9151F237-0B87-4C55-8174-C7B143D7AC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -1993,14 +1993,6 @@
       <font>
         <b val="0"/>
         <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
         <color theme="2" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -2043,6 +2035,24 @@
         <strike val="0"/>
         <color theme="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2250,16 +2260,6 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2602,15 +2602,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="51" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="1" max="1" width="9.69140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="51" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>52</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>55</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -2799,19 +2799,19 @@
         <v>377</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46244.628836111115</v>
+        <v>46249.394910185183</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>381</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>383</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
         <v>384</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>375</v>
       </c>
@@ -2910,38 +2910,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AA100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="255.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="159.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="255.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="31"/>
+    <col min="1" max="1" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.921875" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.23046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.4609375" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4609375" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.61328125" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.921875" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.921875" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.23046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="170.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="171.07421875" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.921875" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.23046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.07421875" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.921875" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="36.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.61328125" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="169.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3024,7 +3025,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -3118,7 +3119,7 @@
         <v>Continent.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -3210,7 +3211,7 @@
         <v>SubContinent.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>Region that defines characteristics of life in the natural environment.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -3395,7 +3396,7 @@
         <v>Country.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -3487,7 +3488,7 @@
         <v>Nation</v>
       </c>
     </row>
-    <row r="7" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -3580,7 +3581,7 @@
         <v>Geographic Region of Brazil. of Brazil there are 5 main Geographic Regions.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -3673,7 +3674,7 @@
         <v>Intermediate Geographic Region. Defined by the IBGE of Brazil, there are 133 Intermediate Geographic Regions, of a larger scale, which are articulated by regional capitals or large urban centers. Designed to organize the territory by articulating the Immediate Geographic Regions through a higher hierarchical pole differentiated from the flows of private and public management and the existence of urban functions of greater complexity.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -3766,7 +3767,7 @@
         <v>Immediate geographic region. Defined by the IBGE of Brazil, there are 510 Geographic Regions of smaller scale, they are articulated by medium and small cities. It is in these centers that the population seeks what they need on a daily basis: buying products, looking for a job, accessing health and education services and solving issues in public agencies, such as the INSS, the Ministry of Labor and Justice.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -3859,7 +3860,7 @@
         <v>State.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -3951,7 +3952,7 @@
         <v>Federative Unit of Brazil.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -4044,7 +4045,7 @@
         <v>Province.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>Capital of a State in Brazil.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -4231,7 +4232,7 @@
         <v>Capital City of a state located in the southern region of Brazil.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -4325,7 +4326,7 @@
         <v>Capital City of a State located in the Southeast region of Brazil.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -4419,7 +4420,7 @@
         <v>Capital City of a State located in the Northern region of Brazil.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -4513,7 +4514,7 @@
         <v>Capital City of a state located in the Northeast region of Brazil.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -4607,7 +4608,7 @@
         <v>Capital City of a state located in the Midwest region of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -4701,7 +4702,7 @@
         <v>City of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -4795,7 +4796,7 @@
         <v>City located in the southern region of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -4889,7 +4890,7 @@
         <v>City located in the Southeast region of Brazil.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
@@ -4983,7 +4984,7 @@
         <v>City located in the North region of Brazil.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
@@ -5077,7 +5078,7 @@
         <v>City located in the Northeast region of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
@@ -5171,7 +5172,7 @@
         <v>City located in the Midwest region of Brazil.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
@@ -5264,7 +5265,7 @@
         <v>Metropolis.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
@@ -5357,7 +5358,7 @@
         <v>Municipality.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
@@ -5450,7 +5451,7 @@
         <v>Climatic region.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
@@ -5543,7 +5544,7 @@
         <v>Climate zone.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
@@ -5636,7 +5637,7 @@
         <v>Local climate zone (FTZ) according to Stewart and Oke's methodology for qualifying heat islands in urban areas.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
@@ -5728,7 +5729,7 @@
         <v>Ifcreferent defines a position at a specific offset along an alignment curve.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
@@ -5820,7 +5821,7 @@
         <v>Represents where an administrative (city or state) or maintenance boundary (different companies or regionals) intersects the linear element (rails or roads) being measured.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
@@ -5912,7 +5913,7 @@
         <v>It is the location of an intersection specified by the name of the referent. the intersection location of the intersection's street reference lines. it is not precise or deterministic.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
@@ -6004,7 +6005,7 @@
         <v>Used to completely describe a linearly referenced location, given by the line element.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
@@ -6096,7 +6097,7 @@
         <v>Point in kilometer.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
@@ -6188,7 +6189,7 @@
         <v>The reference is the location of a visible physical reference point in the field.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="60">
         <v>36</v>
       </c>
@@ -6280,7 +6281,7 @@
         <v>Point in mile.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="60">
         <v>37</v>
       </c>
@@ -6372,7 +6373,7 @@
         <v>A reference marker is a notation referent, located in the right-of-way of a highway, railroad or other transportation system spaced at uniform distances.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="60">
         <v>38</v>
       </c>
@@ -6464,7 +6465,7 @@
         <v>Season.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="60">
         <v>39</v>
       </c>
@@ -6556,7 +6557,7 @@
         <v>Specifies the superelevation (transverse slope) at a specific location along a road alignment, and the type of transition from the previous location.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="60">
         <v>40</v>
       </c>
@@ -6648,7 +6649,7 @@
         <v>Event type that specifies the width at a specific location along a road alignment.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="60">
         <v>41</v>
       </c>
@@ -6740,7 +6741,7 @@
         <v>Elevation points positioned inside the land.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="60">
         <v>42</v>
       </c>
@@ -6832,7 +6833,7 @@
         <v>Altimetric elevation points positioned on the perimeter of the land.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="60">
         <v>43</v>
       </c>
@@ -6924,7 +6925,7 @@
         <v>Three-dimensional solid terrain. Revit models above 2024 use solid terrain models, while still maintaining the terrain mesh scheme.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="60">
         <v>44</v>
       </c>
@@ -7016,7 +7017,7 @@
         <v>Three-dimensional maha of the terrain. Revit models prior to 2024 use surface terrain models.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="60">
         <v>45</v>
       </c>
@@ -7108,7 +7109,7 @@
         <v>Three-dimensional terrain solid: core layer.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="60">
         <v>46</v>
       </c>
@@ -7200,7 +7201,7 @@
         <v>Three-dimensional solid of the terrain: substrate layer.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="60">
         <v>47</v>
       </c>
@@ -7292,7 +7293,7 @@
         <v>Three-dimensional solid of the terrain: membrane layer.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="60">
         <v>48</v>
       </c>
@@ -7384,7 +7385,7 @@
         <v>Three-dimensional solid terrain: insulation layer.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="60">
         <v>49</v>
       </c>
@@ -7476,7 +7477,7 @@
         <v>Three-dimensional solid of the terrain: surface layer.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="60">
         <v>50</v>
       </c>
@@ -7568,7 +7569,7 @@
         <v>10-meter level curve.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="60">
         <v>51</v>
       </c>
@@ -7660,7 +7661,7 @@
         <v>5 meter level curve.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="60">
         <v>52</v>
       </c>
@@ -7752,7 +7753,7 @@
         <v>Level curve of 1 meter.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="60">
         <v>53</v>
       </c>
@@ -7844,7 +7845,7 @@
         <v>Submetric contour line, its value must be less than 1m and can be 5 cm, 10 cm, 25 cm, etc. For adjustments of boxes or poles on the ground.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="60">
         <v>54</v>
       </c>
@@ -7936,7 +7937,7 @@
         <v>Land polling point.</v>
       </c>
     </row>
-    <row r="55" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="60">
         <v>55</v>
       </c>
@@ -8031,7 +8032,7 @@
         <v>AP stands for Planning Area.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="60">
         <v>56</v>
       </c>
@@ -8125,7 +8126,7 @@
         <v>RA stands for Administrative Region.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="60">
         <v>57</v>
       </c>
@@ -8217,7 +8218,7 @@
         <v>Area of Special Interest.</v>
       </c>
     </row>
-    <row r="58" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="60">
         <v>58</v>
       </c>
@@ -8309,7 +8310,7 @@
         <v>Area with occupancy restrictions</v>
       </c>
     </row>
-    <row r="59" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="60">
         <v>59</v>
       </c>
@@ -8401,7 +8402,7 @@
         <v>Areas of the city of Rio de Janeiro.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="60">
         <v>60</v>
       </c>
@@ -8493,7 +8494,7 @@
         <v>City Neighborhood</v>
       </c>
     </row>
-    <row r="61" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="60">
         <v>61</v>
       </c>
@@ -8585,7 +8586,7 @@
         <v>Zone of use of the municipal zoning of the city of Rio de Janeiro.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="60">
         <v>62</v>
       </c>
@@ -8677,7 +8678,7 @@
         <v>City Neighborhood</v>
       </c>
     </row>
-    <row r="63" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="60">
         <v>63</v>
       </c>
@@ -8769,7 +8770,7 @@
         <v>Block of a neighborhood.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="60">
         <v>64</v>
       </c>
@@ -8861,7 +8862,7 @@
         <v>Large land that has not yet been subdivided.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="60">
         <v>65</v>
       </c>
@@ -8953,7 +8954,7 @@
         <v>Urban allotment.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="60">
         <v>66</v>
       </c>
@@ -9045,7 +9046,7 @@
         <v>Urban parcel.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="60">
         <v>67</v>
       </c>
@@ -9137,7 +9138,7 @@
         <v>Urban lot.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="60">
         <v>68</v>
       </c>
@@ -9230,7 +9231,7 @@
         <v>Building.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="60">
         <v>69</v>
       </c>
@@ -9323,7 +9324,7 @@
         <v>Built block.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="60">
         <v>70</v>
       </c>
@@ -9416,7 +9417,7 @@
         <v>Building.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="60">
         <v>71</v>
       </c>
@@ -9509,7 +9510,7 @@
         <v>Home.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="60">
         <v>72</v>
       </c>
@@ -9602,7 +9603,7 @@
         <v>Social Interest Housing.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="60">
         <v>73</v>
       </c>
@@ -9694,7 +9695,7 @@
         <v>Shed.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="60">
         <v>74</v>
       </c>
@@ -9786,7 +9787,7 @@
         <v>Edicule.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="60">
         <v>75</v>
       </c>
@@ -9879,7 +9880,7 @@
         <v>Unity.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="60">
         <v>76</v>
       </c>
@@ -9971,7 +9972,7 @@
         <v>Sector.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="60">
         <v>77</v>
       </c>
@@ -10063,7 +10064,7 @@
         <v>Division.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="60">
         <v>78</v>
       </c>
@@ -10155,7 +10156,7 @@
         <v>Department</v>
       </c>
     </row>
-    <row r="79" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="60">
         <v>79</v>
       </c>
@@ -10247,7 +10248,7 @@
         <v>Environment.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="60">
         <v>80</v>
       </c>
@@ -10339,7 +10340,7 @@
         <v>Apartment</v>
       </c>
     </row>
-    <row r="81" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="60">
         <v>81</v>
       </c>
@@ -10431,7 +10432,7 @@
         <v>Circulation Center.</v>
       </c>
     </row>
-    <row r="82" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="60">
         <v>82</v>
       </c>
@@ -10523,7 +10524,7 @@
         <v>National Hospital.</v>
       </c>
     </row>
-    <row r="83" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="60">
         <v>83</v>
       </c>
@@ -10615,7 +10616,7 @@
         <v>State Hospital.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="60">
         <v>84</v>
       </c>
@@ -10707,7 +10708,7 @@
         <v>Municipal Hospital.</v>
       </c>
     </row>
-    <row r="85" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="60">
         <v>85</v>
       </c>
@@ -10799,7 +10800,7 @@
         <v>UBS Basic Health Unit. Primary and preventive health care offered by the SUS.</v>
       </c>
     </row>
-    <row r="86" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="60">
         <v>86</v>
       </c>
@@ -10891,7 +10892,7 @@
         <v>UPA Emergency Health Care Unit. Urgencies and emergencies 24x7.</v>
       </c>
     </row>
-    <row r="87" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="60">
         <v>87</v>
       </c>
@@ -10983,7 +10984,7 @@
         <v>Federal University.</v>
       </c>
     </row>
-    <row r="88" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="60">
         <v>88</v>
       </c>
@@ -11075,7 +11076,7 @@
         <v>State University.</v>
       </c>
     </row>
-    <row r="89" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="60">
         <v>89</v>
       </c>
@@ -11167,7 +11168,7 @@
         <v>State School.</v>
       </c>
     </row>
-    <row r="90" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="60">
         <v>90</v>
       </c>
@@ -11259,7 +11260,7 @@
         <v>Municipal School.</v>
       </c>
     </row>
-    <row r="91" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="60">
         <v>91</v>
       </c>
@@ -11351,7 +11352,7 @@
         <v>The application colleges are educational institutions linked to universities, with the mission of integrating theory and practice in the training of students and teachers.</v>
       </c>
     </row>
-    <row r="92" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="60">
         <v>92</v>
       </c>
@@ -11443,7 +11444,7 @@
         <v>Military education institutions include military elementary and secondary education colleges as well as the vocational schools of the Armed Forces.</v>
       </c>
     </row>
-    <row r="93" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="60">
         <v>93</v>
       </c>
@@ -11535,7 +11536,7 @@
         <v>Meteorological station managed by the National Institute of Meteorology (INMET) dependent on the Ministry of Agriculture and Livestock.</v>
       </c>
     </row>
-    <row r="94" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="60">
         <v>94</v>
       </c>
@@ -11627,7 +11628,7 @@
         <v>Automatic meteorological station managed by the National Institute of Meteorology (INMET) dependent on the Ministry of Agriculture and Livestock.</v>
       </c>
     </row>
-    <row r="95" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="60">
         <v>95</v>
       </c>
@@ -11719,7 +11720,7 @@
         <v>Conventional meteorological station managed by the National Institute of Meteorology (INMET) dependent on the Ministry of Agriculture and Livestock.</v>
       </c>
     </row>
-    <row r="96" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="60">
         <v>96</v>
       </c>
@@ -11811,7 +11812,7 @@
         <v>IBGE Index - Number of inhabitants per square kilometer measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="97" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="60">
         <v>97</v>
       </c>
@@ -11903,7 +11904,7 @@
         <v>IBGE Index - Number of inhabitants per square kilometer measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="98" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="60">
         <v>98</v>
       </c>
@@ -11995,7 +11996,7 @@
         <v>IBGE Index - IDU (Urban Development Index) evaluates the quality of life and access to urban services measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="99" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="60">
         <v>99</v>
       </c>
@@ -12087,7 +12088,7 @@
         <v>IBGE Index - Proportion between urban and rural population measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="100" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="60">
         <v>100</v>
       </c>
@@ -12186,7 +12187,7 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F101:F1048576 A1:D1 L1:Q1 S1:W1 AB1:XFD1 A101:D1048576 S101:W1048576 AA101:XFD1048576">
+  <conditionalFormatting sqref="F1 F101:F1048576 A1:D1 S1:W1 A101:D1048576 S101:W1048576 AA101:XFD1048576">
     <cfRule type="cellIs" dxfId="30" priority="444" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -12194,35 +12195,35 @@
   <conditionalFormatting sqref="F1">
     <cfRule type="duplicateValues" dxfId="29" priority="1482"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L2:Q6 S2:U28 AB2:XFD29 L7:O9 Q7:Q9 L10:Q29 S29:T29 U29:U40 O30:O40">
-    <cfRule type="cellIs" dxfId="27" priority="13" operator="equal">
+  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AB1:XFD29 S2:U28 L7:O9 Q7:Q9 L10:Q29 S29:T29 U29:U40 O30:O40">
+    <cfRule type="cellIs" dxfId="28" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="26" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F96:F100 F2:F93">
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101:F1048576 F1">
     <cfRule type="duplicateValues" dxfId="14" priority="147"/>
@@ -12236,8 +12237,8 @@
     <cfRule type="duplicateValues" dxfId="8" priority="972"/>
     <cfRule type="duplicateValues" dxfId="7" priority="980"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA100 V2:V100 A2:B100">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA1:AA100 A2:B100 V2:V100">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12248,15 +12249,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
@@ -12321,7 +12322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -12386,7 +12387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -12454,7 +12455,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12466,14 +12467,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21">
         <v>1</v>
       </c>
@@ -12487,7 +12488,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
         <v>2</v>
       </c>
@@ -12501,7 +12502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>3</v>
       </c>
@@ -12515,7 +12516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>4</v>
       </c>
@@ -12529,7 +12530,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -12543,7 +12544,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>6</v>
       </c>
@@ -12559,7 +12560,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A6">
-    <cfRule type="cellIs" dxfId="5" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12570,68 +12571,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.84375" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="8.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="9.7109375" style="46" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.140625" style="25"/>
+    <col min="15" max="15" width="34.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.3828125" style="25" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.69140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.15234375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="27" t="s">
         <v>74</v>
       </c>
@@ -12800,7 +12801,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="36">
         <v>2</v>
       </c>
@@ -12974,7 +12975,7 @@
         <v>"Continente"</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="36">
         <v>3</v>
       </c>
@@ -13148,7 +13149,7 @@
         <v>"SubContinente"</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="36">
         <v>4</v>
       </c>
@@ -13322,7 +13323,7 @@
         <v>"País"</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="36">
         <v>5</v>
       </c>
@@ -13496,7 +13497,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="36">
         <v>6</v>
       </c>
@@ -13670,7 +13671,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="36">
         <v>7</v>
       </c>
@@ -13844,7 +13845,7 @@
         <v>"Estado"</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="36">
         <v>8</v>
       </c>
@@ -14019,7 +14020,7 @@
         <v>"Capital"</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="36">
         <v>9</v>
       </c>
@@ -14193,7 +14194,7 @@
         <v>"UF"</v>
       </c>
     </row>
-    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="36">
         <v>10</v>
       </c>
@@ -14371,20 +14372,20 @@
   <autoFilter ref="F1:F6" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576 G2 G4:G5 H10:BB10 D10:F1048576 H11:XFD1048576">
-    <cfRule type="cellIs" dxfId="4" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:BB9">
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:F8 H4:BB8 BC4:XFD10 H1:XFD3">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="H1:XFD3 D1:F8 H4:BB8 BC4:XFD10">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B85A09-A651-4FB1-9694-8D6BECB7F5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F24CEC-543B-459B-82AC-1E1EA0AC0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2661" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="577">
   <si>
     <t>Key</t>
   </si>
@@ -1279,9 +1279,6 @@
     <t>[ OST_SpecialityEquipment ]</t>
   </si>
   <si>
-    <t>null ]</t>
-  </si>
-  <si>
     <t>[ IfcReferentBOUNDARY ]</t>
   </si>
   <si>
@@ -1333,9 +1330,6 @@
     <t>[ IfcBuildingElementProxy ]</t>
   </si>
   <si>
-    <t>[ null ]</t>
-  </si>
-  <si>
     <t>[ OST_ToposolidMembrane ]</t>
   </si>
   <si>
@@ -1786,10 +1780,31 @@
     <t>Classe IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parãmetro Rvt</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
   </si>
 </sst>
 </file>
@@ -1897,7 +1912,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2024,6 +2039,18 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE79D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2076,7 +2103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2281,11 +2308,71 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="38">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2331,14 +2418,6 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2949,7 +3028,7 @@
         <v>46</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C3" s="50" t="s">
         <v>376</v>
@@ -3105,7 +3184,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C17" s="50" t="s">
         <v>376</v>
@@ -3117,7 +3196,7 @@
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46253.656048726851</v>
+        <v>46258.60356909722</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>376</v>
@@ -3185,7 +3264,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C24" s="50" t="s">
         <v>376</v>
@@ -3196,7 +3275,7 @@
         <v>60</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C25" s="50" t="s">
         <v>377</v>
@@ -3221,7 +3300,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
@@ -3248,7 +3327,7 @@
     <col min="24" max="24" width="9.7109375" style="31" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="51.85546875" style="31" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" style="31" customWidth="1"/>
     <col min="28" max="28" width="6" style="31" customWidth="1"/>
     <col min="29" max="29" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
     <col min="30" max="16384" width="9.140625" style="31"/>
@@ -3331,13 +3410,13 @@
         <v>79</v>
       </c>
       <c r="Z1" s="16" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="AA1" s="16" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AB1" s="16" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AC1" s="16" t="s">
         <v>372</v>
@@ -3348,7 +3427,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>253</v>
@@ -3402,7 +3481,7 @@
         <v>80</v>
       </c>
       <c r="R2" s="64" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S2" s="64" t="s">
         <v>1</v>
@@ -3420,23 +3499,23 @@
         <v>Naturais</v>
       </c>
       <c r="W2" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X2" s="65" t="str">
-        <f t="shared" ref="X2:X61" si="2">CONCATENATE("Key-BRASIL-",A2)</f>
-        <v>Key-BRASIL-2</v>
+        <f>CONCATENATE("Key-BRASIL_MG-",A2)</f>
+        <v>Key-BRASIL_MG-2</v>
       </c>
       <c r="Y2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z2" s="68" t="s">
-        <v>570</v>
+      <c r="Z2" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="68" t="s">
-        <v>570</v>
+      <c r="AB2" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC2" s="68" t="s">
         <v>1</v>
@@ -3447,7 +3526,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C3" s="29" t="s">
         <v>253</v>
@@ -3481,15 +3560,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M3" s="67" t="str">
-        <f t="shared" ref="M3:O57" si="3">_xlfn.CONCAT(SUBSTITUTE(D3,"."," "))</f>
+        <f t="shared" ref="M3:O57" si="2">_xlfn.CONCAT(SUBSTITUTE(D3,"."," "))</f>
         <v>Geográficas</v>
       </c>
       <c r="N3" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Naturais</v>
       </c>
       <c r="O3" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>SubContinente</v>
       </c>
       <c r="P3" s="67" t="s">
@@ -3499,7 +3578,7 @@
         <v>81</v>
       </c>
       <c r="R3" s="64" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="S3" s="64" t="s">
         <v>1</v>
@@ -3517,23 +3596,23 @@
         <v>Naturais</v>
       </c>
       <c r="W3" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X3" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-3</v>
+        <f t="shared" ref="X3:X66" si="3">CONCATENATE("Key-BRASIL_MG-",A3)</f>
+        <v>Key-BRASIL_MG-3</v>
       </c>
       <c r="Y3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z3" s="68" t="s">
-        <v>570</v>
+      <c r="Z3" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="AB3" s="68" t="s">
-        <v>570</v>
+      <c r="AB3" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC3" s="68" t="s">
         <v>1</v>
@@ -3544,7 +3623,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C4" s="29" t="s">
         <v>253</v>
@@ -3578,15 +3657,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M4" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N4" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Naturais</v>
       </c>
       <c r="O4" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Bioma</v>
       </c>
       <c r="P4" s="67" t="s">
@@ -3596,7 +3675,7 @@
         <v>83</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="S4" s="64" t="s">
         <v>1</v>
@@ -3614,23 +3693,23 @@
         <v>Naturais</v>
       </c>
       <c r="W4" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X4" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-4</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-4</v>
       </c>
       <c r="Y4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z4" s="68" t="s">
-        <v>570</v>
+      <c r="Z4" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="AB4" s="68" t="s">
-        <v>570</v>
+      <c r="AB4" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC4" s="68" t="s">
         <v>1</v>
@@ -3641,7 +3720,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>253</v>
@@ -3676,15 +3755,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M5" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N5" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O5" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>País</v>
       </c>
       <c r="P5" s="67" t="s">
@@ -3694,7 +3773,7 @@
         <v>84</v>
       </c>
       <c r="R5" s="64" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="S5" s="64" t="s">
         <v>1</v>
@@ -3712,23 +3791,23 @@
         <v>Políticas</v>
       </c>
       <c r="W5" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X5" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-5</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-5</v>
       </c>
       <c r="Y5" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z5" s="68" t="s">
-        <v>570</v>
+      <c r="Z5" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA5" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB5" s="68" t="s">
-        <v>570</v>
+      <c r="AB5" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC5" s="68" t="s">
         <v>1</v>
@@ -3739,7 +3818,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>253</v>
@@ -3773,15 +3852,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M6" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N6" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O6" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Nação</v>
       </c>
       <c r="P6" s="67" t="s">
@@ -3791,7 +3870,7 @@
         <v>86</v>
       </c>
       <c r="R6" s="64" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="S6" s="64" t="s">
         <v>1</v>
@@ -3809,23 +3888,23 @@
         <v>Políticas</v>
       </c>
       <c r="W6" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X6" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-6</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-6</v>
       </c>
       <c r="Y6" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z6" s="68" t="s">
-        <v>570</v>
+      <c r="Z6" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA6" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB6" s="68" t="s">
-        <v>570</v>
+      <c r="AB6" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC6" s="68" t="s">
         <v>1</v>
@@ -3836,7 +3915,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C7" s="29" t="s">
         <v>253</v>
@@ -3870,26 +3949,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M7" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N7" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O7" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região</v>
       </c>
       <c r="P7" s="69" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q7" s="67" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","es")</f>
         <v>Región geográfica de Brasil. de Brasil hay 5 regiones geográficas principales.</v>
       </c>
       <c r="R7" s="64" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="S7" s="64" t="s">
         <v>1</v>
@@ -3907,23 +3986,23 @@
         <v>Políticas</v>
       </c>
       <c r="W7" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X7" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-7</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-7</v>
       </c>
       <c r="Y7" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z7" s="68" t="s">
-        <v>570</v>
+      <c r="Z7" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA7" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB7" s="68" t="s">
-        <v>570</v>
+      <c r="AB7" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC7" s="68" t="s">
         <v>1</v>
@@ -3934,7 +4013,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>253</v>
@@ -3946,7 +4025,7 @@
         <v>255</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G8" s="66" t="s">
         <v>1</v>
@@ -3968,26 +4047,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M8" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N8" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O8" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Intermediária</v>
       </c>
       <c r="P8" s="69" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Q8" s="67" t="str">
         <f t="shared" ref="Q8:Q9" si="4">_xlfn.TRANSLATE(P8,"pt","es")</f>
         <v>Región geográfica intermedia. Definidas por el IBGE de Brasil, existen 133 Regiones Geográficas Intermedias, de mayor escala, que se articulan por capitales regionales o grandes centros urbanos. Diseñado para organizar el territorio articulando las Regiones Geográficas Inmediatas a través de un polo jerárquico superior, diferenciado de los flujos de gestión privada y pública y de la existencia de funciones urbanas de mayor complejidad.</v>
       </c>
       <c r="R8" s="64" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="S8" s="64" t="s">
         <v>1</v>
@@ -4005,23 +4084,23 @@
         <v>Políticas</v>
       </c>
       <c r="W8" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X8" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-8</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-8</v>
       </c>
       <c r="Y8" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z8" s="68" t="s">
-        <v>570</v>
+      <c r="Z8" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA8" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB8" s="68" t="s">
-        <v>570</v>
+      <c r="AB8" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC8" s="68" t="s">
         <v>1</v>
@@ -4032,7 +4111,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>253</v>
@@ -4044,7 +4123,7 @@
         <v>255</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G9" s="66" t="s">
         <v>1</v>
@@ -4066,26 +4145,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M9" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N9" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O9" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Imediata</v>
       </c>
       <c r="P9" s="69" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q9" s="67" t="str">
         <f t="shared" si="4"/>
         <v>Región geográfica inmediata. Definida por el IBGE de Brasil, hay 510 regiones geográficas de menor escala, articuladas por ciudades medianas y pequeñas. Es en estos centros donde la población busca lo que necesita a diario: comprar productos, buscar empleo, acceder a servicios de salud y educación y resolver problemas en organismos públicos, como el INSS, el Ministerio de Trabajo y Justicia.</v>
       </c>
       <c r="R9" s="64" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="S9" s="64" t="s">
         <v>1</v>
@@ -4103,23 +4182,23 @@
         <v>Políticas</v>
       </c>
       <c r="W9" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X9" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-9</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-9</v>
       </c>
       <c r="Y9" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z9" s="68" t="s">
-        <v>570</v>
+      <c r="Z9" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA9" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB9" s="68" t="s">
-        <v>570</v>
+      <c r="AB9" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC9" s="68" t="s">
         <v>1</v>
@@ -4130,7 +4209,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>253</v>
@@ -4165,15 +4244,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M10" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N10" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O10" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Estado</v>
       </c>
       <c r="P10" s="67" t="s">
@@ -4183,7 +4262,7 @@
         <v>89</v>
       </c>
       <c r="R10" s="64" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="S10" s="64" t="s">
         <v>1</v>
@@ -4201,23 +4280,23 @@
         <v>Políticas</v>
       </c>
       <c r="W10" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X10" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-10</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-10</v>
       </c>
       <c r="Y10" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z10" s="68" t="s">
-        <v>570</v>
+      <c r="Z10" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA10" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB10" s="68" t="s">
-        <v>570</v>
+      <c r="AB10" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC10" s="68" t="s">
         <v>1</v>
@@ -4228,7 +4307,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>253</v>
@@ -4262,15 +4341,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M11" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N11" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O11" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>UF</v>
       </c>
       <c r="P11" s="67" t="s">
@@ -4280,7 +4359,7 @@
         <v>91</v>
       </c>
       <c r="R11" s="64" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S11" s="64" t="s">
         <v>1</v>
@@ -4298,23 +4377,23 @@
         <v>Políticas</v>
       </c>
       <c r="W11" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X11" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-11</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-11</v>
       </c>
       <c r="Y11" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z11" s="68" t="s">
-        <v>570</v>
+      <c r="Z11" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA11" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB11" s="68" t="s">
-        <v>570</v>
+      <c r="AB11" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC11" s="68" t="s">
         <v>1</v>
@@ -4325,7 +4404,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>253</v>
@@ -4360,15 +4439,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M12" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N12" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O12" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Província</v>
       </c>
       <c r="P12" s="67" t="s">
@@ -4378,7 +4457,7 @@
         <v>93</v>
       </c>
       <c r="R12" s="64" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="S12" s="64" t="s">
         <v>1</v>
@@ -4396,23 +4475,23 @@
         <v>Políticas</v>
       </c>
       <c r="W12" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X12" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-12</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-12</v>
       </c>
       <c r="Y12" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z12" s="68" t="s">
-        <v>570</v>
+      <c r="Z12" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA12" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB12" s="68" t="s">
-        <v>570</v>
+      <c r="AB12" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC12" s="68" t="s">
         <v>1</v>
@@ -4423,7 +4502,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C13" s="29" t="s">
         <v>253</v>
@@ -4458,25 +4537,25 @@
         <v>Fronteiras</v>
       </c>
       <c r="M13" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N13" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O13" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Capital</v>
       </c>
       <c r="P13" s="67" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q13" s="67" t="s">
         <v>94</v>
       </c>
       <c r="R13" s="64" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="S13" s="64" t="s">
         <v>1</v>
@@ -4494,23 +4573,23 @@
         <v>Políticas</v>
       </c>
       <c r="W13" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X13" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-13</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-13</v>
       </c>
       <c r="Y13" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z13" s="68" t="s">
-        <v>570</v>
+      <c r="Z13" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA13" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB13" s="68" t="s">
-        <v>570</v>
+      <c r="AB13" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC13" s="68" t="s">
         <v>1</v>
@@ -4521,7 +4600,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>253</v>
@@ -4533,7 +4612,7 @@
         <v>255</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G14" s="66" t="s">
         <v>1</v>
@@ -4556,26 +4635,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M14" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N14" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O14" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Capital do Sul</v>
       </c>
       <c r="P14" s="67" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q14" s="67" t="str">
         <f t="shared" ref="Q14:Q24" si="6">_xlfn.TRANSLATE(P14,"pt","es")</f>
         <v>Ciudad capital de un estado situado en la región sur de Brasil.</v>
       </c>
       <c r="R14" s="64" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="S14" s="64" t="s">
         <v>1</v>
@@ -4593,23 +4672,23 @@
         <v>Políticas</v>
       </c>
       <c r="W14" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X14" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-14</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-14</v>
       </c>
       <c r="Y14" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z14" s="68" t="s">
-        <v>570</v>
+      <c r="Z14" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA14" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB14" s="68" t="s">
-        <v>570</v>
+      <c r="AB14" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC14" s="68" t="s">
         <v>1</v>
@@ -4620,7 +4699,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>253</v>
@@ -4632,7 +4711,7 @@
         <v>255</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G15" s="66" t="s">
         <v>1</v>
@@ -4655,26 +4734,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M15" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N15" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O15" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Capital do Sudeste</v>
       </c>
       <c r="P15" s="67" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q15" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un estado situado en la región sureste de Brasil.</v>
       </c>
       <c r="R15" s="64" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="S15" s="64" t="s">
         <v>1</v>
@@ -4692,23 +4771,23 @@
         <v>Políticas</v>
       </c>
       <c r="W15" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X15" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-15</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-15</v>
       </c>
       <c r="Y15" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z15" s="68" t="s">
-        <v>570</v>
+      <c r="Z15" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA15" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB15" s="68" t="s">
-        <v>570</v>
+      <c r="AB15" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC15" s="68" t="s">
         <v>1</v>
@@ -4719,7 +4798,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>253</v>
@@ -4731,7 +4810,7 @@
         <v>255</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G16" s="66" t="s">
         <v>1</v>
@@ -4754,26 +4833,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M16" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N16" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O16" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Capital do Norte</v>
       </c>
       <c r="P16" s="67" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Q16" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un Estado situado en la región norte de Brasil.</v>
       </c>
       <c r="R16" s="64" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="S16" s="64" t="s">
         <v>1</v>
@@ -4791,23 +4870,23 @@
         <v>Políticas</v>
       </c>
       <c r="W16" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X16" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-16</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-16</v>
       </c>
       <c r="Y16" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z16" s="68" t="s">
-        <v>570</v>
+      <c r="Z16" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA16" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB16" s="68" t="s">
-        <v>570</v>
+      <c r="AB16" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC16" s="68" t="s">
         <v>1</v>
@@ -4818,7 +4897,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C17" s="29" t="s">
         <v>253</v>
@@ -4830,7 +4909,7 @@
         <v>255</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G17" s="66" t="s">
         <v>1</v>
@@ -4853,26 +4932,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M17" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N17" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O17" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Capital do Nordeste</v>
       </c>
       <c r="P17" s="67" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q17" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un estado situado en la región noreste de Brasil.</v>
       </c>
       <c r="R17" s="64" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="S17" s="64" t="s">
         <v>1</v>
@@ -4890,23 +4969,23 @@
         <v>Políticas</v>
       </c>
       <c r="W17" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X17" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-17</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-17</v>
       </c>
       <c r="Y17" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z17" s="68" t="s">
-        <v>570</v>
+      <c r="Z17" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA17" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB17" s="68" t="s">
-        <v>570</v>
+      <c r="AB17" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC17" s="68" t="s">
         <v>1</v>
@@ -4917,7 +4996,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>253</v>
@@ -4929,7 +5008,7 @@
         <v>255</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G18" s="66" t="s">
         <v>1</v>
@@ -4952,26 +5031,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M18" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N18" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O18" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Capital do CentroOeste</v>
       </c>
       <c r="P18" s="67" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q18" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un estado situado en la región del Medio Oeste de Brasil.</v>
       </c>
       <c r="R18" s="64" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="S18" s="64" t="s">
         <v>1</v>
@@ -4989,23 +5068,23 @@
         <v>Políticas</v>
       </c>
       <c r="W18" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X18" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-18</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-18</v>
       </c>
       <c r="Y18" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z18" s="68" t="s">
-        <v>570</v>
+      <c r="Z18" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA18" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB18" s="68" t="s">
-        <v>570</v>
+      <c r="AB18" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC18" s="68" t="s">
         <v>1</v>
@@ -5016,7 +5095,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C19" s="29" t="s">
         <v>253</v>
@@ -5051,26 +5130,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M19" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N19" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O19" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Cidade</v>
       </c>
       <c r="P19" s="67" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Q19" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad de Brasil.</v>
       </c>
       <c r="R19" s="64" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="S19" s="64" t="s">
         <v>1</v>
@@ -5088,23 +5167,23 @@
         <v>Políticas</v>
       </c>
       <c r="W19" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X19" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-19</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-19</v>
       </c>
       <c r="Y19" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z19" s="68" t="s">
-        <v>570</v>
+      <c r="Z19" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA19" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB19" s="68" t="s">
-        <v>570</v>
+      <c r="AB19" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC19" s="68" t="s">
         <v>1</v>
@@ -5115,7 +5194,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>253</v>
@@ -5127,7 +5206,7 @@
         <v>255</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G20" s="66" t="s">
         <v>1</v>
@@ -5150,26 +5229,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M20" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N20" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O20" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Cidade do Sul</v>
       </c>
       <c r="P20" s="67" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="Q20" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región sur de Brasil.</v>
       </c>
       <c r="R20" s="64" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="S20" s="64" t="s">
         <v>1</v>
@@ -5187,23 +5266,23 @@
         <v>Políticas</v>
       </c>
       <c r="W20" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X20" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-20</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-20</v>
       </c>
       <c r="Y20" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z20" s="68" t="s">
-        <v>570</v>
+      <c r="Z20" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA20" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB20" s="68" t="s">
-        <v>570</v>
+      <c r="AB20" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC20" s="68" t="s">
         <v>1</v>
@@ -5214,7 +5293,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>253</v>
@@ -5226,7 +5305,7 @@
         <v>255</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G21" s="66" t="s">
         <v>1</v>
@@ -5249,26 +5328,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M21" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N21" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O21" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Cidade do Sudeste</v>
       </c>
       <c r="P21" s="67" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Q21" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región sureste de Brasil.</v>
       </c>
       <c r="R21" s="64" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="S21" s="64" t="s">
         <v>1</v>
@@ -5286,23 +5365,23 @@
         <v>Políticas</v>
       </c>
       <c r="W21" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X21" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-21</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-21</v>
       </c>
       <c r="Y21" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z21" s="68" t="s">
-        <v>570</v>
+      <c r="Z21" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA21" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB21" s="68" t="s">
-        <v>570</v>
+      <c r="AB21" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC21" s="68" t="s">
         <v>1</v>
@@ -5313,7 +5392,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>253</v>
@@ -5325,7 +5404,7 @@
         <v>255</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G22" s="66" t="s">
         <v>1</v>
@@ -5348,26 +5427,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M22" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N22" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O22" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Cidade do Norte</v>
       </c>
       <c r="P22" s="67" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Q22" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región norte de Brasil.</v>
       </c>
       <c r="R22" s="64" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="S22" s="64" t="s">
         <v>1</v>
@@ -5385,23 +5464,23 @@
         <v>Políticas</v>
       </c>
       <c r="W22" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X22" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-22</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-22</v>
       </c>
       <c r="Y22" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z22" s="68" t="s">
-        <v>570</v>
+      <c r="Z22" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA22" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB22" s="68" t="s">
-        <v>570</v>
+      <c r="AB22" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC22" s="68" t="s">
         <v>1</v>
@@ -5412,7 +5491,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C23" s="29" t="s">
         <v>253</v>
@@ -5424,7 +5503,7 @@
         <v>255</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G23" s="66" t="s">
         <v>1</v>
@@ -5447,26 +5526,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M23" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N23" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O23" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Cidade do Nordeste</v>
       </c>
       <c r="P23" s="67" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Q23" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región noreste de Brasil.</v>
       </c>
       <c r="R23" s="64" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="S23" s="64" t="s">
         <v>1</v>
@@ -5484,23 +5563,23 @@
         <v>Políticas</v>
       </c>
       <c r="W23" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X23" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-23</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-23</v>
       </c>
       <c r="Y23" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z23" s="68" t="s">
-        <v>570</v>
+      <c r="Z23" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA23" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB23" s="68" t="s">
-        <v>570</v>
+      <c r="AB23" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC23" s="68" t="s">
         <v>1</v>
@@ -5511,7 +5590,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C24" s="29" t="s">
         <v>253</v>
@@ -5523,7 +5602,7 @@
         <v>255</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G24" s="66" t="s">
         <v>1</v>
@@ -5546,26 +5625,26 @@
         <v>Fronteiras</v>
       </c>
       <c r="M24" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N24" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O24" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Cidade do CentroOeste</v>
       </c>
       <c r="P24" s="67" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="Q24" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región del Medio Oeste de Brasil.</v>
       </c>
       <c r="R24" s="64" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="S24" s="64" t="s">
         <v>1</v>
@@ -5583,23 +5662,23 @@
         <v>Políticas</v>
       </c>
       <c r="W24" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X24" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-24</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-24</v>
       </c>
       <c r="Y24" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z24" s="68" t="s">
-        <v>570</v>
+      <c r="Z24" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA24" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB24" s="68" t="s">
-        <v>570</v>
+      <c r="AB24" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC24" s="68" t="s">
         <v>1</v>
@@ -5610,7 +5689,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C25" s="29" t="s">
         <v>253</v>
@@ -5645,15 +5724,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M25" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N25" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O25" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Metrópoli</v>
       </c>
       <c r="P25" s="67" t="s">
@@ -5663,7 +5742,7 @@
         <v>95</v>
       </c>
       <c r="R25" s="64" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="S25" s="64" t="s">
         <v>1</v>
@@ -5681,23 +5760,23 @@
         <v>Políticas</v>
       </c>
       <c r="W25" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X25" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-25</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-25</v>
       </c>
       <c r="Y25" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z25" s="68" t="s">
-        <v>570</v>
+      <c r="Z25" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA25" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB25" s="68" t="s">
-        <v>570</v>
+      <c r="AB25" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC25" s="68" t="s">
         <v>1</v>
@@ -5708,7 +5787,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C26" s="29" t="s">
         <v>253</v>
@@ -5743,15 +5822,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M26" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Geográficas</v>
       </c>
       <c r="N26" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Políticas</v>
       </c>
       <c r="O26" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Município</v>
       </c>
       <c r="P26" s="67" t="s">
@@ -5761,7 +5840,7 @@
         <v>97</v>
       </c>
       <c r="R26" s="64" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="S26" s="64" t="s">
         <v>1</v>
@@ -5779,23 +5858,23 @@
         <v>Políticas</v>
       </c>
       <c r="W26" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X26" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-26</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-26</v>
       </c>
       <c r="Y26" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z26" s="68" t="s">
-        <v>570</v>
+      <c r="Z26" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA26" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB26" s="68" t="s">
-        <v>570</v>
+      <c r="AB26" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC26" s="68" t="s">
         <v>1</v>
@@ -5806,7 +5885,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C27" s="29" t="s">
         <v>253</v>
@@ -5841,15 +5920,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M27" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Térmicas</v>
       </c>
       <c r="N27" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Bioclimáticas</v>
       </c>
       <c r="O27" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Climática</v>
       </c>
       <c r="P27" s="67" t="s">
@@ -5859,7 +5938,7 @@
         <v>99</v>
       </c>
       <c r="R27" s="64" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="S27" s="64" t="s">
         <v>1</v>
@@ -5877,23 +5956,23 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W27" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X27" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-27</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-27</v>
       </c>
       <c r="Y27" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z27" s="68" t="s">
-        <v>570</v>
+      <c r="Z27" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA27" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB27" s="68" t="s">
-        <v>570</v>
+      <c r="AB27" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC27" s="68" t="s">
         <v>1</v>
@@ -5904,7 +5983,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C28" s="29" t="s">
         <v>253</v>
@@ -5939,15 +6018,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M28" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Térmicas</v>
       </c>
       <c r="N28" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Bioclimáticas</v>
       </c>
       <c r="O28" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zona Climática</v>
       </c>
       <c r="P28" s="67" t="s">
@@ -5957,7 +6036,7 @@
         <v>101</v>
       </c>
       <c r="R28" s="64" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="S28" s="64" t="s">
         <v>1</v>
@@ -5975,23 +6054,23 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W28" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X28" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-28</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-28</v>
       </c>
       <c r="Y28" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z28" s="68" t="s">
-        <v>570</v>
+      <c r="Z28" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA28" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB28" s="68" t="s">
-        <v>570</v>
+      <c r="AB28" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC28" s="68" t="s">
         <v>1</v>
@@ -6002,7 +6081,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C29" s="29" t="s">
         <v>253</v>
@@ -6037,15 +6116,15 @@
         <v>Fronteiras</v>
       </c>
       <c r="M29" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Térmicas</v>
       </c>
       <c r="N29" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Ilhas de Calor</v>
       </c>
       <c r="O29" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zona Climática Local</v>
       </c>
       <c r="P29" s="67" t="s">
@@ -6055,7 +6134,7 @@
         <v>103</v>
       </c>
       <c r="R29" s="64" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="S29" s="64" t="s">
         <v>1</v>
@@ -6073,23 +6152,23 @@
         <v>Ilhas de Calor</v>
       </c>
       <c r="W29" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X29" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-29</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-29</v>
       </c>
       <c r="Y29" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z29" s="68" t="s">
-        <v>570</v>
+      <c r="Z29" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA29" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB29" s="68" t="s">
-        <v>570</v>
+      <c r="AB29" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC29" s="68" t="s">
         <v>1</v>
@@ -6100,7 +6179,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C30" s="29" t="s">
         <v>253</v>
@@ -6152,7 +6231,7 @@
         <v>223</v>
       </c>
       <c r="R30" s="64" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="S30" s="64" t="s">
         <v>1</v>
@@ -6170,23 +6249,23 @@
         <v>Marcos</v>
       </c>
       <c r="W30" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X30" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-30</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-30</v>
       </c>
       <c r="Y30" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z30" s="68" t="s">
-        <v>570</v>
+      <c r="Z30" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA30" s="68" t="s">
-        <v>402</v>
-      </c>
-      <c r="AB30" s="68" t="s">
-        <v>570</v>
+        <v>401</v>
+      </c>
+      <c r="AB30" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC30" s="68" t="s">
         <v>1</v>
@@ -6197,7 +6276,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C31" s="29" t="s">
         <v>253</v>
@@ -6249,7 +6328,7 @@
         <v>225</v>
       </c>
       <c r="R31" s="64" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="S31" s="64" t="s">
         <v>1</v>
@@ -6267,23 +6346,23 @@
         <v>Marcos</v>
       </c>
       <c r="W31" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X31" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-31</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-31</v>
       </c>
       <c r="Y31" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z31" s="68" t="s">
-        <v>570</v>
+      <c r="Z31" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA31" s="68" t="s">
-        <v>403</v>
-      </c>
-      <c r="AB31" s="68" t="s">
-        <v>570</v>
+        <v>402</v>
+      </c>
+      <c r="AB31" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC31" s="68" t="s">
         <v>1</v>
@@ -6294,7 +6373,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C32" s="29" t="s">
         <v>253</v>
@@ -6346,7 +6425,7 @@
         <v>227</v>
       </c>
       <c r="R32" s="64" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="S32" s="64" t="s">
         <v>1</v>
@@ -6364,23 +6443,23 @@
         <v>Marcos</v>
       </c>
       <c r="W32" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X32" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-32</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-32</v>
       </c>
       <c r="Y32" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z32" s="68" t="s">
-        <v>570</v>
+      <c r="Z32" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA32" s="68" t="s">
-        <v>404</v>
-      </c>
-      <c r="AB32" s="68" t="s">
-        <v>570</v>
+        <v>403</v>
+      </c>
+      <c r="AB32" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC32" s="68" t="s">
         <v>1</v>
@@ -6391,7 +6470,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>253</v>
@@ -6443,7 +6522,7 @@
         <v>235</v>
       </c>
       <c r="R33" s="64" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="S33" s="64" t="s">
         <v>1</v>
@@ -6461,23 +6540,23 @@
         <v>Marcos</v>
       </c>
       <c r="W33" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X33" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-33</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-33</v>
       </c>
       <c r="Y33" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z33" s="68" t="s">
-        <v>570</v>
+      <c r="Z33" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA33" s="68" t="s">
-        <v>405</v>
-      </c>
-      <c r="AB33" s="68" t="s">
-        <v>570</v>
+        <v>404</v>
+      </c>
+      <c r="AB33" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC33" s="68" t="s">
         <v>1</v>
@@ -6488,7 +6567,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C34" s="29" t="s">
         <v>253</v>
@@ -6540,7 +6619,7 @@
         <v>229</v>
       </c>
       <c r="R34" s="64" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S34" s="64" t="s">
         <v>1</v>
@@ -6558,23 +6637,23 @@
         <v>Marcos</v>
       </c>
       <c r="W34" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X34" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-34</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-34</v>
       </c>
       <c r="Y34" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z34" s="68" t="s">
-        <v>570</v>
+      <c r="Z34" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA34" s="68" t="s">
-        <v>406</v>
-      </c>
-      <c r="AB34" s="68" t="s">
-        <v>570</v>
+        <v>405</v>
+      </c>
+      <c r="AB34" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC34" s="68" t="s">
         <v>1</v>
@@ -6585,7 +6664,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C35" s="29" t="s">
         <v>253</v>
@@ -6637,7 +6716,7 @@
         <v>231</v>
       </c>
       <c r="R35" s="64" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="S35" s="64" t="s">
         <v>1</v>
@@ -6655,23 +6734,23 @@
         <v>Marcos</v>
       </c>
       <c r="W35" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X35" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-35</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-35</v>
       </c>
       <c r="Y35" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z35" s="68" t="s">
-        <v>570</v>
+      <c r="Z35" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA35" s="68" t="s">
-        <v>407</v>
-      </c>
-      <c r="AB35" s="68" t="s">
-        <v>570</v>
+        <v>406</v>
+      </c>
+      <c r="AB35" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC35" s="68" t="s">
         <v>1</v>
@@ -6682,7 +6761,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C36" s="29" t="s">
         <v>253</v>
@@ -6734,7 +6813,7 @@
         <v>233</v>
       </c>
       <c r="R36" s="64" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="S36" s="64" t="s">
         <v>1</v>
@@ -6752,23 +6831,23 @@
         <v>Marcos</v>
       </c>
       <c r="W36" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X36" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-36</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-36</v>
       </c>
       <c r="Y36" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z36" s="68" t="s">
-        <v>570</v>
+      <c r="Z36" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA36" s="68" t="s">
-        <v>408</v>
-      </c>
-      <c r="AB36" s="68" t="s">
-        <v>570</v>
+        <v>407</v>
+      </c>
+      <c r="AB36" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC36" s="68" t="s">
         <v>1</v>
@@ -6779,7 +6858,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C37" s="29" t="s">
         <v>253</v>
@@ -6831,7 +6910,7 @@
         <v>237</v>
       </c>
       <c r="R37" s="64" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="S37" s="64" t="s">
         <v>1</v>
@@ -6849,23 +6928,23 @@
         <v>Marcos</v>
       </c>
       <c r="W37" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X37" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-37</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-37</v>
       </c>
       <c r="Y37" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z37" s="68" t="s">
-        <v>570</v>
+      <c r="Z37" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA37" s="68" t="s">
-        <v>409</v>
-      </c>
-      <c r="AB37" s="68" t="s">
-        <v>570</v>
+        <v>408</v>
+      </c>
+      <c r="AB37" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC37" s="68" t="s">
         <v>1</v>
@@ -6876,7 +6955,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C38" s="29" t="s">
         <v>253</v>
@@ -6928,7 +7007,7 @@
         <v>239</v>
       </c>
       <c r="R38" s="64" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="S38" s="64" t="s">
         <v>1</v>
@@ -6946,23 +7025,23 @@
         <v>Marcos</v>
       </c>
       <c r="W38" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X38" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-38</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-38</v>
       </c>
       <c r="Y38" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z38" s="68" t="s">
-        <v>570</v>
+      <c r="Z38" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA38" s="68" t="s">
-        <v>410</v>
-      </c>
-      <c r="AB38" s="68" t="s">
-        <v>570</v>
+        <v>409</v>
+      </c>
+      <c r="AB38" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC38" s="68" t="s">
         <v>1</v>
@@ -6973,7 +7052,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C39" s="29" t="s">
         <v>253</v>
@@ -7025,7 +7104,7 @@
         <v>241</v>
       </c>
       <c r="R39" s="64" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S39" s="64" t="s">
         <v>1</v>
@@ -7043,23 +7122,23 @@
         <v>Marcos</v>
       </c>
       <c r="W39" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X39" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-39</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-39</v>
       </c>
       <c r="Y39" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z39" s="68" t="s">
-        <v>570</v>
+      <c r="Z39" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA39" s="68" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB39" s="68" t="s">
-        <v>570</v>
+        <v>410</v>
+      </c>
+      <c r="AB39" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC39" s="68" t="s">
         <v>1</v>
@@ -7070,7 +7149,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>253</v>
@@ -7122,7 +7201,7 @@
         <v>243</v>
       </c>
       <c r="R40" s="64" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S40" s="64" t="s">
         <v>1</v>
@@ -7140,23 +7219,23 @@
         <v>Marcos</v>
       </c>
       <c r="W40" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X40" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-40</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-40</v>
       </c>
       <c r="Y40" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z40" s="68" t="s">
-        <v>570</v>
+      <c r="Z40" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA40" s="68" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB40" s="68" t="s">
-        <v>570</v>
+        <v>411</v>
+      </c>
+      <c r="AB40" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC40" s="68" t="s">
         <v>1</v>
@@ -7167,10 +7246,10 @@
         <v>41</v>
       </c>
       <c r="B41" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>273</v>
@@ -7219,7 +7298,7 @@
         <v>350</v>
       </c>
       <c r="R41" s="64" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="S41" s="64" t="s">
         <v>1</v>
@@ -7237,23 +7316,23 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W41" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X41" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-41</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-41</v>
       </c>
       <c r="Y41" s="64" t="s">
         <v>386</v>
       </c>
-      <c r="Z41" s="68" t="s">
-        <v>570</v>
+      <c r="Z41" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA41" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB41" s="68" t="s">
-        <v>570</v>
+        <v>411</v>
+      </c>
+      <c r="AB41" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC41" s="68" t="s">
         <v>1</v>
@@ -7264,10 +7343,10 @@
         <v>42</v>
       </c>
       <c r="B42" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>273</v>
@@ -7316,7 +7395,7 @@
         <v>351</v>
       </c>
       <c r="R42" s="64" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S42" s="64" t="s">
         <v>1</v>
@@ -7334,23 +7413,23 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W42" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X42" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-42</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-42</v>
       </c>
       <c r="Y42" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="Z42" s="68" t="s">
-        <v>570</v>
+      <c r="Z42" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA42" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB42" s="68" t="s">
-        <v>570</v>
+        <v>412</v>
+      </c>
+      <c r="AB42" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC42" s="68" t="s">
         <v>1</v>
@@ -7361,10 +7440,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D43" s="29" t="s">
         <v>273</v>
@@ -7413,7 +7492,7 @@
         <v>352</v>
       </c>
       <c r="R43" s="64" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S43" s="64" t="s">
         <v>1</v>
@@ -7431,23 +7510,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W43" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X43" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-43</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-43</v>
       </c>
       <c r="Y43" s="64" t="s">
         <v>388</v>
       </c>
-      <c r="Z43" s="68" t="s">
-        <v>570</v>
+      <c r="Z43" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA43" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB43" s="68" t="s">
-        <v>570</v>
+        <v>412</v>
+      </c>
+      <c r="AB43" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC43" s="68" t="s">
         <v>1</v>
@@ -7458,10 +7537,10 @@
         <v>44</v>
       </c>
       <c r="B44" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D44" s="29" t="s">
         <v>273</v>
@@ -7492,11 +7571,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M44" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N44" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O44" s="67" t="str">
@@ -7510,7 +7589,7 @@
         <v>353</v>
       </c>
       <c r="R44" s="64" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S44" s="64" t="s">
         <v>1</v>
@@ -7528,23 +7607,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W44" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X44" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-44</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-44</v>
       </c>
       <c r="Y44" s="64" t="s">
         <v>389</v>
       </c>
-      <c r="Z44" s="68" t="s">
-        <v>570</v>
+      <c r="Z44" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA44" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB44" s="68" t="s">
-        <v>570</v>
+        <v>412</v>
+      </c>
+      <c r="AB44" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC44" s="68" t="s">
         <v>1</v>
@@ -7555,10 +7634,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D45" s="29" t="s">
         <v>273</v>
@@ -7589,11 +7668,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M45" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N45" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O45" s="67" t="str">
@@ -7607,7 +7686,7 @@
         <v>354</v>
       </c>
       <c r="R45" s="64" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S45" s="64" t="s">
         <v>1</v>
@@ -7625,23 +7704,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W45" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X45" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-45</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-45</v>
       </c>
       <c r="Y45" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="Z45" s="68" t="s">
-        <v>570</v>
+      <c r="Z45" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA45" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB45" s="68" t="s">
-        <v>570</v>
+        <v>412</v>
+      </c>
+      <c r="AB45" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC45" s="68" t="s">
         <v>1</v>
@@ -7652,10 +7731,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D46" s="29" t="s">
         <v>273</v>
@@ -7686,11 +7765,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M46" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N46" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O46" s="67" t="str">
@@ -7704,7 +7783,7 @@
         <v>355</v>
       </c>
       <c r="R46" s="64" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="S46" s="64" t="s">
         <v>1</v>
@@ -7722,23 +7801,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W46" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X46" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-46</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-46</v>
       </c>
       <c r="Y46" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="Z46" s="68" t="s">
-        <v>570</v>
+      <c r="Z46" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA46" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB46" s="68" t="s">
-        <v>570</v>
+        <v>412</v>
+      </c>
+      <c r="AB46" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC46" s="68" t="s">
         <v>1</v>
@@ -7749,10 +7828,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D47" s="29" t="s">
         <v>273</v>
@@ -7783,11 +7862,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M47" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N47" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O47" s="67" t="str">
@@ -7801,7 +7880,7 @@
         <v>356</v>
       </c>
       <c r="R47" s="64" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="S47" s="64" t="s">
         <v>1</v>
@@ -7819,23 +7898,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W47" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X47" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-47</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-47</v>
       </c>
       <c r="Y47" s="64" t="s">
-        <v>420</v>
-      </c>
-      <c r="Z47" s="68" t="s">
-        <v>570</v>
+        <v>418</v>
+      </c>
+      <c r="Z47" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA47" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB47" s="68" t="s">
-        <v>570</v>
+        <v>412</v>
+      </c>
+      <c r="AB47" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC47" s="68" t="s">
         <v>1</v>
@@ -7846,10 +7925,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D48" s="29" t="s">
         <v>273</v>
@@ -7880,11 +7959,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M48" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N48" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O48" s="67" t="str">
@@ -7898,7 +7977,7 @@
         <v>357</v>
       </c>
       <c r="R48" s="64" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="S48" s="64" t="s">
         <v>1</v>
@@ -7916,23 +7995,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W48" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X48" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-48</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-48</v>
       </c>
       <c r="Y48" s="64" t="s">
         <v>392</v>
       </c>
-      <c r="Z48" s="68" t="s">
-        <v>570</v>
+      <c r="Z48" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA48" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB48" s="68" t="s">
-        <v>570</v>
+        <v>412</v>
+      </c>
+      <c r="AB48" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC48" s="68" t="s">
         <v>1</v>
@@ -7943,10 +8022,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D49" s="29" t="s">
         <v>273</v>
@@ -7977,11 +8056,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M49" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N49" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Terrenos</v>
       </c>
       <c r="O49" s="67" t="str">
@@ -7995,7 +8074,7 @@
         <v>358</v>
       </c>
       <c r="R49" s="64" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S49" s="64" t="s">
         <v>1</v>
@@ -8013,23 +8092,23 @@
         <v>Terrenos</v>
       </c>
       <c r="W49" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X49" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-49</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-49</v>
       </c>
       <c r="Y49" s="64" t="s">
         <v>393</v>
       </c>
-      <c r="Z49" s="68" t="s">
-        <v>570</v>
+      <c r="Z49" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA49" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB49" s="68" t="s">
-        <v>570</v>
+        <v>413</v>
+      </c>
+      <c r="AB49" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC49" s="68" t="s">
         <v>1</v>
@@ -8040,10 +8119,10 @@
         <v>50</v>
       </c>
       <c r="B50" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D50" s="29" t="s">
         <v>273</v>
@@ -8074,11 +8153,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M50" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N50" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O50" s="67" t="str">
@@ -8092,7 +8171,7 @@
         <v>359</v>
       </c>
       <c r="R50" s="64" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S50" s="64" t="s">
         <v>1</v>
@@ -8110,23 +8189,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W50" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X50" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-50</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-50</v>
       </c>
       <c r="Y50" s="64" t="s">
         <v>394</v>
       </c>
-      <c r="Z50" s="68" t="s">
-        <v>570</v>
+      <c r="Z50" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA50" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB50" s="68" t="s">
-        <v>570</v>
+        <v>413</v>
+      </c>
+      <c r="AB50" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC50" s="68" t="s">
         <v>1</v>
@@ -8137,10 +8216,10 @@
         <v>51</v>
       </c>
       <c r="B51" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D51" s="29" t="s">
         <v>273</v>
@@ -8171,11 +8250,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M51" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N51" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O51" s="67" t="str">
@@ -8189,7 +8268,7 @@
         <v>360</v>
       </c>
       <c r="R51" s="64" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S51" s="64" t="s">
         <v>1</v>
@@ -8207,23 +8286,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W51" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X51" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-51</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-51</v>
       </c>
       <c r="Y51" s="64" t="s">
         <v>394</v>
       </c>
-      <c r="Z51" s="68" t="s">
-        <v>570</v>
+      <c r="Z51" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA51" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB51" s="68" t="s">
-        <v>570</v>
+        <v>413</v>
+      </c>
+      <c r="AB51" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC51" s="68" t="s">
         <v>1</v>
@@ -8234,10 +8313,10 @@
         <v>52</v>
       </c>
       <c r="B52" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D52" s="29" t="s">
         <v>273</v>
@@ -8268,11 +8347,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M52" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N52" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O52" s="67" t="str">
@@ -8286,7 +8365,7 @@
         <v>361</v>
       </c>
       <c r="R52" s="64" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="S52" s="64" t="s">
         <v>1</v>
@@ -8304,23 +8383,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W52" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X52" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-52</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-52</v>
       </c>
       <c r="Y52" s="64" t="s">
         <v>394</v>
       </c>
-      <c r="Z52" s="68" t="s">
-        <v>570</v>
+      <c r="Z52" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA52" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB52" s="68" t="s">
-        <v>570</v>
+        <v>413</v>
+      </c>
+      <c r="AB52" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC52" s="68" t="s">
         <v>1</v>
@@ -8331,10 +8410,10 @@
         <v>53</v>
       </c>
       <c r="B53" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D53" s="29" t="s">
         <v>273</v>
@@ -8365,11 +8444,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M53" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N53" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Curvas de Nível</v>
       </c>
       <c r="O53" s="67" t="str">
@@ -8383,7 +8462,7 @@
         <v>362</v>
       </c>
       <c r="R53" s="64" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="S53" s="64" t="s">
         <v>1</v>
@@ -8401,23 +8480,23 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W53" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X53" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-53</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-53</v>
       </c>
       <c r="Y53" s="64" t="s">
         <v>394</v>
       </c>
-      <c r="Z53" s="68" t="s">
-        <v>570</v>
+      <c r="Z53" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA53" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB53" s="68" t="s">
-        <v>570</v>
+        <v>411</v>
+      </c>
+      <c r="AB53" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC53" s="68" t="s">
         <v>1</v>
@@ -8428,10 +8507,10 @@
         <v>54</v>
       </c>
       <c r="B54" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D54" s="29" t="s">
         <v>273</v>
@@ -8462,11 +8541,11 @@
         <v>Topográficos</v>
       </c>
       <c r="M54" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Altimetrias</v>
       </c>
       <c r="N54" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Sondagens</v>
       </c>
       <c r="O54" s="67" t="str">
@@ -8480,7 +8559,7 @@
         <v>363</v>
       </c>
       <c r="R54" s="64" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="S54" s="64" t="s">
         <v>1</v>
@@ -8498,23 +8577,23 @@
         <v>Sondagens</v>
       </c>
       <c r="W54" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X54" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-54</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-54</v>
       </c>
       <c r="Y54" s="64" t="s">
         <v>386</v>
       </c>
-      <c r="Z54" s="68" t="s">
-        <v>570</v>
+      <c r="Z54" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA54" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB54" s="68" t="s">
-        <v>570</v>
+      <c r="AB54" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC54" s="68" t="s">
         <v>1</v>
@@ -8525,13 +8604,13 @@
         <v>55</v>
       </c>
       <c r="B55" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C55" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E55" s="29" t="s">
         <v>270</v>
@@ -8562,15 +8641,15 @@
         <v>Urbanísticos</v>
       </c>
       <c r="M55" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>De Planejamento</v>
       </c>
       <c r="N55" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zonificações</v>
       </c>
       <c r="O55" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Area de Planejamento</v>
       </c>
       <c r="P55" s="67" t="s">
@@ -8580,7 +8659,7 @@
         <v>105</v>
       </c>
       <c r="R55" s="64" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="S55" s="64" t="s">
         <v>1</v>
@@ -8598,23 +8677,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W55" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X55" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-55</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-55</v>
       </c>
       <c r="Y55" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z55" s="68" t="s">
-        <v>570</v>
+      <c r="Z55" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA55" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB55" s="68" t="s">
-        <v>570</v>
+      <c r="AB55" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC55" s="68" t="s">
         <v>1</v>
@@ -8625,13 +8704,13 @@
         <v>56</v>
       </c>
       <c r="B56" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E56" s="29" t="s">
         <v>270</v>
@@ -8661,15 +8740,15 @@
         <v>Urbanísticos</v>
       </c>
       <c r="M56" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>De Planejamento</v>
       </c>
       <c r="N56" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zonificações</v>
       </c>
       <c r="O56" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Região Administrativa</v>
       </c>
       <c r="P56" s="67" t="s">
@@ -8679,7 +8758,7 @@
         <v>107</v>
       </c>
       <c r="R56" s="64" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="S56" s="64" t="s">
         <v>1</v>
@@ -8697,23 +8776,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W56" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X56" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-56</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-56</v>
       </c>
       <c r="Y56" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z56" s="68" t="s">
-        <v>570</v>
+      <c r="Z56" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA56" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB56" s="68" t="s">
-        <v>570</v>
+      <c r="AB56" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC56" s="68" t="s">
         <v>1</v>
@@ -8724,13 +8803,13 @@
         <v>57</v>
       </c>
       <c r="B57" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C57" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E57" s="29" t="s">
         <v>270</v>
@@ -8758,15 +8837,15 @@
         <v>Urbanísticos</v>
       </c>
       <c r="M57" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>De Planejamento</v>
       </c>
       <c r="N57" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Zonificações</v>
       </c>
       <c r="O57" s="67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Area de Interesse Especial</v>
       </c>
       <c r="P57" s="67" t="s">
@@ -8776,7 +8855,7 @@
         <v>108</v>
       </c>
       <c r="R57" s="64" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="S57" s="64" t="s">
         <v>1</v>
@@ -8794,23 +8873,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W57" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X57" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-57</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-57</v>
       </c>
       <c r="Y57" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z57" s="68" t="s">
-        <v>570</v>
+      <c r="Z57" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA57" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB57" s="68" t="s">
-        <v>570</v>
+      <c r="AB57" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC57" s="68" t="s">
         <v>1</v>
@@ -8821,13 +8900,13 @@
         <v>58</v>
       </c>
       <c r="B58" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E58" s="29" t="s">
         <v>270</v>
@@ -8873,7 +8952,7 @@
         <v>111</v>
       </c>
       <c r="R58" s="64" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S58" s="64" t="s">
         <v>1</v>
@@ -8891,23 +8970,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W58" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X58" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-58</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-58</v>
       </c>
       <c r="Y58" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z58" s="68" t="s">
-        <v>570</v>
+      <c r="Z58" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA58" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB58" s="68" t="s">
-        <v>570</v>
+      <c r="AB58" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC58" s="68" t="s">
         <v>1</v>
@@ -8918,13 +8997,13 @@
         <v>59</v>
       </c>
       <c r="B59" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C59" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E59" s="29" t="s">
         <v>270</v>
@@ -8970,7 +9049,7 @@
         <v>114</v>
       </c>
       <c r="R59" s="64" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="S59" s="64" t="s">
         <v>1</v>
@@ -8988,23 +9067,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W59" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X59" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-59</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-59</v>
       </c>
       <c r="Y59" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z59" s="68" t="s">
-        <v>570</v>
+      <c r="Z59" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA59" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB59" s="68" t="s">
-        <v>570</v>
+      <c r="AB59" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC59" s="68" t="s">
         <v>1</v>
@@ -9015,13 +9094,13 @@
         <v>60</v>
       </c>
       <c r="B60" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C60" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E60" s="29" t="s">
         <v>270</v>
@@ -9067,7 +9146,7 @@
         <v>117</v>
       </c>
       <c r="R60" s="64" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="S60" s="64" t="s">
         <v>1</v>
@@ -9085,23 +9164,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W60" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X60" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-60</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-60</v>
       </c>
       <c r="Y60" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z60" s="68" t="s">
-        <v>570</v>
+      <c r="Z60" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA60" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB60" s="68" t="s">
-        <v>570</v>
+      <c r="AB60" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC60" s="68" t="s">
         <v>1</v>
@@ -9112,13 +9191,13 @@
         <v>61</v>
       </c>
       <c r="B61" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C61" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>270</v>
@@ -9164,7 +9243,7 @@
         <v>118</v>
       </c>
       <c r="R61" s="64" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="S61" s="64" t="s">
         <v>1</v>
@@ -9182,23 +9261,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W61" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X61" s="65" t="str">
-        <f t="shared" si="2"/>
-        <v>Key-BRASIL-61</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-61</v>
       </c>
       <c r="Y61" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z61" s="68" t="s">
-        <v>570</v>
+      <c r="Z61" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA61" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB61" s="68" t="s">
-        <v>570</v>
+      <c r="AB61" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC61" s="68" t="s">
         <v>1</v>
@@ -9209,13 +9288,13 @@
         <v>62</v>
       </c>
       <c r="B62" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C62" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E62" s="29" t="s">
         <v>270</v>
@@ -9261,7 +9340,7 @@
         <v>117</v>
       </c>
       <c r="R62" s="64" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="S62" s="64" t="s">
         <v>1</v>
@@ -9279,23 +9358,23 @@
         <v>Zonificações</v>
       </c>
       <c r="W62" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X62" s="65" t="str">
-        <f t="shared" ref="X62:X100" si="15">CONCATENATE("Key-BRASIL-",A62)</f>
-        <v>Key-BRASIL-62</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-62</v>
       </c>
       <c r="Y62" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z62" s="68" t="s">
-        <v>570</v>
+      <c r="Z62" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA62" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB62" s="68" t="s">
-        <v>570</v>
+        <v>414</v>
+      </c>
+      <c r="AB62" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC62" s="68" t="s">
         <v>1</v>
@@ -9306,13 +9385,13 @@
         <v>63</v>
       </c>
       <c r="B63" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C63" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E63" s="29" t="s">
         <v>269</v>
@@ -9358,7 +9437,7 @@
         <v>122</v>
       </c>
       <c r="R63" s="64" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="S63" s="64" t="s">
         <v>1</v>
@@ -9376,23 +9455,23 @@
         <v>Frações</v>
       </c>
       <c r="W63" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X63" s="65" t="str">
-        <f t="shared" si="15"/>
-        <v>Key-BRASIL-63</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-63</v>
       </c>
       <c r="Y63" s="64" t="s">
         <v>395</v>
       </c>
-      <c r="Z63" s="68" t="s">
-        <v>570</v>
+      <c r="Z63" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA63" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB63" s="68" t="s">
-        <v>570</v>
+        <v>414</v>
+      </c>
+      <c r="AB63" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC63" s="68" t="s">
         <v>1</v>
@@ -9403,13 +9482,13 @@
         <v>64</v>
       </c>
       <c r="B64" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E64" s="29" t="s">
         <v>269</v>
@@ -9455,7 +9534,7 @@
         <v>124</v>
       </c>
       <c r="R64" s="64" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="S64" s="64" t="s">
         <v>1</v>
@@ -9473,23 +9552,23 @@
         <v>Frações</v>
       </c>
       <c r="W64" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X64" s="65" t="str">
-        <f t="shared" si="15"/>
-        <v>Key-BRASIL-64</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-64</v>
       </c>
       <c r="Y64" s="64" t="s">
         <v>395</v>
       </c>
-      <c r="Z64" s="68" t="s">
-        <v>570</v>
+      <c r="Z64" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA64" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB64" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB64" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC64" s="68" t="s">
         <v>1</v>
@@ -9500,13 +9579,13 @@
         <v>65</v>
       </c>
       <c r="B65" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C65" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E65" s="29" t="s">
         <v>269</v>
@@ -9552,7 +9631,7 @@
         <v>126</v>
       </c>
       <c r="R65" s="64" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="S65" s="64" t="s">
         <v>1</v>
@@ -9570,23 +9649,23 @@
         <v>Frações</v>
       </c>
       <c r="W65" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X65" s="65" t="str">
-        <f t="shared" si="15"/>
-        <v>Key-BRASIL-65</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-65</v>
       </c>
       <c r="Y65" s="64" t="s">
         <v>396</v>
       </c>
-      <c r="Z65" s="68" t="s">
-        <v>570</v>
+      <c r="Z65" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA65" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB65" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB65" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC65" s="68" t="s">
         <v>1</v>
@@ -9597,13 +9676,13 @@
         <v>66</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E66" s="29" t="s">
         <v>269</v>
@@ -9649,7 +9728,7 @@
         <v>128</v>
       </c>
       <c r="R66" s="64" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="S66" s="64" t="s">
         <v>1</v>
@@ -9667,23 +9746,23 @@
         <v>Frações</v>
       </c>
       <c r="W66" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X66" s="65" t="str">
-        <f t="shared" si="15"/>
-        <v>Key-BRASIL-66</v>
+        <f t="shared" si="3"/>
+        <v>Key-BRASIL_MG-66</v>
       </c>
       <c r="Y66" s="64" t="s">
         <v>396</v>
       </c>
-      <c r="Z66" s="68" t="s">
-        <v>570</v>
+      <c r="Z66" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA66" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB66" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB66" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC66" s="68" t="s">
         <v>1</v>
@@ -9694,13 +9773,13 @@
         <v>67</v>
       </c>
       <c r="B67" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C67" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E67" s="29" t="s">
         <v>269</v>
@@ -9746,7 +9825,7 @@
         <v>130</v>
       </c>
       <c r="R67" s="64" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="S67" s="64" t="s">
         <v>1</v>
@@ -9764,23 +9843,23 @@
         <v>Frações</v>
       </c>
       <c r="W67" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X67" s="65" t="str">
-        <f t="shared" si="15"/>
-        <v>Key-BRASIL-67</v>
+        <f t="shared" ref="X67:X101" si="15">CONCATENATE("Key-BRASIL_MG-",A67)</f>
+        <v>Key-BRASIL_MG-67</v>
       </c>
       <c r="Y67" s="64" t="s">
         <v>396</v>
       </c>
-      <c r="Z67" s="68" t="s">
-        <v>570</v>
+      <c r="Z67" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA67" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB67" s="68" t="s">
-        <v>570</v>
+      <c r="AB67" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC67" s="68" t="s">
         <v>1</v>
@@ -9791,10 +9870,10 @@
         <v>68</v>
       </c>
       <c r="B68" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C68" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C68" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D68" s="29" t="s">
         <v>264</v>
@@ -9844,7 +9923,7 @@
         <v>364</v>
       </c>
       <c r="R68" s="64" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="S68" s="64" t="s">
         <v>1</v>
@@ -9862,23 +9941,23 @@
         <v>Construídas</v>
       </c>
       <c r="W68" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X68" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-68</v>
+        <v>Key-BRASIL_MG-68</v>
       </c>
       <c r="Y68" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z68" s="68" t="s">
-        <v>570</v>
+      <c r="Z68" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA68" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB68" s="68" t="s">
-        <v>570</v>
+      <c r="AB68" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC68" s="68" t="s">
         <v>1</v>
@@ -9889,10 +9968,10 @@
         <v>69</v>
       </c>
       <c r="B69" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C69" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C69" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D69" s="29" t="s">
         <v>264</v>
@@ -9942,7 +10021,7 @@
         <v>132</v>
       </c>
       <c r="R69" s="64" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="S69" s="64" t="s">
         <v>1</v>
@@ -9960,23 +10039,23 @@
         <v>Construídas</v>
       </c>
       <c r="W69" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X69" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-69</v>
+        <v>Key-BRASIL_MG-69</v>
       </c>
       <c r="Y69" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z69" s="68" t="s">
-        <v>570</v>
+      <c r="Z69" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA69" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB69" s="68" t="s">
-        <v>570</v>
+      <c r="AB69" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC69" s="68" t="s">
         <v>1</v>
@@ -9987,10 +10066,10 @@
         <v>70</v>
       </c>
       <c r="B70" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C70" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C70" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D70" s="29" t="s">
         <v>264</v>
@@ -10040,7 +10119,7 @@
         <v>134</v>
       </c>
       <c r="R70" s="64" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="S70" s="64" t="s">
         <v>1</v>
@@ -10058,23 +10137,23 @@
         <v>Construídas</v>
       </c>
       <c r="W70" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X70" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-70</v>
+        <v>Key-BRASIL_MG-70</v>
       </c>
       <c r="Y70" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z70" s="68" t="s">
-        <v>570</v>
+      <c r="Z70" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA70" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB70" s="68" t="s">
-        <v>570</v>
+      <c r="AB70" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC70" s="68" t="s">
         <v>1</v>
@@ -10085,10 +10164,10 @@
         <v>71</v>
       </c>
       <c r="B71" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C71" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C71" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D71" s="29" t="s">
         <v>264</v>
@@ -10138,7 +10217,7 @@
         <v>135</v>
       </c>
       <c r="R71" s="64" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="S71" s="64" t="s">
         <v>1</v>
@@ -10156,23 +10235,23 @@
         <v>Construídas</v>
       </c>
       <c r="W71" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X71" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-71</v>
+        <v>Key-BRASIL_MG-71</v>
       </c>
       <c r="Y71" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z71" s="68" t="s">
-        <v>570</v>
+      <c r="Z71" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA71" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB71" s="68" t="s">
-        <v>570</v>
+      <c r="AB71" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC71" s="68" t="s">
         <v>1</v>
@@ -10183,10 +10262,10 @@
         <v>72</v>
       </c>
       <c r="B72" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C72" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C72" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D72" s="29" t="s">
         <v>264</v>
@@ -10236,7 +10315,7 @@
         <v>137</v>
       </c>
       <c r="R72" s="64" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="S72" s="64" t="s">
         <v>1</v>
@@ -10254,23 +10333,23 @@
         <v>Construídas</v>
       </c>
       <c r="W72" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X72" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-72</v>
+        <v>Key-BRASIL_MG-72</v>
       </c>
       <c r="Y72" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z72" s="68" t="s">
-        <v>570</v>
+      <c r="Z72" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA72" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB72" s="68" t="s">
-        <v>570</v>
+      <c r="AB72" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC72" s="68" t="s">
         <v>1</v>
@@ -10281,10 +10360,10 @@
         <v>73</v>
       </c>
       <c r="B73" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C73" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C73" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D73" s="29" t="s">
         <v>264</v>
@@ -10333,7 +10412,7 @@
         <v>140</v>
       </c>
       <c r="R73" s="64" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="S73" s="64" t="s">
         <v>1</v>
@@ -10351,23 +10430,23 @@
         <v>Construídas</v>
       </c>
       <c r="W73" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X73" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-73</v>
+        <v>Key-BRASIL_MG-73</v>
       </c>
       <c r="Y73" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z73" s="68" t="s">
-        <v>570</v>
+      <c r="Z73" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA73" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB73" s="68" t="s">
-        <v>570</v>
+      <c r="AB73" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC73" s="68" t="s">
         <v>1</v>
@@ -10378,10 +10457,10 @@
         <v>74</v>
       </c>
       <c r="B74" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C74" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C74" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D74" s="29" t="s">
         <v>264</v>
@@ -10430,7 +10509,7 @@
         <v>141</v>
       </c>
       <c r="R74" s="64" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="S74" s="64" t="s">
         <v>1</v>
@@ -10448,23 +10527,23 @@
         <v>Construídas</v>
       </c>
       <c r="W74" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X74" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-74</v>
+        <v>Key-BRASIL_MG-74</v>
       </c>
       <c r="Y74" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z74" s="68" t="s">
-        <v>570</v>
+      <c r="Z74" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA74" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB74" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB74" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC74" s="68" t="s">
         <v>1</v>
@@ -10475,10 +10554,10 @@
         <v>75</v>
       </c>
       <c r="B75" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C75" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C75" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D75" s="29" t="s">
         <v>265</v>
@@ -10528,7 +10607,7 @@
         <v>144</v>
       </c>
       <c r="R75" s="64" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="S75" s="64" t="s">
         <v>1</v>
@@ -10546,23 +10625,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W75" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X75" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-75</v>
+        <v>Key-BRASIL_MG-75</v>
       </c>
       <c r="Y75" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z75" s="68" t="s">
-        <v>570</v>
+      <c r="Z75" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA75" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB75" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB75" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC75" s="68" t="s">
         <v>1</v>
@@ -10573,10 +10652,10 @@
         <v>76</v>
       </c>
       <c r="B76" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C76" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C76" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D76" s="29" t="s">
         <v>265</v>
@@ -10625,7 +10704,7 @@
         <v>145</v>
       </c>
       <c r="R76" s="64" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="S76" s="64" t="s">
         <v>1</v>
@@ -10643,23 +10722,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W76" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X76" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-76</v>
+        <v>Key-BRASIL_MG-76</v>
       </c>
       <c r="Y76" s="64" t="s">
         <v>397</v>
       </c>
-      <c r="Z76" s="68" t="s">
-        <v>570</v>
+      <c r="Z76" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA76" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB76" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB76" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC76" s="68" t="s">
         <v>1</v>
@@ -10670,10 +10749,10 @@
         <v>77</v>
       </c>
       <c r="B77" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C77" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C77" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D77" s="29" t="s">
         <v>265</v>
@@ -10722,7 +10801,7 @@
         <v>147</v>
       </c>
       <c r="R77" s="64" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="S77" s="64" t="s">
         <v>1</v>
@@ -10740,23 +10819,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W77" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X77" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-77</v>
+        <v>Key-BRASIL_MG-77</v>
       </c>
       <c r="Y77" s="64" t="s">
         <v>397</v>
       </c>
-      <c r="Z77" s="68" t="s">
-        <v>570</v>
+      <c r="Z77" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA77" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB77" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB77" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC77" s="68" t="s">
         <v>1</v>
@@ -10767,10 +10846,10 @@
         <v>78</v>
       </c>
       <c r="B78" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C78" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C78" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D78" s="29" t="s">
         <v>265</v>
@@ -10819,7 +10898,7 @@
         <v>148</v>
       </c>
       <c r="R78" s="64" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="S78" s="64" t="s">
         <v>1</v>
@@ -10837,23 +10916,23 @@
         <v>Organizativas</v>
       </c>
       <c r="W78" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X78" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-78</v>
+        <v>Key-BRASIL_MG-78</v>
       </c>
       <c r="Y78" s="64" t="s">
         <v>397</v>
       </c>
-      <c r="Z78" s="68" t="s">
-        <v>570</v>
+      <c r="Z78" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA78" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB78" s="68" t="s">
-        <v>570</v>
+        <v>416</v>
+      </c>
+      <c r="AB78" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC78" s="68" t="s">
         <v>1</v>
@@ -10864,10 +10943,10 @@
         <v>79</v>
       </c>
       <c r="B79" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C79" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C79" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D79" s="29" t="s">
         <v>265</v>
@@ -10916,7 +10995,7 @@
         <v>149</v>
       </c>
       <c r="R79" s="64" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="S79" s="64" t="s">
         <v>1</v>
@@ -10934,23 +11013,23 @@
         <v>Distribuição</v>
       </c>
       <c r="W79" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X79" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-79</v>
+        <v>Key-BRASIL_MG-79</v>
       </c>
       <c r="Y79" s="64" t="s">
         <v>398</v>
       </c>
-      <c r="Z79" s="68" t="s">
-        <v>570</v>
+      <c r="Z79" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA79" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB79" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB79" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC79" s="68" t="s">
         <v>1</v>
@@ -10961,10 +11040,10 @@
         <v>80</v>
       </c>
       <c r="B80" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C80" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C80" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D80" s="29" t="s">
         <v>265</v>
@@ -11013,7 +11092,7 @@
         <v>150</v>
       </c>
       <c r="R80" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="S80" s="64" t="s">
         <v>1</v>
@@ -11031,23 +11110,23 @@
         <v>Distribuição</v>
       </c>
       <c r="W80" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X80" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-80</v>
+        <v>Key-BRASIL_MG-80</v>
       </c>
       <c r="Y80" s="64" t="s">
         <v>397</v>
       </c>
-      <c r="Z80" s="68" t="s">
-        <v>570</v>
+      <c r="Z80" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA80" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB80" s="68" t="s">
-        <v>570</v>
+        <v>415</v>
+      </c>
+      <c r="AB80" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC80" s="68" t="s">
         <v>1</v>
@@ -11058,10 +11137,10 @@
         <v>81</v>
       </c>
       <c r="B81" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C81" s="29" t="s">
         <v>438</v>
-      </c>
-      <c r="C81" s="29" t="s">
-        <v>440</v>
       </c>
       <c r="D81" s="29" t="s">
         <v>265</v>
@@ -11110,7 +11189,7 @@
         <v>152</v>
       </c>
       <c r="R81" s="64" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="S81" s="64" t="s">
         <v>1</v>
@@ -11128,23 +11207,23 @@
         <v>Distribuição</v>
       </c>
       <c r="W81" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X81" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-81</v>
+        <v>Key-BRASIL_MG-81</v>
       </c>
       <c r="Y81" s="64" t="s">
         <v>397</v>
       </c>
-      <c r="Z81" s="68" t="s">
-        <v>570</v>
+      <c r="Z81" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA81" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB81" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB81" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC81" s="68" t="s">
         <v>1</v>
@@ -11155,13 +11234,13 @@
         <v>82</v>
       </c>
       <c r="B82" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C82" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E82" s="29" t="s">
         <v>153</v>
@@ -11207,7 +11286,7 @@
         <v>155</v>
       </c>
       <c r="R82" s="64" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="S82" s="64" t="s">
         <v>1</v>
@@ -11225,23 +11304,23 @@
         <v>Saúde</v>
       </c>
       <c r="W82" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X82" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-82</v>
+        <v>Key-BRASIL_MG-82</v>
       </c>
       <c r="Y82" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z82" s="68" t="s">
-        <v>570</v>
+      <c r="Z82" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA82" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB82" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB82" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC82" s="68" t="s">
         <v>1</v>
@@ -11252,13 +11331,13 @@
         <v>83</v>
       </c>
       <c r="B83" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C83" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E83" s="29" t="s">
         <v>153</v>
@@ -11304,7 +11383,7 @@
         <v>157</v>
       </c>
       <c r="R83" s="64" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="S83" s="64" t="s">
         <v>1</v>
@@ -11322,23 +11401,23 @@
         <v>Saúde</v>
       </c>
       <c r="W83" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X83" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-83</v>
+        <v>Key-BRASIL_MG-83</v>
       </c>
       <c r="Y83" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z83" s="68" t="s">
-        <v>570</v>
+      <c r="Z83" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA83" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB83" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB83" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC83" s="68" t="s">
         <v>1</v>
@@ -11349,13 +11428,13 @@
         <v>84</v>
       </c>
       <c r="B84" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C84" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E84" s="29" t="s">
         <v>153</v>
@@ -11401,7 +11480,7 @@
         <v>159</v>
       </c>
       <c r="R84" s="64" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="S84" s="64" t="s">
         <v>1</v>
@@ -11419,23 +11498,23 @@
         <v>Saúde</v>
       </c>
       <c r="W84" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X84" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-84</v>
+        <v>Key-BRASIL_MG-84</v>
       </c>
       <c r="Y84" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z84" s="68" t="s">
-        <v>570</v>
+      <c r="Z84" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA84" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB84" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB84" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC84" s="68" t="s">
         <v>1</v>
@@ -11446,13 +11525,13 @@
         <v>85</v>
       </c>
       <c r="B85" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E85" s="29" t="s">
         <v>153</v>
@@ -11498,7 +11577,7 @@
         <v>162</v>
       </c>
       <c r="R85" s="64" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="S85" s="64" t="s">
         <v>1</v>
@@ -11516,23 +11595,23 @@
         <v>Saúde</v>
       </c>
       <c r="W85" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X85" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-85</v>
+        <v>Key-BRASIL_MG-85</v>
       </c>
       <c r="Y85" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z85" s="68" t="s">
-        <v>570</v>
+      <c r="Z85" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA85" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB85" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB85" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC85" s="68" t="s">
         <v>1</v>
@@ -11543,13 +11622,13 @@
         <v>86</v>
       </c>
       <c r="B86" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E86" s="29" t="s">
         <v>153</v>
@@ -11595,7 +11674,7 @@
         <v>165</v>
       </c>
       <c r="R86" s="64" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="S86" s="64" t="s">
         <v>1</v>
@@ -11613,23 +11692,23 @@
         <v>Saúde</v>
       </c>
       <c r="W86" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X86" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-86</v>
+        <v>Key-BRASIL_MG-86</v>
       </c>
       <c r="Y86" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z86" s="68" t="s">
-        <v>570</v>
+      <c r="Z86" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA86" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB86" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB86" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC86" s="68" t="s">
         <v>1</v>
@@ -11640,13 +11719,13 @@
         <v>87</v>
       </c>
       <c r="B87" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C87" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E87" s="29" t="s">
         <v>268</v>
@@ -11692,7 +11771,7 @@
         <v>167</v>
       </c>
       <c r="R87" s="64" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="S87" s="64" t="s">
         <v>1</v>
@@ -11710,23 +11789,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W87" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X87" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-87</v>
+        <v>Key-BRASIL_MG-87</v>
       </c>
       <c r="Y87" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z87" s="68" t="s">
-        <v>570</v>
+      <c r="Z87" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA87" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB87" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB87" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC87" s="68" t="s">
         <v>1</v>
@@ -11737,13 +11816,13 @@
         <v>88</v>
       </c>
       <c r="B88" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E88" s="29" t="s">
         <v>268</v>
@@ -11789,7 +11868,7 @@
         <v>169</v>
       </c>
       <c r="R88" s="64" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="S88" s="64" t="s">
         <v>1</v>
@@ -11807,23 +11886,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W88" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X88" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-88</v>
+        <v>Key-BRASIL_MG-88</v>
       </c>
       <c r="Y88" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z88" s="68" t="s">
-        <v>570</v>
+      <c r="Z88" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA88" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB88" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB88" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC88" s="68" t="s">
         <v>1</v>
@@ -11834,13 +11913,13 @@
         <v>89</v>
       </c>
       <c r="B89" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E89" s="29" t="s">
         <v>268</v>
@@ -11886,7 +11965,7 @@
         <v>171</v>
       </c>
       <c r="R89" s="64" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="S89" s="64" t="s">
         <v>1</v>
@@ -11904,23 +11983,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W89" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X89" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-89</v>
+        <v>Key-BRASIL_MG-89</v>
       </c>
       <c r="Y89" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z89" s="68" t="s">
-        <v>570</v>
+      <c r="Z89" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA89" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB89" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB89" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC89" s="68" t="s">
         <v>1</v>
@@ -11931,13 +12010,13 @@
         <v>90</v>
       </c>
       <c r="B90" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C90" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E90" s="29" t="s">
         <v>268</v>
@@ -11983,7 +12062,7 @@
         <v>173</v>
       </c>
       <c r="R90" s="64" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="S90" s="64" t="s">
         <v>1</v>
@@ -12001,23 +12080,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W90" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X90" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-90</v>
+        <v>Key-BRASIL_MG-90</v>
       </c>
       <c r="Y90" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z90" s="68" t="s">
-        <v>570</v>
+      <c r="Z90" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA90" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB90" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB90" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC90" s="68" t="s">
         <v>1</v>
@@ -12028,13 +12107,13 @@
         <v>91</v>
       </c>
       <c r="B91" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C91" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E91" s="29" t="s">
         <v>268</v>
@@ -12080,7 +12159,7 @@
         <v>367</v>
       </c>
       <c r="R91" s="64" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="S91" s="64" t="s">
         <v>1</v>
@@ -12098,23 +12177,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W91" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X91" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-91</v>
+        <v>Key-BRASIL_MG-91</v>
       </c>
       <c r="Y91" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z91" s="68" t="s">
-        <v>570</v>
+      <c r="Z91" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA91" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB91" s="68" t="s">
-        <v>570</v>
+        <v>417</v>
+      </c>
+      <c r="AB91" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC91" s="68" t="s">
         <v>1</v>
@@ -12125,13 +12204,13 @@
         <v>92</v>
       </c>
       <c r="B92" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C92" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E92" s="29" t="s">
         <v>268</v>
@@ -12177,7 +12256,7 @@
         <v>370</v>
       </c>
       <c r="R92" s="64" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="S92" s="64" t="s">
         <v>1</v>
@@ -12195,23 +12274,23 @@
         <v>Educacionais</v>
       </c>
       <c r="W92" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X92" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-92</v>
+        <v>Key-BRASIL_MG-92</v>
       </c>
       <c r="Y92" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="Z92" s="68" t="s">
-        <v>570</v>
+      <c r="Z92" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA92" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB92" s="68" t="s">
-        <v>570</v>
+        <v>411</v>
+      </c>
+      <c r="AB92" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC92" s="68" t="s">
         <v>1</v>
@@ -12222,13 +12301,13 @@
         <v>93</v>
       </c>
       <c r="B93" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C93" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E93" s="29" t="s">
         <v>174</v>
@@ -12274,7 +12353,7 @@
         <v>177</v>
       </c>
       <c r="R93" s="64" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="S93" s="64" t="s">
         <v>1</v>
@@ -12292,23 +12371,23 @@
         <v>INMET</v>
       </c>
       <c r="W93" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X93" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-93</v>
+        <v>Key-BRASIL_MG-93</v>
       </c>
       <c r="Y93" s="64" t="s">
         <v>400</v>
       </c>
-      <c r="Z93" s="68" t="s">
-        <v>570</v>
+      <c r="Z93" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA93" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB93" s="68" t="s">
-        <v>570</v>
+        <v>411</v>
+      </c>
+      <c r="AB93" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC93" s="68" t="s">
         <v>1</v>
@@ -12319,19 +12398,19 @@
         <v>94</v>
       </c>
       <c r="B94" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C94" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E94" s="29" t="s">
         <v>174</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G94" s="66" t="s">
         <v>1</v>
@@ -12365,13 +12444,13 @@
         <v>Estação Meteorológica Automática</v>
       </c>
       <c r="P94" s="67" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="Q94" s="67" t="s">
         <v>177</v>
       </c>
       <c r="R94" s="64" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="S94" s="64" t="s">
         <v>1</v>
@@ -12389,23 +12468,23 @@
         <v>INMET</v>
       </c>
       <c r="W94" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X94" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-94</v>
+        <v>Key-BRASIL_MG-94</v>
       </c>
       <c r="Y94" s="64" t="s">
         <v>400</v>
       </c>
-      <c r="Z94" s="68" t="s">
-        <v>570</v>
+      <c r="Z94" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA94" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB94" s="68" t="s">
-        <v>570</v>
+        <v>411</v>
+      </c>
+      <c r="AB94" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC94" s="68" t="s">
         <v>1</v>
@@ -12416,19 +12495,19 @@
         <v>95</v>
       </c>
       <c r="B95" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C95" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E95" s="29" t="s">
         <v>174</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G95" s="66" t="s">
         <v>1</v>
@@ -12462,13 +12541,13 @@
         <v>Estação Meteorológica Convencional</v>
       </c>
       <c r="P95" s="67" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q95" s="67" t="s">
         <v>177</v>
       </c>
       <c r="R95" s="64" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="S95" s="64" t="s">
         <v>1</v>
@@ -12486,23 +12565,23 @@
         <v>INMET</v>
       </c>
       <c r="W95" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X95" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-95</v>
+        <v>Key-BRASIL_MG-95</v>
       </c>
       <c r="Y95" s="64" t="s">
         <v>400</v>
       </c>
-      <c r="Z95" s="68" t="s">
-        <v>570</v>
+      <c r="Z95" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AA95" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB95" s="68" t="s">
-        <v>570</v>
+        <v>411</v>
+      </c>
+      <c r="AB95" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC95" s="68" t="s">
         <v>1</v>
@@ -12513,13 +12592,13 @@
         <v>96</v>
       </c>
       <c r="B96" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E96" s="29" t="s">
         <v>178</v>
@@ -12565,7 +12644,7 @@
         <v>181</v>
       </c>
       <c r="R96" s="64" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="S96" s="64" t="s">
         <v>1</v>
@@ -12583,23 +12662,23 @@
         <v>IBGE</v>
       </c>
       <c r="W96" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X96" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-96</v>
-      </c>
-      <c r="Y96" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z96" s="68" t="s">
-        <v>570</v>
-      </c>
-      <c r="AA96" s="64" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB96" s="68" t="s">
-        <v>570</v>
+        <v>Key-BRASIL_MG-96</v>
+      </c>
+      <c r="Y96" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC96" s="68" t="s">
         <v>1</v>
@@ -12610,13 +12689,13 @@
         <v>97</v>
       </c>
       <c r="B97" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E97" s="29" t="s">
         <v>178</v>
@@ -12662,7 +12741,7 @@
         <v>181</v>
       </c>
       <c r="R97" s="64" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="S97" s="64" t="s">
         <v>1</v>
@@ -12680,23 +12759,23 @@
         <v>IBGE</v>
       </c>
       <c r="W97" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X97" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-97</v>
-      </c>
-      <c r="Y97" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z97" s="68" t="s">
-        <v>570</v>
-      </c>
-      <c r="AA97" s="64" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB97" s="68" t="s">
-        <v>570</v>
+        <v>Key-BRASIL_MG-97</v>
+      </c>
+      <c r="Y97" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA97" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB97" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC97" s="68" t="s">
         <v>1</v>
@@ -12707,13 +12786,13 @@
         <v>98</v>
       </c>
       <c r="B98" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C98" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E98" s="29" t="s">
         <v>178</v>
@@ -12759,7 +12838,7 @@
         <v>185</v>
       </c>
       <c r="R98" s="64" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="S98" s="64" t="s">
         <v>1</v>
@@ -12777,23 +12856,23 @@
         <v>IBGE</v>
       </c>
       <c r="W98" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X98" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-98</v>
-      </c>
-      <c r="Y98" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z98" s="68" t="s">
-        <v>570</v>
-      </c>
-      <c r="AA98" s="64" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB98" s="68" t="s">
-        <v>570</v>
+        <v>Key-BRASIL_MG-98</v>
+      </c>
+      <c r="Y98" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z98" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB98" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC98" s="68" t="s">
         <v>1</v>
@@ -12804,13 +12883,13 @@
         <v>99</v>
       </c>
       <c r="B99" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C99" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E99" s="29" t="s">
         <v>178</v>
@@ -12856,7 +12935,7 @@
         <v>188</v>
       </c>
       <c r="R99" s="64" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="S99" s="64" t="s">
         <v>1</v>
@@ -12874,23 +12953,23 @@
         <v>IBGE</v>
       </c>
       <c r="W99" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X99" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-99</v>
-      </c>
-      <c r="Y99" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z99" s="68" t="s">
-        <v>570</v>
-      </c>
-      <c r="AA99" s="64" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB99" s="68" t="s">
-        <v>570</v>
+        <v>Key-BRASIL_MG-99</v>
+      </c>
+      <c r="Y99" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="74" t="s">
+        <v>1</v>
       </c>
       <c r="AC99" s="68" t="s">
         <v>1</v>
@@ -12901,13 +12980,13 @@
         <v>100</v>
       </c>
       <c r="B100" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C100" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E100" s="29" t="s">
         <v>178</v>
@@ -12953,7 +13032,7 @@
         <v>191</v>
       </c>
       <c r="R100" s="64" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="S100" s="64" t="s">
         <v>1</v>
@@ -12971,97 +13050,207 @@
         <v>IBGE</v>
       </c>
       <c r="W100" s="64" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X100" s="65" t="str">
         <f t="shared" si="15"/>
-        <v>Key-BRASIL-100</v>
-      </c>
-      <c r="Y100" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="Z100" s="68" t="s">
+        <v>Key-BRASIL_MG-100</v>
+      </c>
+      <c r="Y100" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA100" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB100" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC100" s="68" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="60">
+        <v>101</v>
+      </c>
+      <c r="B101" s="70" t="s">
+        <v>569</v>
+      </c>
+      <c r="C101" s="71" t="s">
         <v>570</v>
       </c>
-      <c r="AA100" s="64" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB100" s="68" t="s">
-        <v>570</v>
-      </c>
-      <c r="AC100" s="68" t="s">
+      <c r="D101" s="71" t="s">
+        <v>571</v>
+      </c>
+      <c r="E101" s="71" t="s">
+        <v>572</v>
+      </c>
+      <c r="F101" s="71" t="s">
+        <v>573</v>
+      </c>
+      <c r="G101" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" s="72" t="str">
+        <f t="shared" ref="L101:O101" si="18">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M101" s="72" t="str">
+        <f t="shared" si="18"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N101" s="72" t="str">
+        <f t="shared" si="18"/>
+        <v>Macros</v>
+      </c>
+      <c r="O101" s="72" t="str">
+        <f t="shared" si="18"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P101" s="73" t="s">
+        <v>574</v>
+      </c>
+      <c r="Q101" s="73" t="s">
+        <v>575</v>
+      </c>
+      <c r="R101" s="73" t="s">
+        <v>576</v>
+      </c>
+      <c r="S101" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="T101" s="73" t="str">
+        <f t="shared" ref="T101:V101" si="19">SUBSTITUTE(C101, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U101" s="73" t="str">
+        <f t="shared" si="19"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V101" s="64" t="str">
+        <f t="shared" si="19"/>
+        <v>Macros</v>
+      </c>
+      <c r="W101" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="X101" s="65" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-BRASIL_MG-101</v>
+      </c>
+      <c r="Y101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC101" s="74" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:D100 T41:V100 L41:Q1048576 AD41:XFD1048576">
-    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B100 A101 W2:W101">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F101:F1048576 A1:D1 T1:X1 A101:D1048576 T101:X1048576">
-    <cfRule type="cellIs" dxfId="32" priority="446" operator="equal">
+  <conditionalFormatting sqref="C2:D100 T41:V100 L41:Q100 AD41:XFD100 AD102:XFD1048576 L102:Q1048576">
+    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F102:F1048576 A1:D1 T1:X1 A102:D1048576 T102:X1048576">
+    <cfRule type="cellIs" dxfId="36" priority="450" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="31" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AD1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="30" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="24" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F101:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="16" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="966"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="978"/>
+  <conditionalFormatting sqref="F102:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="20" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="982"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F101:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="963"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="970"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="982"/>
+  <conditionalFormatting sqref="F102:F1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="986"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B100 W2:W100">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+  <conditionalFormatting sqref="R1:R100">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R101:R1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+  <conditionalFormatting sqref="R102:R1048576">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R100">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+  <conditionalFormatting sqref="B101">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F101">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R101">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13278,7 +13467,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13383,7 +13572,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A6">
-    <cfRule type="cellIs" dxfId="4" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13463,7 +13652,7 @@
         <v>34</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D1" s="19" t="s">
         <v>33</v>
@@ -13776,22 +13965,22 @@
         <v>379</v>
       </c>
       <c r="AY2" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ2" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA2" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB2" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC2" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD2" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE2" s="38" t="str">
         <f t="shared" ref="BE2" si="0">_xlfn.CONCAT("""",C2,"""")</f>
@@ -13950,22 +14139,22 @@
         <v>379</v>
       </c>
       <c r="AY3" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ3" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA3" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC3" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD3" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE3" s="38" t="str">
         <f t="shared" ref="BE3:BE10" si="1">_xlfn.CONCAT("""",C3,"""")</f>
@@ -14124,22 +14313,22 @@
         <v>379</v>
       </c>
       <c r="AY4" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ4" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA4" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB4" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC4" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD4" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE4" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14298,22 +14487,22 @@
         <v>379</v>
       </c>
       <c r="AY5" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ5" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA5" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB5" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC5" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD5" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE5" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14472,22 +14661,22 @@
         <v>379</v>
       </c>
       <c r="AY6" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ6" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA6" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB6" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC6" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD6" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE6" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14538,7 +14727,7 @@
         <v>78</v>
       </c>
       <c r="O7" s="28" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P7" s="37" t="s">
         <v>1</v>
@@ -14646,22 +14835,22 @@
         <v>379</v>
       </c>
       <c r="AY7" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ7" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA7" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB7" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC7" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD7" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE7" s="38" t="str">
         <f t="shared" si="1"/>
@@ -14812,31 +15001,31 @@
         <v>1</v>
       </c>
       <c r="AV8" s="30" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AW8" s="38" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AX8" s="30" t="s">
         <v>379</v>
       </c>
       <c r="AY8" s="38" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AZ8" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA8" s="38" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="BB8" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC8" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD8" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE8" s="38" t="str">
         <f t="shared" ref="BE8" si="2">_xlfn.CONCAT("""",C8,"""")</f>
@@ -14887,7 +15076,7 @@
         <v>78</v>
       </c>
       <c r="O9" s="28" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P9" s="37" t="s">
         <v>1</v>
@@ -14995,22 +15184,22 @@
         <v>379</v>
       </c>
       <c r="AY9" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ9" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA9" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB9" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC9" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD9" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE9" s="38" t="str">
         <f t="shared" si="1"/>
@@ -15061,7 +15250,7 @@
         <v>78</v>
       </c>
       <c r="O10" s="28" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P10" s="37" t="s">
         <v>1</v>
@@ -15169,22 +15358,22 @@
         <v>379</v>
       </c>
       <c r="AY10" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AZ10" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA10" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BB10" s="30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BC10" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD10" s="30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BE10" s="38" t="str">
         <f t="shared" si="1"/>
@@ -15195,20 +15384,20 @@
   <autoFilter ref="F1:F6" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576 G2 G4:G5 H10:BB10 D10:F1048576 H11:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:BB9">
-    <cfRule type="cellIs" dxfId="1" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:XFD3 D1:F8 H4:BB8 BC4:XFD10">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F24CEC-543B-459B-82AC-1E1EA0AC0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4C8B2F-62CC-440E-913A-E9FD69FED075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -2330,49 +2330,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="36">
     <dxf>
       <font>
         <b val="0"/>
@@ -2424,6 +2382,7 @@
       <font>
         <b val="0"/>
         <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -2434,6 +2393,23 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2673,6 +2649,14 @@
       <font>
         <b val="0"/>
         <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -2993,15 +2977,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="51" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="1" max="1" width="9.69140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="51" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -3012,7 +2996,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -3023,7 +3007,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
@@ -3034,7 +3018,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -3045,7 +3029,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -3057,7 +3041,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -3069,7 +3053,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3080,7 +3064,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -3091,7 +3075,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
@@ -3102,7 +3086,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
@@ -3113,7 +3097,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
@@ -3124,7 +3108,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -3135,7 +3119,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>52</v>
       </c>
@@ -3146,7 +3130,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -3157,7 +3141,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
@@ -3168,7 +3152,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>55</v>
       </c>
@@ -3179,7 +3163,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -3190,19 +3174,19 @@
         <v>376</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46258.60356909722</v>
+        <v>46264.565892245373</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>380</v>
       </c>
@@ -3213,7 +3197,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>382</v>
       </c>
@@ -3225,7 +3209,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
         <v>383</v>
       </c>
@@ -3237,7 +3221,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
@@ -3248,7 +3232,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -3259,7 +3243,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
@@ -3270,7 +3254,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
@@ -3281,7 +3265,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>374</v>
       </c>
@@ -3301,39 +3285,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AC101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.3046875" style="31" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="23.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="232.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="230.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="51.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.5703125" style="31" customWidth="1"/>
+    <col min="10" max="11" width="23.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="232.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="230.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="51.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.53515625" style="31" customWidth="1"/>
     <col min="28" max="28" width="6" style="31" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="31"/>
+    <col min="29" max="29" width="4.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3422,7 +3406,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -3521,7 +3505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -3618,7 +3602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -3715,7 +3699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -3813,7 +3797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -3910,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -4008,7 +3992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -4106,7 +4090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -4204,7 +4188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -4302,7 +4286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -4399,7 +4383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -4497,7 +4481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -4595,7 +4579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -4694,7 +4678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -4793,7 +4777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -4892,7 +4876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -4991,7 +4975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -5090,7 +5074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -5189,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -5288,7 +5272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -5387,7 +5371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
@@ -5486,7 +5470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
@@ -5585,7 +5569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
@@ -5684,7 +5668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
@@ -5782,7 +5766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
@@ -5880,7 +5864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
@@ -5978,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
@@ -6076,7 +6060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
@@ -6174,7 +6158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
@@ -6271,7 +6255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
@@ -6368,7 +6352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
@@ -6465,7 +6449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
@@ -6562,7 +6546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
@@ -6659,7 +6643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
@@ -6756,7 +6740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="60">
         <v>36</v>
       </c>
@@ -6853,7 +6837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="60">
         <v>37</v>
       </c>
@@ -6950,7 +6934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="60">
         <v>38</v>
       </c>
@@ -7047,7 +7031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="60">
         <v>39</v>
       </c>
@@ -7144,7 +7128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="60">
         <v>40</v>
       </c>
@@ -7241,7 +7225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="60">
         <v>41</v>
       </c>
@@ -7338,7 +7322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="60">
         <v>42</v>
       </c>
@@ -7435,7 +7419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="60">
         <v>43</v>
       </c>
@@ -7532,7 +7516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="60">
         <v>44</v>
       </c>
@@ -7629,7 +7613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="60">
         <v>45</v>
       </c>
@@ -7726,7 +7710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="60">
         <v>46</v>
       </c>
@@ -7823,7 +7807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="60">
         <v>47</v>
       </c>
@@ -7920,7 +7904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="60">
         <v>48</v>
       </c>
@@ -8017,7 +8001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="60">
         <v>49</v>
       </c>
@@ -8114,7 +8098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="60">
         <v>50</v>
       </c>
@@ -8211,7 +8195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="60">
         <v>51</v>
       </c>
@@ -8308,7 +8292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="60">
         <v>52</v>
       </c>
@@ -8405,7 +8389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="60">
         <v>53</v>
       </c>
@@ -8502,7 +8486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="60">
         <v>54</v>
       </c>
@@ -8599,7 +8583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="60">
         <v>55</v>
       </c>
@@ -8699,7 +8683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="60">
         <v>56</v>
       </c>
@@ -8798,7 +8782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="60">
         <v>57</v>
       </c>
@@ -8895,7 +8879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="60">
         <v>58</v>
       </c>
@@ -8992,7 +8976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="60">
         <v>59</v>
       </c>
@@ -9089,7 +9073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="60">
         <v>60</v>
       </c>
@@ -9186,7 +9170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="60">
         <v>61</v>
       </c>
@@ -9283,7 +9267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="60">
         <v>62</v>
       </c>
@@ -9380,7 +9364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="60">
         <v>63</v>
       </c>
@@ -9477,7 +9461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="60">
         <v>64</v>
       </c>
@@ -9574,7 +9558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="60">
         <v>65</v>
       </c>
@@ -9671,7 +9655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="60">
         <v>66</v>
       </c>
@@ -9768,7 +9752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="60">
         <v>67</v>
       </c>
@@ -9865,7 +9849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="60">
         <v>68</v>
       </c>
@@ -9963,7 +9947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="60">
         <v>69</v>
       </c>
@@ -10061,7 +10045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="60">
         <v>70</v>
       </c>
@@ -10159,7 +10143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="60">
         <v>71</v>
       </c>
@@ -10257,7 +10241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="60">
         <v>72</v>
       </c>
@@ -10355,7 +10339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="60">
         <v>73</v>
       </c>
@@ -10452,7 +10436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="60">
         <v>74</v>
       </c>
@@ -10549,7 +10533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="60">
         <v>75</v>
       </c>
@@ -10647,7 +10631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="60">
         <v>76</v>
       </c>
@@ -10744,7 +10728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="60">
         <v>77</v>
       </c>
@@ -10841,7 +10825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="60">
         <v>78</v>
       </c>
@@ -10938,7 +10922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="60">
         <v>79</v>
       </c>
@@ -11035,7 +11019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="60">
         <v>80</v>
       </c>
@@ -11132,7 +11116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="60">
         <v>81</v>
       </c>
@@ -11229,7 +11213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="60">
         <v>82</v>
       </c>
@@ -11326,7 +11310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="60">
         <v>83</v>
       </c>
@@ -11423,7 +11407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="60">
         <v>84</v>
       </c>
@@ -11520,7 +11504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="60">
         <v>85</v>
       </c>
@@ -11617,7 +11601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="60">
         <v>86</v>
       </c>
@@ -11714,7 +11698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="60">
         <v>87</v>
       </c>
@@ -11811,7 +11795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="60">
         <v>88</v>
       </c>
@@ -11908,7 +11892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="60">
         <v>89</v>
       </c>
@@ -12005,7 +11989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="60">
         <v>90</v>
       </c>
@@ -12102,7 +12086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="60">
         <v>91</v>
       </c>
@@ -12199,7 +12183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="60">
         <v>92</v>
       </c>
@@ -12296,7 +12280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="60">
         <v>93</v>
       </c>
@@ -12393,7 +12377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="60">
         <v>94</v>
       </c>
@@ -12490,7 +12474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="60">
         <v>95</v>
       </c>
@@ -12587,7 +12571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="60">
         <v>96</v>
       </c>
@@ -12684,7 +12668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="60">
         <v>97</v>
       </c>
@@ -12781,7 +12765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="60">
         <v>98</v>
       </c>
@@ -12878,7 +12862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="60">
         <v>99</v>
       </c>
@@ -12975,7 +12959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:29" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="60">
         <v>100</v>
       </c>
@@ -13072,7 +13056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:29" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="60">
         <v>101</v>
       </c>
@@ -13083,10 +13067,10 @@
         <v>570</v>
       </c>
       <c r="D101" s="71" t="s">
+        <v>572</v>
+      </c>
+      <c r="E101" s="71" t="s">
         <v>571</v>
-      </c>
-      <c r="E101" s="71" t="s">
-        <v>572</v>
       </c>
       <c r="F101" s="71" t="s">
         <v>573</v>
@@ -13112,11 +13096,11 @@
       </c>
       <c r="M101" s="72" t="str">
         <f t="shared" si="18"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N101" s="72" t="str">
         <f t="shared" si="18"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O101" s="72" t="str">
         <f t="shared" si="18"/>
@@ -13140,11 +13124,11 @@
       </c>
       <c r="U101" s="73" t="str">
         <f t="shared" si="19"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V101" s="64" t="str">
         <f t="shared" si="19"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W101" s="64" t="s">
         <v>435</v>
@@ -13171,86 +13155,81 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B100 A101 W2:W101">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B101">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D100 T41:V100 L41:Q100 AD41:XFD100 AD102:XFD1048576 L102:Q1048576">
-    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
+  <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AD41:XFD100 AD102:XFD1048576">
+    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F102:F1048576 A1:D1 T1:X1 A102:D1048576 T102:X1048576">
-    <cfRule type="cellIs" dxfId="36" priority="450" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="450" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="35" priority="1488"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AD1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="34" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="29" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F101">
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="20" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="970"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:F1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="967"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="986"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R100">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
+  <conditionalFormatting sqref="L102:R1048576">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R102:R1048576">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+  <conditionalFormatting sqref="R1:R101">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F101">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R101">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="W2:W101">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13261,15 +13240,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
@@ -13334,7 +13313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -13399,7 +13378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -13467,7 +13446,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13479,14 +13458,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21">
         <v>1</v>
       </c>
@@ -13500,7 +13479,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
         <v>2</v>
       </c>
@@ -13514,7 +13493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>3</v>
       </c>
@@ -13528,7 +13507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>4</v>
       </c>
@@ -13542,7 +13521,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -13556,7 +13535,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>6</v>
       </c>
@@ -13572,7 +13551,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A6">
-    <cfRule type="cellIs" dxfId="9" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13583,68 +13562,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.84375" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="8.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="9.7109375" style="46" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.140625" style="25"/>
+    <col min="15" max="15" width="34.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.3828125" style="25" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.69140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.69140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.15234375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="27" t="s">
         <v>74</v>
       </c>
@@ -13813,7 +13792,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="36">
         <v>2</v>
       </c>
@@ -13987,7 +13966,7 @@
         <v>"Continente"</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="36">
         <v>3</v>
       </c>
@@ -14161,7 +14140,7 @@
         <v>"SubContinente"</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="36">
         <v>4</v>
       </c>
@@ -14335,7 +14314,7 @@
         <v>"País"</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="36">
         <v>5</v>
       </c>
@@ -14509,7 +14488,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="36">
         <v>6</v>
       </c>
@@ -14683,7 +14662,7 @@
         <v>"Região"</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="36">
         <v>7</v>
       </c>
@@ -14857,7 +14836,7 @@
         <v>"Estado"</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="36">
         <v>8</v>
       </c>
@@ -15032,7 +15011,7 @@
         <v>"Capital"</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="36">
         <v>9</v>
       </c>
@@ -15206,7 +15185,7 @@
         <v>"UF"</v>
       </c>
     </row>
-    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="36">
         <v>10</v>
       </c>
@@ -15384,20 +15363,20 @@
   <autoFilter ref="F1:F6" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576 G2 G4:G5 H10:BB10 D10:F1048576 H11:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:BB9">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:XFD3 D1:F8 H4:BB8 BC4:XFD10">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4C8B2F-62CC-440E-913A-E9FD69FED075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60694CD2-78D9-4F39-A519-DC222AEFCB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2866" uniqueCount="596">
   <si>
     <t>Key</t>
   </si>
@@ -1258,18 +1258,9 @@
     <t>[ OST_ToposolidFinish1 ]</t>
   </si>
   <si>
-    <t>[ OST_TopographyContours , OST_ToposolidContours , OST_ToposolidSecondaryContours ]</t>
-  </si>
-  <si>
     <t>[ OST_Floors ]</t>
   </si>
   <si>
-    <t>[ OST_SiteProperty , OST_SitePropertyLineSegment ]</t>
-  </si>
-  <si>
-    <t>[ OST_Areas , OST_Rooms ]</t>
-  </si>
-  <si>
     <t>[ OST_Rooms ]</t>
   </si>
   <si>
@@ -1795,16 +1786,82 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Paisagística</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>[ OST_TopographyContours : OST_ToposolidContours : OST_ToposolidSecondaryContours ]</t>
+  </si>
+  <si>
+    <t>[ OST_SiteProperty : OST_SitePropertyLineSegment ]</t>
+  </si>
+  <si>
+    <t>[ OST_Areas : OST_Rooms ]</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1912,7 +1969,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2041,12 +2098,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
@@ -2103,7 +2154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2308,29 +2359,32 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="37">
     <dxf>
       <font>
         <b val="0"/>
@@ -2644,6 +2698,16 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2977,15 +3041,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.53515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="51" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="6"/>
+    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="51" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -2996,7 +3060,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -3007,18 +3071,18 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C3" s="50" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -3029,7 +3093,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -3041,7 +3105,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -3053,7 +3117,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3064,7 +3128,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -3075,7 +3139,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
@@ -3086,7 +3150,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
@@ -3097,7 +3161,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
@@ -3108,7 +3172,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -3119,7 +3183,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>52</v>
       </c>
@@ -3130,7 +3194,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -3141,7 +3205,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
@@ -3152,7 +3216,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>55</v>
       </c>
@@ -3163,30 +3227,30 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C17" s="50" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46264.565892245373</v>
+        <v>46268.69424675926</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>380</v>
       </c>
@@ -3197,7 +3261,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>382</v>
       </c>
@@ -3209,7 +3273,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>383</v>
       </c>
@@ -3221,7 +3285,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
@@ -3232,7 +3296,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -3243,29 +3307,29 @@
         <v>376</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C24" s="50" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C25" s="50" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>374</v>
       </c>
@@ -3284,40 +3348,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AC101"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD105"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.53515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.84375" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="31" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="23.3828125" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.53515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="232.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="230.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.53515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="51.84375" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.53515625" style="31" customWidth="1"/>
+    <col min="10" max="11" width="23.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="232.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="230.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="51.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" style="31" customWidth="1"/>
     <col min="28" max="28" width="6" style="31" customWidth="1"/>
-    <col min="29" max="29" width="4.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="31"/>
+    <col min="29" max="30" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3394,24 +3458,27 @@
         <v>79</v>
       </c>
       <c r="Z1" s="16" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="AA1" s="16" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AB1" s="16" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AC1" s="16" t="s">
         <v>372</v>
       </c>
+      <c r="AD1" s="16" t="s">
+        <v>595</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60">
         <v>2</v>
       </c>
       <c r="B2" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>253</v>
@@ -3465,7 +3532,7 @@
         <v>80</v>
       </c>
       <c r="R2" s="64" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="S2" s="64" t="s">
         <v>1</v>
@@ -3483,7 +3550,7 @@
         <v>Naturais</v>
       </c>
       <c r="W2" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X2" s="65" t="str">
         <f>CONCATENATE("Key-BRASIL_MG-",A2)</f>
@@ -3492,25 +3559,28 @@
       <c r="Y2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z2" s="74" t="s">
+      <c r="Z2" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="74" t="s">
+      <c r="AB2" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC2" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD2" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="60">
         <v>3</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C3" s="29" t="s">
         <v>253</v>
@@ -3562,7 +3632,7 @@
         <v>81</v>
       </c>
       <c r="R3" s="64" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="S3" s="64" t="s">
         <v>1</v>
@@ -3580,7 +3650,7 @@
         <v>Naturais</v>
       </c>
       <c r="W3" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X3" s="65" t="str">
         <f t="shared" ref="X3:X66" si="3">CONCATENATE("Key-BRASIL_MG-",A3)</f>
@@ -3589,25 +3659,28 @@
       <c r="Y3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z3" s="74" t="s">
+      <c r="Z3" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="AB3" s="74" t="s">
+      <c r="AB3" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC3" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD3" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="60">
         <v>4</v>
       </c>
       <c r="B4" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C4" s="29" t="s">
         <v>253</v>
@@ -3659,7 +3732,7 @@
         <v>83</v>
       </c>
       <c r="R4" s="64" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="S4" s="64" t="s">
         <v>1</v>
@@ -3677,7 +3750,7 @@
         <v>Naturais</v>
       </c>
       <c r="W4" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X4" s="65" t="str">
         <f t="shared" si="3"/>
@@ -3686,25 +3759,28 @@
       <c r="Y4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z4" s="74" t="s">
+      <c r="Z4" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="AB4" s="74" t="s">
+      <c r="AB4" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC4" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD4" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <v>5</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>253</v>
@@ -3757,7 +3833,7 @@
         <v>84</v>
       </c>
       <c r="R5" s="64" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="S5" s="64" t="s">
         <v>1</v>
@@ -3775,7 +3851,7 @@
         <v>Políticas</v>
       </c>
       <c r="W5" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X5" s="65" t="str">
         <f t="shared" si="3"/>
@@ -3784,25 +3860,28 @@
       <c r="Y5" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z5" s="74" t="s">
+      <c r="Z5" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA5" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB5" s="74" t="s">
+      <c r="AB5" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC5" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD5" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="60">
         <v>6</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>253</v>
@@ -3854,7 +3933,7 @@
         <v>86</v>
       </c>
       <c r="R6" s="64" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="S6" s="64" t="s">
         <v>1</v>
@@ -3872,7 +3951,7 @@
         <v>Políticas</v>
       </c>
       <c r="W6" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X6" s="65" t="str">
         <f t="shared" si="3"/>
@@ -3881,25 +3960,28 @@
       <c r="Y6" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z6" s="74" t="s">
+      <c r="Z6" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA6" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB6" s="74" t="s">
+      <c r="AB6" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC6" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD6" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="60">
         <v>7</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C7" s="29" t="s">
         <v>253</v>
@@ -3945,14 +4027,14 @@
         <v>Região</v>
       </c>
       <c r="P7" s="69" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="Q7" s="67" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","es")</f>
         <v>Región geográfica de Brasil. de Brasil hay 5 regiones geográficas principales.</v>
       </c>
       <c r="R7" s="64" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="S7" s="64" t="s">
         <v>1</v>
@@ -3970,7 +4052,7 @@
         <v>Políticas</v>
       </c>
       <c r="W7" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X7" s="65" t="str">
         <f t="shared" si="3"/>
@@ -3979,25 +4061,28 @@
       <c r="Y7" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z7" s="74" t="s">
+      <c r="Z7" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA7" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB7" s="74" t="s">
+      <c r="AB7" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC7" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD7" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="60">
         <v>8</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>253</v>
@@ -4009,7 +4094,7 @@
         <v>255</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G8" s="66" t="s">
         <v>1</v>
@@ -4043,14 +4128,14 @@
         <v>Região Intermediária</v>
       </c>
       <c r="P8" s="69" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Q8" s="67" t="str">
         <f t="shared" ref="Q8:Q9" si="4">_xlfn.TRANSLATE(P8,"pt","es")</f>
         <v>Región geográfica intermedia. Definidas por el IBGE de Brasil, existen 133 Regiones Geográficas Intermedias, de mayor escala, que se articulan por capitales regionales o grandes centros urbanos. Diseñado para organizar el territorio articulando las Regiones Geográficas Inmediatas a través de un polo jerárquico superior, diferenciado de los flujos de gestión privada y pública y de la existencia de funciones urbanas de mayor complejidad.</v>
       </c>
       <c r="R8" s="64" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="S8" s="64" t="s">
         <v>1</v>
@@ -4068,7 +4153,7 @@
         <v>Políticas</v>
       </c>
       <c r="W8" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X8" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4077,25 +4162,28 @@
       <c r="Y8" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z8" s="74" t="s">
+      <c r="Z8" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA8" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB8" s="74" t="s">
+      <c r="AB8" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC8" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD8" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="60">
         <v>9</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>253</v>
@@ -4107,7 +4195,7 @@
         <v>255</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G9" s="66" t="s">
         <v>1</v>
@@ -4141,14 +4229,14 @@
         <v>Região Imediata</v>
       </c>
       <c r="P9" s="69" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="Q9" s="67" t="str">
         <f t="shared" si="4"/>
         <v>Región geográfica inmediata. Definida por el IBGE de Brasil, hay 510 regiones geográficas de menor escala, articuladas por ciudades medianas y pequeñas. Es en estos centros donde la población busca lo que necesita a diario: comprar productos, buscar empleo, acceder a servicios de salud y educación y resolver problemas en organismos públicos, como el INSS, el Ministerio de Trabajo y Justicia.</v>
       </c>
       <c r="R9" s="64" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="S9" s="64" t="s">
         <v>1</v>
@@ -4166,7 +4254,7 @@
         <v>Políticas</v>
       </c>
       <c r="W9" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X9" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4175,25 +4263,28 @@
       <c r="Y9" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z9" s="74" t="s">
+      <c r="Z9" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA9" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB9" s="74" t="s">
+      <c r="AB9" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC9" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD9" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60">
         <v>10</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>253</v>
@@ -4246,7 +4337,7 @@
         <v>89</v>
       </c>
       <c r="R10" s="64" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="S10" s="64" t="s">
         <v>1</v>
@@ -4264,7 +4355,7 @@
         <v>Políticas</v>
       </c>
       <c r="W10" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X10" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4273,25 +4364,28 @@
       <c r="Y10" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z10" s="74" t="s">
+      <c r="Z10" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA10" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB10" s="74" t="s">
+      <c r="AB10" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC10" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD10" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60">
         <v>11</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>253</v>
@@ -4343,7 +4437,7 @@
         <v>91</v>
       </c>
       <c r="R11" s="64" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="S11" s="64" t="s">
         <v>1</v>
@@ -4361,7 +4455,7 @@
         <v>Políticas</v>
       </c>
       <c r="W11" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X11" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4370,25 +4464,28 @@
       <c r="Y11" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z11" s="74" t="s">
+      <c r="Z11" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA11" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB11" s="74" t="s">
+      <c r="AB11" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC11" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD11" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="60">
         <v>12</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>253</v>
@@ -4441,7 +4538,7 @@
         <v>93</v>
       </c>
       <c r="R12" s="64" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="S12" s="64" t="s">
         <v>1</v>
@@ -4459,7 +4556,7 @@
         <v>Políticas</v>
       </c>
       <c r="W12" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X12" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4468,25 +4565,28 @@
       <c r="Y12" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z12" s="74" t="s">
+      <c r="Z12" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA12" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB12" s="74" t="s">
+      <c r="AB12" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC12" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD12" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60">
         <v>13</v>
       </c>
       <c r="B13" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C13" s="29" t="s">
         <v>253</v>
@@ -4533,13 +4633,13 @@
         <v>Capital</v>
       </c>
       <c r="P13" s="67" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="Q13" s="67" t="s">
         <v>94</v>
       </c>
       <c r="R13" s="64" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="S13" s="64" t="s">
         <v>1</v>
@@ -4557,7 +4657,7 @@
         <v>Políticas</v>
       </c>
       <c r="W13" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X13" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4566,25 +4666,28 @@
       <c r="Y13" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z13" s="74" t="s">
+      <c r="Z13" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA13" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB13" s="74" t="s">
+      <c r="AB13" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC13" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD13" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="60">
         <v>14</v>
       </c>
       <c r="B14" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>253</v>
@@ -4596,7 +4699,7 @@
         <v>255</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G14" s="66" t="s">
         <v>1</v>
@@ -4631,14 +4734,14 @@
         <v>Capital do Sul</v>
       </c>
       <c r="P14" s="67" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="Q14" s="67" t="str">
         <f t="shared" ref="Q14:Q24" si="6">_xlfn.TRANSLATE(P14,"pt","es")</f>
         <v>Ciudad capital de un estado situado en la región sur de Brasil.</v>
       </c>
       <c r="R14" s="64" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="S14" s="64" t="s">
         <v>1</v>
@@ -4656,7 +4759,7 @@
         <v>Políticas</v>
       </c>
       <c r="W14" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X14" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4665,25 +4768,28 @@
       <c r="Y14" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z14" s="74" t="s">
+      <c r="Z14" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA14" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB14" s="74" t="s">
+      <c r="AB14" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC14" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD14" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="60">
         <v>15</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>253</v>
@@ -4695,7 +4801,7 @@
         <v>255</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G15" s="66" t="s">
         <v>1</v>
@@ -4730,14 +4836,14 @@
         <v>Capital do Sudeste</v>
       </c>
       <c r="P15" s="67" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q15" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un estado situado en la región sureste de Brasil.</v>
       </c>
       <c r="R15" s="64" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="S15" s="64" t="s">
         <v>1</v>
@@ -4755,7 +4861,7 @@
         <v>Políticas</v>
       </c>
       <c r="W15" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X15" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4764,25 +4870,28 @@
       <c r="Y15" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z15" s="74" t="s">
+      <c r="Z15" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA15" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB15" s="74" t="s">
+      <c r="AB15" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC15" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD15" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="60">
         <v>16</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>253</v>
@@ -4794,7 +4903,7 @@
         <v>255</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G16" s="66" t="s">
         <v>1</v>
@@ -4829,14 +4938,14 @@
         <v>Capital do Norte</v>
       </c>
       <c r="P16" s="67" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="Q16" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un Estado situado en la región norte de Brasil.</v>
       </c>
       <c r="R16" s="64" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="S16" s="64" t="s">
         <v>1</v>
@@ -4854,7 +4963,7 @@
         <v>Políticas</v>
       </c>
       <c r="W16" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X16" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4863,25 +4972,28 @@
       <c r="Y16" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z16" s="74" t="s">
+      <c r="Z16" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA16" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB16" s="74" t="s">
+      <c r="AB16" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC16" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD16" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="60">
         <v>17</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C17" s="29" t="s">
         <v>253</v>
@@ -4893,7 +5005,7 @@
         <v>255</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G17" s="66" t="s">
         <v>1</v>
@@ -4928,14 +5040,14 @@
         <v>Capital do Nordeste</v>
       </c>
       <c r="P17" s="67" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="Q17" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un estado situado en la región noreste de Brasil.</v>
       </c>
       <c r="R17" s="64" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="S17" s="64" t="s">
         <v>1</v>
@@ -4953,7 +5065,7 @@
         <v>Políticas</v>
       </c>
       <c r="W17" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X17" s="65" t="str">
         <f t="shared" si="3"/>
@@ -4962,25 +5074,28 @@
       <c r="Y17" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z17" s="74" t="s">
+      <c r="Z17" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA17" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB17" s="74" t="s">
+      <c r="AB17" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC17" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD17" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="60">
         <v>18</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>253</v>
@@ -4992,7 +5107,7 @@
         <v>255</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G18" s="66" t="s">
         <v>1</v>
@@ -5027,14 +5142,14 @@
         <v>Capital do CentroOeste</v>
       </c>
       <c r="P18" s="67" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="Q18" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad capital de un estado situado en la región del Medio Oeste de Brasil.</v>
       </c>
       <c r="R18" s="64" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="S18" s="64" t="s">
         <v>1</v>
@@ -5052,7 +5167,7 @@
         <v>Políticas</v>
       </c>
       <c r="W18" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X18" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5061,25 +5176,28 @@
       <c r="Y18" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z18" s="74" t="s">
+      <c r="Z18" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA18" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB18" s="74" t="s">
+      <c r="AB18" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC18" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD18" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="60">
         <v>19</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C19" s="29" t="s">
         <v>253</v>
@@ -5126,14 +5244,14 @@
         <v>Cidade</v>
       </c>
       <c r="P19" s="67" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="Q19" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad de Brasil.</v>
       </c>
       <c r="R19" s="64" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="S19" s="64" t="s">
         <v>1</v>
@@ -5151,7 +5269,7 @@
         <v>Políticas</v>
       </c>
       <c r="W19" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X19" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5160,25 +5278,28 @@
       <c r="Y19" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z19" s="74" t="s">
+      <c r="Z19" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA19" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB19" s="74" t="s">
+      <c r="AB19" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC19" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD19" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="60">
         <v>20</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>253</v>
@@ -5190,7 +5311,7 @@
         <v>255</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G20" s="66" t="s">
         <v>1</v>
@@ -5225,14 +5346,14 @@
         <v>Cidade do Sul</v>
       </c>
       <c r="P20" s="67" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="Q20" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región sur de Brasil.</v>
       </c>
       <c r="R20" s="64" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="S20" s="64" t="s">
         <v>1</v>
@@ -5250,7 +5371,7 @@
         <v>Políticas</v>
       </c>
       <c r="W20" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X20" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5259,25 +5380,28 @@
       <c r="Y20" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z20" s="74" t="s">
+      <c r="Z20" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA20" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB20" s="74" t="s">
+      <c r="AB20" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC20" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD20" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="60">
         <v>21</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>253</v>
@@ -5289,7 +5413,7 @@
         <v>255</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G21" s="66" t="s">
         <v>1</v>
@@ -5324,14 +5448,14 @@
         <v>Cidade do Sudeste</v>
       </c>
       <c r="P21" s="67" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q21" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región sureste de Brasil.</v>
       </c>
       <c r="R21" s="64" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="S21" s="64" t="s">
         <v>1</v>
@@ -5349,7 +5473,7 @@
         <v>Políticas</v>
       </c>
       <c r="W21" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X21" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5358,25 +5482,28 @@
       <c r="Y21" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z21" s="74" t="s">
+      <c r="Z21" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA21" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB21" s="74" t="s">
+      <c r="AB21" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC21" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD21" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60">
         <v>22</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>253</v>
@@ -5388,7 +5515,7 @@
         <v>255</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G22" s="66" t="s">
         <v>1</v>
@@ -5423,14 +5550,14 @@
         <v>Cidade do Norte</v>
       </c>
       <c r="P22" s="67" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="Q22" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región norte de Brasil.</v>
       </c>
       <c r="R22" s="64" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="S22" s="64" t="s">
         <v>1</v>
@@ -5448,7 +5575,7 @@
         <v>Políticas</v>
       </c>
       <c r="W22" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X22" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5457,25 +5584,28 @@
       <c r="Y22" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z22" s="74" t="s">
+      <c r="Z22" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA22" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB22" s="74" t="s">
+      <c r="AB22" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC22" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD22" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="60">
         <v>23</v>
       </c>
       <c r="B23" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C23" s="29" t="s">
         <v>253</v>
@@ -5487,7 +5617,7 @@
         <v>255</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G23" s="66" t="s">
         <v>1</v>
@@ -5522,14 +5652,14 @@
         <v>Cidade do Nordeste</v>
       </c>
       <c r="P23" s="67" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="Q23" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región noreste de Brasil.</v>
       </c>
       <c r="R23" s="64" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="S23" s="64" t="s">
         <v>1</v>
@@ -5547,7 +5677,7 @@
         <v>Políticas</v>
       </c>
       <c r="W23" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X23" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5556,25 +5686,28 @@
       <c r="Y23" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z23" s="74" t="s">
+      <c r="Z23" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA23" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB23" s="74" t="s">
+      <c r="AB23" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC23" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD23" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="60">
         <v>24</v>
       </c>
       <c r="B24" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C24" s="29" t="s">
         <v>253</v>
@@ -5586,7 +5719,7 @@
         <v>255</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G24" s="66" t="s">
         <v>1</v>
@@ -5621,14 +5754,14 @@
         <v>Cidade do CentroOeste</v>
       </c>
       <c r="P24" s="67" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="Q24" s="67" t="str">
         <f t="shared" si="6"/>
         <v>Ciudad situada en la región del Medio Oeste de Brasil.</v>
       </c>
       <c r="R24" s="64" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="S24" s="64" t="s">
         <v>1</v>
@@ -5646,7 +5779,7 @@
         <v>Políticas</v>
       </c>
       <c r="W24" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X24" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5655,25 +5788,28 @@
       <c r="Y24" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z24" s="74" t="s">
+      <c r="Z24" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA24" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB24" s="74" t="s">
+      <c r="AB24" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC24" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD24" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60">
         <v>25</v>
       </c>
       <c r="B25" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C25" s="29" t="s">
         <v>253</v>
@@ -5726,7 +5862,7 @@
         <v>95</v>
       </c>
       <c r="R25" s="64" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="S25" s="64" t="s">
         <v>1</v>
@@ -5744,7 +5880,7 @@
         <v>Políticas</v>
       </c>
       <c r="W25" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X25" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5753,25 +5889,28 @@
       <c r="Y25" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z25" s="74" t="s">
+      <c r="Z25" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA25" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB25" s="74" t="s">
+      <c r="AB25" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC25" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD25" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60">
         <v>26</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C26" s="29" t="s">
         <v>253</v>
@@ -5824,7 +5963,7 @@
         <v>97</v>
       </c>
       <c r="R26" s="64" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="S26" s="64" t="s">
         <v>1</v>
@@ -5842,7 +5981,7 @@
         <v>Políticas</v>
       </c>
       <c r="W26" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X26" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5851,25 +5990,28 @@
       <c r="Y26" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z26" s="74" t="s">
+      <c r="Z26" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA26" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB26" s="74" t="s">
+      <c r="AB26" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC26" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD26" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60">
         <v>27</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C27" s="29" t="s">
         <v>253</v>
@@ -5922,7 +6064,7 @@
         <v>99</v>
       </c>
       <c r="R27" s="64" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="S27" s="64" t="s">
         <v>1</v>
@@ -5940,7 +6082,7 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W27" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X27" s="65" t="str">
         <f t="shared" si="3"/>
@@ -5949,25 +6091,28 @@
       <c r="Y27" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z27" s="74" t="s">
+      <c r="Z27" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA27" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB27" s="74" t="s">
+      <c r="AB27" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC27" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD27" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60">
         <v>28</v>
       </c>
       <c r="B28" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C28" s="29" t="s">
         <v>253</v>
@@ -6020,7 +6165,7 @@
         <v>101</v>
       </c>
       <c r="R28" s="64" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="S28" s="64" t="s">
         <v>1</v>
@@ -6038,7 +6183,7 @@
         <v>Bioclimáticas</v>
       </c>
       <c r="W28" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X28" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6047,25 +6192,28 @@
       <c r="Y28" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z28" s="74" t="s">
+      <c r="Z28" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA28" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB28" s="74" t="s">
+      <c r="AB28" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC28" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD28" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60">
         <v>29</v>
       </c>
       <c r="B29" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C29" s="29" t="s">
         <v>253</v>
@@ -6118,7 +6266,7 @@
         <v>103</v>
       </c>
       <c r="R29" s="64" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="S29" s="64" t="s">
         <v>1</v>
@@ -6136,7 +6284,7 @@
         <v>Ilhas de Calor</v>
       </c>
       <c r="W29" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X29" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6145,25 +6293,28 @@
       <c r="Y29" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z29" s="74" t="s">
+      <c r="Z29" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA29" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB29" s="74" t="s">
+      <c r="AB29" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC29" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD29" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="60">
         <v>30</v>
       </c>
       <c r="B30" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C30" s="29" t="s">
         <v>253</v>
@@ -6215,7 +6366,7 @@
         <v>223</v>
       </c>
       <c r="R30" s="64" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="S30" s="64" t="s">
         <v>1</v>
@@ -6233,7 +6384,7 @@
         <v>Marcos</v>
       </c>
       <c r="W30" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X30" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6242,25 +6393,28 @@
       <c r="Y30" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z30" s="74" t="s">
+      <c r="Z30" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA30" s="68" t="s">
-        <v>401</v>
-      </c>
-      <c r="AB30" s="74" t="s">
+        <v>398</v>
+      </c>
+      <c r="AB30" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC30" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD30" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="60">
         <v>31</v>
       </c>
       <c r="B31" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C31" s="29" t="s">
         <v>253</v>
@@ -6312,7 +6466,7 @@
         <v>225</v>
       </c>
       <c r="R31" s="64" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="S31" s="64" t="s">
         <v>1</v>
@@ -6330,7 +6484,7 @@
         <v>Marcos</v>
       </c>
       <c r="W31" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X31" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6339,25 +6493,28 @@
       <c r="Y31" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z31" s="74" t="s">
+      <c r="Z31" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA31" s="68" t="s">
-        <v>402</v>
-      </c>
-      <c r="AB31" s="74" t="s">
+        <v>399</v>
+      </c>
+      <c r="AB31" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC31" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD31" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60">
         <v>32</v>
       </c>
       <c r="B32" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C32" s="29" t="s">
         <v>253</v>
@@ -6409,7 +6566,7 @@
         <v>227</v>
       </c>
       <c r="R32" s="64" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="S32" s="64" t="s">
         <v>1</v>
@@ -6427,7 +6584,7 @@
         <v>Marcos</v>
       </c>
       <c r="W32" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X32" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6436,25 +6593,28 @@
       <c r="Y32" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z32" s="74" t="s">
+      <c r="Z32" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA32" s="68" t="s">
-        <v>403</v>
-      </c>
-      <c r="AB32" s="74" t="s">
+        <v>400</v>
+      </c>
+      <c r="AB32" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC32" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD32" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
         <v>33</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>253</v>
@@ -6506,7 +6666,7 @@
         <v>235</v>
       </c>
       <c r="R33" s="64" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="S33" s="64" t="s">
         <v>1</v>
@@ -6524,7 +6684,7 @@
         <v>Marcos</v>
       </c>
       <c r="W33" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X33" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6533,25 +6693,28 @@
       <c r="Y33" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z33" s="74" t="s">
+      <c r="Z33" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA33" s="68" t="s">
-        <v>404</v>
-      </c>
-      <c r="AB33" s="74" t="s">
+        <v>401</v>
+      </c>
+      <c r="AB33" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC33" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD33" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="60">
         <v>34</v>
       </c>
       <c r="B34" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C34" s="29" t="s">
         <v>253</v>
@@ -6603,7 +6766,7 @@
         <v>229</v>
       </c>
       <c r="R34" s="64" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="S34" s="64" t="s">
         <v>1</v>
@@ -6621,7 +6784,7 @@
         <v>Marcos</v>
       </c>
       <c r="W34" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X34" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6630,25 +6793,28 @@
       <c r="Y34" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z34" s="74" t="s">
+      <c r="Z34" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA34" s="68" t="s">
-        <v>405</v>
-      </c>
-      <c r="AB34" s="74" t="s">
+        <v>402</v>
+      </c>
+      <c r="AB34" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC34" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD34" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="60">
         <v>35</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C35" s="29" t="s">
         <v>253</v>
@@ -6700,7 +6866,7 @@
         <v>231</v>
       </c>
       <c r="R35" s="64" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="S35" s="64" t="s">
         <v>1</v>
@@ -6718,7 +6884,7 @@
         <v>Marcos</v>
       </c>
       <c r="W35" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X35" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6727,25 +6893,28 @@
       <c r="Y35" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z35" s="74" t="s">
+      <c r="Z35" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA35" s="68" t="s">
-        <v>406</v>
-      </c>
-      <c r="AB35" s="74" t="s">
+        <v>403</v>
+      </c>
+      <c r="AB35" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC35" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD35" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="60">
         <v>36</v>
       </c>
       <c r="B36" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C36" s="29" t="s">
         <v>253</v>
@@ -6797,7 +6966,7 @@
         <v>233</v>
       </c>
       <c r="R36" s="64" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="S36" s="64" t="s">
         <v>1</v>
@@ -6815,7 +6984,7 @@
         <v>Marcos</v>
       </c>
       <c r="W36" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X36" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6824,25 +6993,28 @@
       <c r="Y36" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z36" s="74" t="s">
+      <c r="Z36" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA36" s="68" t="s">
-        <v>407</v>
-      </c>
-      <c r="AB36" s="74" t="s">
+        <v>404</v>
+      </c>
+      <c r="AB36" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC36" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD36" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="60">
         <v>37</v>
       </c>
       <c r="B37" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C37" s="29" t="s">
         <v>253</v>
@@ -6894,7 +7066,7 @@
         <v>237</v>
       </c>
       <c r="R37" s="64" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="S37" s="64" t="s">
         <v>1</v>
@@ -6912,7 +7084,7 @@
         <v>Marcos</v>
       </c>
       <c r="W37" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X37" s="65" t="str">
         <f t="shared" si="3"/>
@@ -6921,25 +7093,28 @@
       <c r="Y37" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z37" s="74" t="s">
+      <c r="Z37" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA37" s="68" t="s">
-        <v>408</v>
-      </c>
-      <c r="AB37" s="74" t="s">
+        <v>405</v>
+      </c>
+      <c r="AB37" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC37" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD37" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="60">
         <v>38</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C38" s="29" t="s">
         <v>253</v>
@@ -6991,7 +7166,7 @@
         <v>239</v>
       </c>
       <c r="R38" s="64" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="S38" s="64" t="s">
         <v>1</v>
@@ -7009,7 +7184,7 @@
         <v>Marcos</v>
       </c>
       <c r="W38" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X38" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7018,25 +7193,28 @@
       <c r="Y38" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z38" s="74" t="s">
+      <c r="Z38" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA38" s="68" t="s">
-        <v>409</v>
-      </c>
-      <c r="AB38" s="74" t="s">
+        <v>406</v>
+      </c>
+      <c r="AB38" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC38" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD38" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="60">
         <v>39</v>
       </c>
       <c r="B39" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C39" s="29" t="s">
         <v>253</v>
@@ -7088,7 +7266,7 @@
         <v>241</v>
       </c>
       <c r="R39" s="64" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="S39" s="64" t="s">
         <v>1</v>
@@ -7106,7 +7284,7 @@
         <v>Marcos</v>
       </c>
       <c r="W39" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X39" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7115,25 +7293,28 @@
       <c r="Y39" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z39" s="74" t="s">
+      <c r="Z39" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA39" s="68" t="s">
-        <v>410</v>
-      </c>
-      <c r="AB39" s="74" t="s">
+        <v>407</v>
+      </c>
+      <c r="AB39" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC39" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD39" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="60">
         <v>40</v>
       </c>
       <c r="B40" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>253</v>
@@ -7185,7 +7366,7 @@
         <v>243</v>
       </c>
       <c r="R40" s="64" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="S40" s="64" t="s">
         <v>1</v>
@@ -7203,7 +7384,7 @@
         <v>Marcos</v>
       </c>
       <c r="W40" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X40" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7212,28 +7393,31 @@
       <c r="Y40" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="Z40" s="74" t="s">
+      <c r="Z40" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA40" s="68" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB40" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB40" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC40" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD40" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="60">
         <v>41</v>
       </c>
       <c r="B41" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>273</v>
@@ -7282,7 +7466,7 @@
         <v>350</v>
       </c>
       <c r="R41" s="64" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="S41" s="64" t="s">
         <v>1</v>
@@ -7300,7 +7484,7 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W41" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X41" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7309,28 +7493,31 @@
       <c r="Y41" s="64" t="s">
         <v>386</v>
       </c>
-      <c r="Z41" s="74" t="s">
+      <c r="Z41" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA41" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB41" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB41" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC41" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD41" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="60">
         <v>42</v>
       </c>
       <c r="B42" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>273</v>
@@ -7379,7 +7566,7 @@
         <v>351</v>
       </c>
       <c r="R42" s="64" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="S42" s="64" t="s">
         <v>1</v>
@@ -7397,7 +7584,7 @@
         <v>Pontos Cotados</v>
       </c>
       <c r="W42" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X42" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7406,28 +7593,31 @@
       <c r="Y42" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="Z42" s="74" t="s">
+      <c r="Z42" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA42" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB42" s="74" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB42" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC42" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD42" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="60">
         <v>43</v>
       </c>
       <c r="B43" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D43" s="29" t="s">
         <v>273</v>
@@ -7476,7 +7666,7 @@
         <v>352</v>
       </c>
       <c r="R43" s="64" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="S43" s="64" t="s">
         <v>1</v>
@@ -7494,7 +7684,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W43" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X43" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7503,28 +7693,31 @@
       <c r="Y43" s="64" t="s">
         <v>388</v>
       </c>
-      <c r="Z43" s="74" t="s">
+      <c r="Z43" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA43" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB43" s="74" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB43" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC43" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD43" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="60">
         <v>44</v>
       </c>
       <c r="B44" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D44" s="29" t="s">
         <v>273</v>
@@ -7573,7 +7766,7 @@
         <v>353</v>
       </c>
       <c r="R44" s="64" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="S44" s="64" t="s">
         <v>1</v>
@@ -7591,7 +7784,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W44" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X44" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7600,28 +7793,31 @@
       <c r="Y44" s="64" t="s">
         <v>389</v>
       </c>
-      <c r="Z44" s="74" t="s">
+      <c r="Z44" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA44" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB44" s="74" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB44" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC44" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD44" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="60">
         <v>45</v>
       </c>
       <c r="B45" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D45" s="29" t="s">
         <v>273</v>
@@ -7670,7 +7866,7 @@
         <v>354</v>
       </c>
       <c r="R45" s="64" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="S45" s="64" t="s">
         <v>1</v>
@@ -7688,7 +7884,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W45" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X45" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7697,28 +7893,31 @@
       <c r="Y45" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="Z45" s="74" t="s">
+      <c r="Z45" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA45" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB45" s="74" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB45" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC45" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD45" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="60">
         <v>46</v>
       </c>
       <c r="B46" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D46" s="29" t="s">
         <v>273</v>
@@ -7767,7 +7966,7 @@
         <v>355</v>
       </c>
       <c r="R46" s="64" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="S46" s="64" t="s">
         <v>1</v>
@@ -7785,7 +7984,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W46" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X46" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7794,28 +7993,31 @@
       <c r="Y46" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="Z46" s="74" t="s">
+      <c r="Z46" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA46" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB46" s="74" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB46" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC46" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD46" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="60">
         <v>47</v>
       </c>
       <c r="B47" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D47" s="29" t="s">
         <v>273</v>
@@ -7864,7 +8066,7 @@
         <v>356</v>
       </c>
       <c r="R47" s="64" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="S47" s="64" t="s">
         <v>1</v>
@@ -7882,37 +8084,40 @@
         <v>Terrenos</v>
       </c>
       <c r="W47" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X47" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-47</v>
       </c>
       <c r="Y47" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="Z47" s="74" t="s">
+        <v>415</v>
+      </c>
+      <c r="Z47" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA47" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB47" s="74" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB47" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC47" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD47" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="60">
         <v>48</v>
       </c>
       <c r="B48" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D48" s="29" t="s">
         <v>273</v>
@@ -7961,7 +8166,7 @@
         <v>357</v>
       </c>
       <c r="R48" s="64" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="S48" s="64" t="s">
         <v>1</v>
@@ -7979,7 +8184,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W48" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X48" s="65" t="str">
         <f t="shared" si="3"/>
@@ -7988,28 +8193,31 @@
       <c r="Y48" s="64" t="s">
         <v>392</v>
       </c>
-      <c r="Z48" s="74" t="s">
+      <c r="Z48" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA48" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB48" s="74" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB48" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC48" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD48" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="60">
         <v>49</v>
       </c>
       <c r="B49" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D49" s="29" t="s">
         <v>273</v>
@@ -8058,7 +8266,7 @@
         <v>358</v>
       </c>
       <c r="R49" s="64" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="S49" s="64" t="s">
         <v>1</v>
@@ -8076,7 +8284,7 @@
         <v>Terrenos</v>
       </c>
       <c r="W49" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X49" s="65" t="str">
         <f t="shared" si="3"/>
@@ -8085,28 +8293,31 @@
       <c r="Y49" s="64" t="s">
         <v>393</v>
       </c>
-      <c r="Z49" s="74" t="s">
+      <c r="Z49" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA49" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB49" s="74" t="s">
+        <v>410</v>
+      </c>
+      <c r="AB49" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC49" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD49" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="60">
         <v>50</v>
       </c>
       <c r="B50" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D50" s="29" t="s">
         <v>273</v>
@@ -8155,7 +8366,7 @@
         <v>359</v>
       </c>
       <c r="R50" s="64" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="S50" s="64" t="s">
         <v>1</v>
@@ -8173,37 +8384,40 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W50" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X50" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-50</v>
       </c>
       <c r="Y50" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="Z50" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="Z50" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA50" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB50" s="74" t="s">
+        <v>410</v>
+      </c>
+      <c r="AB50" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC50" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD50" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="60">
         <v>51</v>
       </c>
       <c r="B51" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D51" s="29" t="s">
         <v>273</v>
@@ -8252,7 +8466,7 @@
         <v>360</v>
       </c>
       <c r="R51" s="64" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="S51" s="64" t="s">
         <v>1</v>
@@ -8270,37 +8484,40 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W51" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X51" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-51</v>
       </c>
       <c r="Y51" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="Z51" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="Z51" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA51" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB51" s="74" t="s">
+        <v>410</v>
+      </c>
+      <c r="AB51" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC51" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD51" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="60">
         <v>52</v>
       </c>
       <c r="B52" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D52" s="29" t="s">
         <v>273</v>
@@ -8349,7 +8566,7 @@
         <v>361</v>
       </c>
       <c r="R52" s="64" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="S52" s="64" t="s">
         <v>1</v>
@@ -8367,37 +8584,40 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W52" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X52" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-52</v>
       </c>
       <c r="Y52" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="Z52" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="Z52" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA52" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB52" s="74" t="s">
+        <v>410</v>
+      </c>
+      <c r="AB52" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC52" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD52" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="60">
         <v>53</v>
       </c>
       <c r="B53" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D53" s="29" t="s">
         <v>273</v>
@@ -8446,7 +8666,7 @@
         <v>362</v>
       </c>
       <c r="R53" s="64" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="S53" s="64" t="s">
         <v>1</v>
@@ -8464,37 +8684,40 @@
         <v>Curvas de Nível</v>
       </c>
       <c r="W53" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X53" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-53</v>
       </c>
       <c r="Y53" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="Z53" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="Z53" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA53" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB53" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB53" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC53" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD53" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="60">
         <v>54</v>
       </c>
       <c r="B54" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D54" s="29" t="s">
         <v>273</v>
@@ -8543,7 +8766,7 @@
         <v>363</v>
       </c>
       <c r="R54" s="64" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S54" s="64" t="s">
         <v>1</v>
@@ -8561,7 +8784,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W54" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X54" s="65" t="str">
         <f t="shared" si="3"/>
@@ -8570,31 +8793,34 @@
       <c r="Y54" s="64" t="s">
         <v>386</v>
       </c>
-      <c r="Z54" s="74" t="s">
+      <c r="Z54" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA54" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB54" s="74" t="s">
+      <c r="AB54" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC54" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD54" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="60">
         <v>55</v>
       </c>
       <c r="B55" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C55" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E55" s="29" t="s">
         <v>270</v>
@@ -8643,7 +8869,7 @@
         <v>105</v>
       </c>
       <c r="R55" s="64" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S55" s="64" t="s">
         <v>1</v>
@@ -8661,7 +8887,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W55" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X55" s="65" t="str">
         <f t="shared" si="3"/>
@@ -8670,31 +8896,34 @@
       <c r="Y55" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z55" s="74" t="s">
+      <c r="Z55" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA55" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB55" s="74" t="s">
+      <c r="AB55" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC55" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD55" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="60">
         <v>56</v>
       </c>
       <c r="B56" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E56" s="29" t="s">
         <v>270</v>
@@ -8742,7 +8971,7 @@
         <v>107</v>
       </c>
       <c r="R56" s="64" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S56" s="64" t="s">
         <v>1</v>
@@ -8760,7 +8989,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W56" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X56" s="65" t="str">
         <f t="shared" si="3"/>
@@ -8769,31 +8998,34 @@
       <c r="Y56" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z56" s="74" t="s">
+      <c r="Z56" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA56" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB56" s="74" t="s">
+      <c r="AB56" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC56" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD56" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="60">
         <v>57</v>
       </c>
       <c r="B57" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C57" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E57" s="29" t="s">
         <v>270</v>
@@ -8839,7 +9071,7 @@
         <v>108</v>
       </c>
       <c r="R57" s="64" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="S57" s="64" t="s">
         <v>1</v>
@@ -8857,7 +9089,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W57" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X57" s="65" t="str">
         <f t="shared" si="3"/>
@@ -8866,31 +9098,34 @@
       <c r="Y57" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z57" s="74" t="s">
+      <c r="Z57" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA57" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB57" s="74" t="s">
+      <c r="AB57" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC57" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD57" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="60">
         <v>58</v>
       </c>
       <c r="B58" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E58" s="29" t="s">
         <v>270</v>
@@ -8936,7 +9171,7 @@
         <v>111</v>
       </c>
       <c r="R58" s="64" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="S58" s="64" t="s">
         <v>1</v>
@@ -8954,7 +9189,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W58" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X58" s="65" t="str">
         <f t="shared" si="3"/>
@@ -8963,31 +9198,34 @@
       <c r="Y58" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z58" s="74" t="s">
+      <c r="Z58" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA58" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB58" s="74" t="s">
+      <c r="AB58" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC58" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD58" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="60">
         <v>59</v>
       </c>
       <c r="B59" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C59" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E59" s="29" t="s">
         <v>270</v>
@@ -9033,7 +9271,7 @@
         <v>114</v>
       </c>
       <c r="R59" s="64" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="S59" s="64" t="s">
         <v>1</v>
@@ -9051,7 +9289,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W59" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X59" s="65" t="str">
         <f t="shared" si="3"/>
@@ -9060,31 +9298,34 @@
       <c r="Y59" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z59" s="74" t="s">
+      <c r="Z59" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA59" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB59" s="74" t="s">
+      <c r="AB59" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC59" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD59" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="60">
         <v>60</v>
       </c>
       <c r="B60" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C60" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E60" s="29" t="s">
         <v>270</v>
@@ -9130,7 +9371,7 @@
         <v>117</v>
       </c>
       <c r="R60" s="64" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="S60" s="64" t="s">
         <v>1</v>
@@ -9148,7 +9389,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W60" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X60" s="65" t="str">
         <f t="shared" si="3"/>
@@ -9157,31 +9398,34 @@
       <c r="Y60" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z60" s="74" t="s">
+      <c r="Z60" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA60" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB60" s="74" t="s">
+      <c r="AB60" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC60" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD60" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="60">
         <v>61</v>
       </c>
       <c r="B61" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C61" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>270</v>
@@ -9227,7 +9471,7 @@
         <v>118</v>
       </c>
       <c r="R61" s="64" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="S61" s="64" t="s">
         <v>1</v>
@@ -9245,7 +9489,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W61" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X61" s="65" t="str">
         <f t="shared" si="3"/>
@@ -9254,31 +9498,34 @@
       <c r="Y61" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z61" s="74" t="s">
+      <c r="Z61" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA61" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB61" s="74" t="s">
+      <c r="AB61" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC61" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD61" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="60">
         <v>62</v>
       </c>
       <c r="B62" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C62" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E62" s="29" t="s">
         <v>270</v>
@@ -9324,7 +9571,7 @@
         <v>117</v>
       </c>
       <c r="R62" s="64" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="S62" s="64" t="s">
         <v>1</v>
@@ -9342,7 +9589,7 @@
         <v>Zonificações</v>
       </c>
       <c r="W62" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X62" s="65" t="str">
         <f t="shared" si="3"/>
@@ -9351,31 +9598,34 @@
       <c r="Y62" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z62" s="74" t="s">
+      <c r="Z62" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA62" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB62" s="74" t="s">
+        <v>411</v>
+      </c>
+      <c r="AB62" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC62" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD62" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="60">
         <v>63</v>
       </c>
       <c r="B63" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C63" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E63" s="29" t="s">
         <v>269</v>
@@ -9421,7 +9671,7 @@
         <v>122</v>
       </c>
       <c r="R63" s="64" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="S63" s="64" t="s">
         <v>1</v>
@@ -9439,40 +9689,43 @@
         <v>Frações</v>
       </c>
       <c r="W63" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X63" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-63</v>
       </c>
       <c r="Y63" s="64" t="s">
-        <v>395</v>
-      </c>
-      <c r="Z63" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="Z63" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA63" s="64" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB63" s="74" t="s">
+        <v>411</v>
+      </c>
+      <c r="AB63" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC63" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD63" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="60">
         <v>64</v>
       </c>
       <c r="B64" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E64" s="29" t="s">
         <v>269</v>
@@ -9518,7 +9771,7 @@
         <v>124</v>
       </c>
       <c r="R64" s="64" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="S64" s="64" t="s">
         <v>1</v>
@@ -9536,40 +9789,43 @@
         <v>Frações</v>
       </c>
       <c r="W64" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X64" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-64</v>
       </c>
       <c r="Y64" s="64" t="s">
-        <v>395</v>
-      </c>
-      <c r="Z64" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="Z64" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA64" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB64" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB64" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC64" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD64" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="60">
         <v>65</v>
       </c>
       <c r="B65" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C65" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E65" s="29" t="s">
         <v>269</v>
@@ -9615,7 +9871,7 @@
         <v>126</v>
       </c>
       <c r="R65" s="64" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="S65" s="64" t="s">
         <v>1</v>
@@ -9633,40 +9889,43 @@
         <v>Frações</v>
       </c>
       <c r="W65" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X65" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-65</v>
       </c>
       <c r="Y65" s="64" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z65" s="74" t="s">
+        <v>593</v>
+      </c>
+      <c r="Z65" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA65" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB65" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB65" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC65" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD65" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="60">
         <v>66</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E66" s="29" t="s">
         <v>269</v>
@@ -9712,7 +9971,7 @@
         <v>128</v>
       </c>
       <c r="R66" s="64" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="S66" s="64" t="s">
         <v>1</v>
@@ -9730,40 +9989,43 @@
         <v>Frações</v>
       </c>
       <c r="W66" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X66" s="65" t="str">
         <f t="shared" si="3"/>
         <v>Key-BRASIL_MG-66</v>
       </c>
       <c r="Y66" s="64" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z66" s="74" t="s">
+        <v>593</v>
+      </c>
+      <c r="Z66" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA66" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB66" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB66" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC66" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD66" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="60">
         <v>67</v>
       </c>
       <c r="B67" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C67" s="29" t="s">
         <v>263</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E67" s="29" t="s">
         <v>269</v>
@@ -9809,7 +10071,7 @@
         <v>130</v>
       </c>
       <c r="R67" s="64" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="S67" s="64" t="s">
         <v>1</v>
@@ -9827,37 +10089,40 @@
         <v>Frações</v>
       </c>
       <c r="W67" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X67" s="65" t="str">
-        <f t="shared" ref="X67:X101" si="15">CONCATENATE("Key-BRASIL_MG-",A67)</f>
+        <f t="shared" ref="X67:X100" si="15">CONCATENATE("Key-BRASIL_MG-",A67)</f>
         <v>Key-BRASIL_MG-67</v>
       </c>
       <c r="Y67" s="64" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z67" s="74" t="s">
+        <v>593</v>
+      </c>
+      <c r="Z67" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA67" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB67" s="74" t="s">
+      <c r="AB67" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC67" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD67" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="60">
         <v>68</v>
       </c>
       <c r="B68" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C68" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D68" s="29" t="s">
         <v>264</v>
@@ -9907,7 +10172,7 @@
         <v>364</v>
       </c>
       <c r="R68" s="64" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="S68" s="64" t="s">
         <v>1</v>
@@ -9925,7 +10190,7 @@
         <v>Construídas</v>
       </c>
       <c r="W68" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X68" s="65" t="str">
         <f t="shared" si="15"/>
@@ -9934,28 +10199,31 @@
       <c r="Y68" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z68" s="74" t="s">
+      <c r="Z68" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA68" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB68" s="74" t="s">
+      <c r="AB68" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC68" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD68" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="60">
         <v>69</v>
       </c>
       <c r="B69" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D69" s="29" t="s">
         <v>264</v>
@@ -10005,7 +10273,7 @@
         <v>132</v>
       </c>
       <c r="R69" s="64" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="S69" s="64" t="s">
         <v>1</v>
@@ -10023,7 +10291,7 @@
         <v>Construídas</v>
       </c>
       <c r="W69" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X69" s="65" t="str">
         <f t="shared" si="15"/>
@@ -10032,28 +10300,31 @@
       <c r="Y69" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z69" s="74" t="s">
+      <c r="Z69" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA69" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB69" s="74" t="s">
+      <c r="AB69" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC69" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD69" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="60">
         <v>70</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D70" s="29" t="s">
         <v>264</v>
@@ -10103,7 +10374,7 @@
         <v>134</v>
       </c>
       <c r="R70" s="64" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="S70" s="64" t="s">
         <v>1</v>
@@ -10121,7 +10392,7 @@
         <v>Construídas</v>
       </c>
       <c r="W70" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X70" s="65" t="str">
         <f t="shared" si="15"/>
@@ -10130,28 +10401,31 @@
       <c r="Y70" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z70" s="74" t="s">
+      <c r="Z70" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA70" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB70" s="74" t="s">
+      <c r="AB70" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC70" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD70" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="60">
         <v>71</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D71" s="29" t="s">
         <v>264</v>
@@ -10201,7 +10475,7 @@
         <v>135</v>
       </c>
       <c r="R71" s="64" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="S71" s="64" t="s">
         <v>1</v>
@@ -10219,7 +10493,7 @@
         <v>Construídas</v>
       </c>
       <c r="W71" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X71" s="65" t="str">
         <f t="shared" si="15"/>
@@ -10228,28 +10502,31 @@
       <c r="Y71" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z71" s="74" t="s">
+      <c r="Z71" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA71" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB71" s="74" t="s">
+      <c r="AB71" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC71" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD71" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="60">
         <v>72</v>
       </c>
       <c r="B72" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D72" s="29" t="s">
         <v>264</v>
@@ -10299,7 +10576,7 @@
         <v>137</v>
       </c>
       <c r="R72" s="64" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="S72" s="64" t="s">
         <v>1</v>
@@ -10317,7 +10594,7 @@
         <v>Construídas</v>
       </c>
       <c r="W72" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X72" s="65" t="str">
         <f t="shared" si="15"/>
@@ -10326,28 +10603,31 @@
       <c r="Y72" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z72" s="74" t="s">
+      <c r="Z72" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA72" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB72" s="74" t="s">
+      <c r="AB72" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC72" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD72" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="60">
         <v>73</v>
       </c>
       <c r="B73" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D73" s="29" t="s">
         <v>264</v>
@@ -10396,7 +10676,7 @@
         <v>140</v>
       </c>
       <c r="R73" s="64" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="S73" s="64" t="s">
         <v>1</v>
@@ -10414,7 +10694,7 @@
         <v>Construídas</v>
       </c>
       <c r="W73" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X73" s="65" t="str">
         <f t="shared" si="15"/>
@@ -10423,28 +10703,31 @@
       <c r="Y73" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z73" s="74" t="s">
+      <c r="Z73" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA73" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="AB73" s="74" t="s">
+      <c r="AB73" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC73" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD73" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="60">
         <v>74</v>
       </c>
       <c r="B74" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D74" s="29" t="s">
         <v>264</v>
@@ -10493,7 +10776,7 @@
         <v>141</v>
       </c>
       <c r="R74" s="64" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="S74" s="64" t="s">
         <v>1</v>
@@ -10511,7 +10794,7 @@
         <v>Construídas</v>
       </c>
       <c r="W74" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X74" s="65" t="str">
         <f t="shared" si="15"/>
@@ -10520,28 +10803,31 @@
       <c r="Y74" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z74" s="74" t="s">
+      <c r="Z74" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA74" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB74" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB74" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC74" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD74" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="60">
         <v>75</v>
       </c>
       <c r="B75" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D75" s="29" t="s">
         <v>265</v>
@@ -10591,7 +10877,7 @@
         <v>144</v>
       </c>
       <c r="R75" s="64" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="S75" s="64" t="s">
         <v>1</v>
@@ -10609,7 +10895,7 @@
         <v>Organizativas</v>
       </c>
       <c r="W75" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X75" s="65" t="str">
         <f t="shared" si="15"/>
@@ -10618,28 +10904,31 @@
       <c r="Y75" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="Z75" s="74" t="s">
+      <c r="Z75" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA75" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB75" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB75" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC75" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD75" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="60">
         <v>76</v>
       </c>
       <c r="B76" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D76" s="29" t="s">
         <v>265</v>
@@ -10688,7 +10977,7 @@
         <v>145</v>
       </c>
       <c r="R76" s="64" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="S76" s="64" t="s">
         <v>1</v>
@@ -10706,37 +10995,40 @@
         <v>Organizativas</v>
       </c>
       <c r="W76" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X76" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-76</v>
       </c>
       <c r="Y76" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z76" s="74" t="s">
+        <v>594</v>
+      </c>
+      <c r="Z76" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA76" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB76" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB76" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC76" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD76" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="60">
         <v>77</v>
       </c>
       <c r="B77" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C77" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D77" s="29" t="s">
         <v>265</v>
@@ -10785,7 +11077,7 @@
         <v>147</v>
       </c>
       <c r="R77" s="64" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="S77" s="64" t="s">
         <v>1</v>
@@ -10803,37 +11095,40 @@
         <v>Organizativas</v>
       </c>
       <c r="W77" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X77" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-77</v>
       </c>
       <c r="Y77" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z77" s="74" t="s">
+        <v>594</v>
+      </c>
+      <c r="Z77" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA77" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB77" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB77" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC77" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD77" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="60">
         <v>78</v>
       </c>
       <c r="B78" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C78" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D78" s="29" t="s">
         <v>265</v>
@@ -10882,7 +11177,7 @@
         <v>148</v>
       </c>
       <c r="R78" s="64" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="S78" s="64" t="s">
         <v>1</v>
@@ -10900,37 +11195,40 @@
         <v>Organizativas</v>
       </c>
       <c r="W78" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X78" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-78</v>
       </c>
       <c r="Y78" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z78" s="74" t="s">
+        <v>594</v>
+      </c>
+      <c r="Z78" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA78" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="AB78" s="74" t="s">
+        <v>413</v>
+      </c>
+      <c r="AB78" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC78" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD78" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="60">
         <v>79</v>
       </c>
       <c r="B79" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C79" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D79" s="29" t="s">
         <v>265</v>
@@ -10979,7 +11277,7 @@
         <v>149</v>
       </c>
       <c r="R79" s="64" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="S79" s="64" t="s">
         <v>1</v>
@@ -10997,37 +11295,40 @@
         <v>Distribuição</v>
       </c>
       <c r="W79" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X79" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-79</v>
       </c>
       <c r="Y79" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="Z79" s="74" t="s">
+        <v>395</v>
+      </c>
+      <c r="Z79" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA79" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB79" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB79" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC79" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD79" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="60">
         <v>80</v>
       </c>
       <c r="B80" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C80" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D80" s="29" t="s">
         <v>265</v>
@@ -11076,7 +11377,7 @@
         <v>150</v>
       </c>
       <c r="R80" s="64" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="S80" s="64" t="s">
         <v>1</v>
@@ -11094,37 +11395,40 @@
         <v>Distribuição</v>
       </c>
       <c r="W80" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X80" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-80</v>
       </c>
       <c r="Y80" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z80" s="74" t="s">
+        <v>594</v>
+      </c>
+      <c r="Z80" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA80" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="AB80" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB80" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC80" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD80" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="60">
         <v>81</v>
       </c>
       <c r="B81" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C81" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D81" s="29" t="s">
         <v>265</v>
@@ -11173,7 +11477,7 @@
         <v>152</v>
       </c>
       <c r="R81" s="64" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="S81" s="64" t="s">
         <v>1</v>
@@ -11191,40 +11495,43 @@
         <v>Distribuição</v>
       </c>
       <c r="W81" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X81" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-81</v>
       </c>
       <c r="Y81" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z81" s="74" t="s">
+        <v>594</v>
+      </c>
+      <c r="Z81" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA81" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB81" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB81" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC81" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD81" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="60">
         <v>82</v>
       </c>
       <c r="B82" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C82" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E82" s="29" t="s">
         <v>153</v>
@@ -11270,7 +11577,7 @@
         <v>155</v>
       </c>
       <c r="R82" s="64" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="S82" s="64" t="s">
         <v>1</v>
@@ -11288,40 +11595,43 @@
         <v>Saúde</v>
       </c>
       <c r="W82" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X82" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-82</v>
       </c>
       <c r="Y82" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z82" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z82" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA82" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB82" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB82" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC82" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD82" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="60">
         <v>83</v>
       </c>
       <c r="B83" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C83" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E83" s="29" t="s">
         <v>153</v>
@@ -11367,7 +11677,7 @@
         <v>157</v>
       </c>
       <c r="R83" s="64" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="S83" s="64" t="s">
         <v>1</v>
@@ -11385,40 +11695,43 @@
         <v>Saúde</v>
       </c>
       <c r="W83" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X83" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-83</v>
       </c>
       <c r="Y83" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z83" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z83" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA83" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB83" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB83" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC83" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD83" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="60">
         <v>84</v>
       </c>
       <c r="B84" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C84" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E84" s="29" t="s">
         <v>153</v>
@@ -11464,7 +11777,7 @@
         <v>159</v>
       </c>
       <c r="R84" s="64" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="S84" s="64" t="s">
         <v>1</v>
@@ -11482,40 +11795,43 @@
         <v>Saúde</v>
       </c>
       <c r="W84" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X84" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-84</v>
       </c>
       <c r="Y84" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z84" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z84" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA84" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB84" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB84" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC84" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD84" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="60">
         <v>85</v>
       </c>
       <c r="B85" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E85" s="29" t="s">
         <v>153</v>
@@ -11561,7 +11877,7 @@
         <v>162</v>
       </c>
       <c r="R85" s="64" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="S85" s="64" t="s">
         <v>1</v>
@@ -11579,40 +11895,43 @@
         <v>Saúde</v>
       </c>
       <c r="W85" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X85" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-85</v>
       </c>
       <c r="Y85" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z85" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z85" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA85" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB85" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB85" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC85" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD85" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="60">
         <v>86</v>
       </c>
       <c r="B86" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E86" s="29" t="s">
         <v>153</v>
@@ -11658,7 +11977,7 @@
         <v>165</v>
       </c>
       <c r="R86" s="64" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="S86" s="64" t="s">
         <v>1</v>
@@ -11676,40 +11995,43 @@
         <v>Saúde</v>
       </c>
       <c r="W86" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X86" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-86</v>
       </c>
       <c r="Y86" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z86" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z86" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA86" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB86" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB86" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC86" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD86" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="60">
         <v>87</v>
       </c>
       <c r="B87" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C87" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E87" s="29" t="s">
         <v>268</v>
@@ -11755,7 +12077,7 @@
         <v>167</v>
       </c>
       <c r="R87" s="64" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="S87" s="64" t="s">
         <v>1</v>
@@ -11773,40 +12095,43 @@
         <v>Educacionais</v>
       </c>
       <c r="W87" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X87" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-87</v>
       </c>
       <c r="Y87" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z87" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z87" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA87" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB87" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB87" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC87" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD87" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="60">
         <v>88</v>
       </c>
       <c r="B88" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E88" s="29" t="s">
         <v>268</v>
@@ -11852,7 +12177,7 @@
         <v>169</v>
       </c>
       <c r="R88" s="64" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="S88" s="64" t="s">
         <v>1</v>
@@ -11870,40 +12195,43 @@
         <v>Educacionais</v>
       </c>
       <c r="W88" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X88" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-88</v>
       </c>
       <c r="Y88" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z88" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z88" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA88" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB88" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB88" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC88" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD88" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="60">
         <v>89</v>
       </c>
       <c r="B89" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E89" s="29" t="s">
         <v>268</v>
@@ -11949,7 +12277,7 @@
         <v>171</v>
       </c>
       <c r="R89" s="64" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="S89" s="64" t="s">
         <v>1</v>
@@ -11967,40 +12295,43 @@
         <v>Educacionais</v>
       </c>
       <c r="W89" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X89" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-89</v>
       </c>
       <c r="Y89" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z89" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z89" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA89" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB89" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB89" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC89" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD89" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="60">
         <v>90</v>
       </c>
       <c r="B90" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C90" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E90" s="29" t="s">
         <v>268</v>
@@ -12046,7 +12377,7 @@
         <v>173</v>
       </c>
       <c r="R90" s="64" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="S90" s="64" t="s">
         <v>1</v>
@@ -12064,40 +12395,43 @@
         <v>Educacionais</v>
       </c>
       <c r="W90" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X90" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-90</v>
       </c>
       <c r="Y90" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z90" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z90" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA90" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB90" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB90" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC90" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD90" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="60">
         <v>91</v>
       </c>
       <c r="B91" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C91" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E91" s="29" t="s">
         <v>268</v>
@@ -12143,7 +12477,7 @@
         <v>367</v>
       </c>
       <c r="R91" s="64" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="S91" s="64" t="s">
         <v>1</v>
@@ -12161,40 +12495,43 @@
         <v>Educacionais</v>
       </c>
       <c r="W91" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X91" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-91</v>
       </c>
       <c r="Y91" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z91" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z91" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA91" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="AB91" s="74" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB91" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC91" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD91" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="60">
         <v>92</v>
       </c>
       <c r="B92" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C92" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E92" s="29" t="s">
         <v>268</v>
@@ -12240,7 +12577,7 @@
         <v>370</v>
       </c>
       <c r="R92" s="64" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="S92" s="64" t="s">
         <v>1</v>
@@ -12258,40 +12595,43 @@
         <v>Educacionais</v>
       </c>
       <c r="W92" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X92" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-92</v>
       </c>
       <c r="Y92" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z92" s="74" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z92" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA92" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB92" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB92" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC92" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD92" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="60">
         <v>93</v>
       </c>
       <c r="B93" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C93" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E93" s="29" t="s">
         <v>174</v>
@@ -12337,7 +12677,7 @@
         <v>177</v>
       </c>
       <c r="R93" s="64" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="S93" s="64" t="s">
         <v>1</v>
@@ -12355,46 +12695,49 @@
         <v>INMET</v>
       </c>
       <c r="W93" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X93" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-93</v>
       </c>
       <c r="Y93" s="64" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z93" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z93" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA93" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB93" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB93" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC93" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD93" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="60">
         <v>94</v>
       </c>
       <c r="B94" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C94" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E94" s="29" t="s">
         <v>174</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G94" s="66" t="s">
         <v>1</v>
@@ -12428,13 +12771,13 @@
         <v>Estação Meteorológica Automática</v>
       </c>
       <c r="P94" s="67" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="Q94" s="67" t="s">
         <v>177</v>
       </c>
       <c r="R94" s="64" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="S94" s="64" t="s">
         <v>1</v>
@@ -12452,46 +12795,49 @@
         <v>INMET</v>
       </c>
       <c r="W94" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X94" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-94</v>
       </c>
       <c r="Y94" s="64" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z94" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z94" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA94" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB94" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB94" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC94" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD94" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="60">
         <v>95</v>
       </c>
       <c r="B95" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C95" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E95" s="29" t="s">
         <v>174</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G95" s="66" t="s">
         <v>1</v>
@@ -12525,13 +12871,13 @@
         <v>Estação Meteorológica Convencional</v>
       </c>
       <c r="P95" s="67" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="Q95" s="67" t="s">
         <v>177</v>
       </c>
       <c r="R95" s="64" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="S95" s="64" t="s">
         <v>1</v>
@@ -12549,40 +12895,43 @@
         <v>INMET</v>
       </c>
       <c r="W95" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X95" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-95</v>
       </c>
       <c r="Y95" s="64" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z95" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z95" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AA95" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB95" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB95" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC95" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD95" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="60">
         <v>96</v>
       </c>
       <c r="B96" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E96" s="29" t="s">
         <v>178</v>
@@ -12628,7 +12977,7 @@
         <v>181</v>
       </c>
       <c r="R96" s="64" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="S96" s="64" t="s">
         <v>1</v>
@@ -12646,40 +12995,43 @@
         <v>IBGE</v>
       </c>
       <c r="W96" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X96" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-96</v>
       </c>
-      <c r="Y96" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z96" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA96" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB96" s="74" t="s">
+      <c r="Y96" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC96" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD96" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="60">
         <v>97</v>
       </c>
       <c r="B97" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E97" s="29" t="s">
         <v>178</v>
@@ -12725,7 +13077,7 @@
         <v>181</v>
       </c>
       <c r="R97" s="64" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="S97" s="64" t="s">
         <v>1</v>
@@ -12743,40 +13095,43 @@
         <v>IBGE</v>
       </c>
       <c r="W97" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X97" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-97</v>
       </c>
-      <c r="Y97" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z97" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA97" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB97" s="74" t="s">
+      <c r="Y97" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA97" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB97" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC97" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD97" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="60">
         <v>98</v>
       </c>
       <c r="B98" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C98" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E98" s="29" t="s">
         <v>178</v>
@@ -12822,7 +13177,7 @@
         <v>185</v>
       </c>
       <c r="R98" s="64" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="S98" s="64" t="s">
         <v>1</v>
@@ -12840,40 +13195,43 @@
         <v>IBGE</v>
       </c>
       <c r="W98" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X98" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-98</v>
       </c>
-      <c r="Y98" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z98" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA98" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB98" s="74" t="s">
+      <c r="Y98" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z98" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB98" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC98" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD98" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="60">
         <v>99</v>
       </c>
       <c r="B99" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C99" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E99" s="29" t="s">
         <v>178</v>
@@ -12919,7 +13277,7 @@
         <v>188</v>
       </c>
       <c r="R99" s="64" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="S99" s="64" t="s">
         <v>1</v>
@@ -12937,40 +13295,43 @@
         <v>IBGE</v>
       </c>
       <c r="W99" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X99" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-99</v>
       </c>
-      <c r="Y99" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z99" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA99" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB99" s="74" t="s">
+      <c r="Y99" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC99" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD99" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="60">
         <v>100</v>
       </c>
       <c r="B100" s="61" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C100" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E100" s="29" t="s">
         <v>178</v>
@@ -13016,7 +13377,7 @@
         <v>191</v>
       </c>
       <c r="R100" s="64" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="S100" s="64" t="s">
         <v>1</v>
@@ -13034,95 +13395,98 @@
         <v>IBGE</v>
       </c>
       <c r="W100" s="64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="X100" s="65" t="str">
         <f t="shared" si="15"/>
         <v>Key-BRASIL_MG-100</v>
       </c>
-      <c r="Y100" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z100" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA100" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB100" s="74" t="s">
+      <c r="Y100" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA100" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB100" s="72" t="s">
         <v>1</v>
       </c>
       <c r="AC100" s="68" t="s">
         <v>1</v>
       </c>
+      <c r="AD100" s="68" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="60">
         <v>101</v>
       </c>
-      <c r="B101" s="70" t="s">
+      <c r="B101" s="74" t="s">
+        <v>566</v>
+      </c>
+      <c r="C101" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="D101" s="35" t="s">
         <v>569</v>
       </c>
-      <c r="C101" s="71" t="s">
+      <c r="E101" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="F101" s="35" t="s">
         <v>570</v>
       </c>
-      <c r="D101" s="71" t="s">
-        <v>572</v>
-      </c>
-      <c r="E101" s="71" t="s">
-        <v>571</v>
-      </c>
-      <c r="F101" s="71" t="s">
-        <v>573</v>
-      </c>
-      <c r="G101" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K101" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L101" s="72" t="str">
-        <f t="shared" ref="L101:O101" si="18">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
+      <c r="G101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" s="70" t="str">
+        <f t="shared" ref="L101:O105" si="18">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M101" s="72" t="str">
+      <c r="M101" s="70" t="str">
         <f t="shared" si="18"/>
         <v>Macros</v>
       </c>
-      <c r="N101" s="72" t="str">
+      <c r="N101" s="70" t="str">
         <f t="shared" si="18"/>
         <v>Métodos</v>
       </c>
-      <c r="O101" s="72" t="str">
+      <c r="O101" s="70" t="str">
         <f t="shared" si="18"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P101" s="73" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q101" s="73" t="s">
-        <v>575</v>
-      </c>
-      <c r="R101" s="73" t="s">
-        <v>576</v>
-      </c>
-      <c r="S101" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="T101" s="73" t="str">
-        <f t="shared" ref="T101:V101" si="19">SUBSTITUTE(C101, ".", " ")</f>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P101" s="71" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q101" s="71" t="s">
+        <v>572</v>
+      </c>
+      <c r="R101" s="71" t="s">
+        <v>573</v>
+      </c>
+      <c r="S101" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="T101" s="71" t="str">
+        <f t="shared" ref="T101:V105" si="19">SUBSTITUTE(C101, ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="U101" s="73" t="str">
+      <c r="U101" s="71" t="str">
         <f t="shared" si="19"/>
         <v>Macros</v>
       </c>
@@ -13130,106 +13494,512 @@
         <f t="shared" si="19"/>
         <v>Métodos</v>
       </c>
-      <c r="W101" s="64" t="s">
-        <v>435</v>
-      </c>
-      <c r="X101" s="65" t="str">
-        <f t="shared" si="15"/>
-        <v>Key-BRASIL_MG-101</v>
-      </c>
-      <c r="Y101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB101" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC101" s="74" t="s">
+      <c r="W101" s="71" t="s">
+        <v>574</v>
+      </c>
+      <c r="X101" s="76" t="str">
+        <f t="shared" ref="X101:X105" si="20">CONCATENATE("Key-PAISA-",A101)</f>
+        <v>Key-PAISA-101</v>
+      </c>
+      <c r="Y101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC101" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD101" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="60">
+        <v>102</v>
+      </c>
+      <c r="B102" s="74" t="s">
+        <v>566</v>
+      </c>
+      <c r="C102" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="D102" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="E102" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="F102" s="35" t="s">
+        <v>575</v>
+      </c>
+      <c r="G102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="I102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="K102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="L102" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>De API</v>
+      </c>
+      <c r="M102" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Macros</v>
+      </c>
+      <c r="N102" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O102" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P102" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q102" s="71" t="s">
+        <v>577</v>
+      </c>
+      <c r="R102" s="71" t="s">
+        <v>578</v>
+      </c>
+      <c r="S102" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="T102" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>De API</v>
+      </c>
+      <c r="U102" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>Macros</v>
+      </c>
+      <c r="V102" s="64" t="str">
+        <f t="shared" si="19"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W102" s="71" t="s">
+        <v>574</v>
+      </c>
+      <c r="X102" s="76" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-PAISA-102</v>
+      </c>
+      <c r="Y102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC102" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD102" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="60">
+        <v>103</v>
+      </c>
+      <c r="B103" s="74" t="s">
+        <v>566</v>
+      </c>
+      <c r="C103" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="D103" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="E103" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="F103" s="35" t="s">
+        <v>579</v>
+      </c>
+      <c r="G103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="I103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="J103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="K103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="L103" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>De API</v>
+      </c>
+      <c r="M103" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Macros</v>
+      </c>
+      <c r="N103" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O103" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P103" s="71" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q103" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="R103" s="71" t="s">
+        <v>582</v>
+      </c>
+      <c r="S103" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="T103" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>De API</v>
+      </c>
+      <c r="U103" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>Macros</v>
+      </c>
+      <c r="V103" s="64" t="str">
+        <f t="shared" si="19"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W103" s="71" t="s">
+        <v>574</v>
+      </c>
+      <c r="X103" s="76" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-PAISA-103</v>
+      </c>
+      <c r="Y103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC103" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD103" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="60">
+        <v>104</v>
+      </c>
+      <c r="B104" s="74" t="s">
+        <v>566</v>
+      </c>
+      <c r="C104" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="D104" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="E104" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="F104" s="35" t="s">
+        <v>583</v>
+      </c>
+      <c r="G104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="I104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="J104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="K104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="L104" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>De API</v>
+      </c>
+      <c r="M104" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Macros</v>
+      </c>
+      <c r="N104" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O104" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P104" s="71" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q104" s="71" t="s">
+        <v>585</v>
+      </c>
+      <c r="R104" s="71" t="s">
+        <v>586</v>
+      </c>
+      <c r="S104" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="T104" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>De API</v>
+      </c>
+      <c r="U104" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>Macros</v>
+      </c>
+      <c r="V104" s="64" t="str">
+        <f t="shared" si="19"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W104" s="71" t="s">
+        <v>574</v>
+      </c>
+      <c r="X104" s="76" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-PAISA-104</v>
+      </c>
+      <c r="Y104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC104" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD104" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="60">
+        <v>105</v>
+      </c>
+      <c r="B105" s="74" t="s">
+        <v>566</v>
+      </c>
+      <c r="C105" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="D105" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="E105" s="35" t="s">
+        <v>587</v>
+      </c>
+      <c r="F105" s="35" t="s">
+        <v>588</v>
+      </c>
+      <c r="G105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="I105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="J105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="K105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="L105" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>De API</v>
+      </c>
+      <c r="M105" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Macros</v>
+      </c>
+      <c r="N105" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O105" s="70" t="str">
+        <f t="shared" si="18"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P105" s="71" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q105" s="71" t="s">
+        <v>590</v>
+      </c>
+      <c r="R105" s="71" t="s">
+        <v>591</v>
+      </c>
+      <c r="S105" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="T105" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>De API</v>
+      </c>
+      <c r="U105" s="71" t="str">
+        <f t="shared" si="19"/>
+        <v>Macros</v>
+      </c>
+      <c r="V105" s="64" t="str">
+        <f t="shared" si="19"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W105" s="71" t="s">
+        <v>574</v>
+      </c>
+      <c r="X105" s="76" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-PAISA-105</v>
+      </c>
+      <c r="Y105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC105" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD105" s="72" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B101">
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B105">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AD41:XFD100 AD102:XFD1048576">
-    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
+  <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AE41:XFD100 AE106:XFD1048576">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F102:F1048576 A1:D1 T1:X1 A102:D1048576 T102:X1048576">
-    <cfRule type="cellIs" dxfId="33" priority="450" operator="equal">
+  <conditionalFormatting sqref="E105:F105">
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F106:F1048576 A1:D1 T1:X1 A106:D1048576 T106:X1048576">
+    <cfRule type="cellIs" dxfId="33" priority="454" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="32" priority="1488"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1492"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AD1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="31" priority="19" operator="equal">
+  <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AE1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
+    <cfRule type="cellIs" dxfId="31" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="30" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="28" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F101">
+  <conditionalFormatting sqref="F101:F104">
     <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F102:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="16" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="970"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="982"/>
+  <conditionalFormatting sqref="F106:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="16" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="986"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F102:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="967"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="986"/>
+  <conditionalFormatting sqref="F106:F1048576">
+    <cfRule type="duplicateValues" dxfId="12" priority="971"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="990"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L102:R1048576">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+  <conditionalFormatting sqref="L106:R1048576">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R101">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R100">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W101">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+  <conditionalFormatting sqref="W2:W100">
+    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13240,15 +14010,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
@@ -13313,7 +14083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -13378,7 +14148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -13458,14 +14228,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" customWidth="1"/>
-    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21">
         <v>1</v>
       </c>
@@ -13479,7 +14249,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="13">
         <v>2</v>
       </c>
@@ -13493,7 +14263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="13">
         <v>3</v>
       </c>
@@ -13507,7 +14277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="13">
         <v>4</v>
       </c>
@@ -13521,7 +14291,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -13535,7 +14305,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" s="34" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="13">
         <v>6</v>
       </c>
@@ -13562,68 +14332,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.53515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.53515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.84375" style="55" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.84375" style="55" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.84375" style="55" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.84375" style="55" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.84375" style="55" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.3828125" style="25" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.69140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="8.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="9.69140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.15234375" style="25"/>
+    <col min="15" max="15" width="34.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.7109375" style="46" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>74</v>
       </c>
@@ -13631,7 +14401,7 @@
         <v>34</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D1" s="19" t="s">
         <v>33</v>
@@ -13792,7 +14562,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="36">
         <v>2</v>
       </c>
@@ -13944,29 +14714,29 @@
         <v>379</v>
       </c>
       <c r="AY2" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ2" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA2" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB2" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC2" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD2" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE2" s="38" t="str">
         <f t="shared" ref="BE2" si="0">_xlfn.CONCAT("""",C2,"""")</f>
         <v>"Continente"</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
         <v>3</v>
       </c>
@@ -14118,29 +14888,29 @@
         <v>379</v>
       </c>
       <c r="AY3" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ3" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA3" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC3" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD3" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE3" s="38" t="str">
         <f t="shared" ref="BE3:BE10" si="1">_xlfn.CONCAT("""",C3,"""")</f>
         <v>"SubContinente"</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
         <v>4</v>
       </c>
@@ -14292,29 +15062,29 @@
         <v>379</v>
       </c>
       <c r="AY4" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ4" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA4" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB4" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC4" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD4" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE4" s="38" t="str">
         <f t="shared" si="1"/>
         <v>"País"</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
         <v>5</v>
       </c>
@@ -14466,29 +15236,29 @@
         <v>379</v>
       </c>
       <c r="AY5" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ5" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA5" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB5" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC5" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD5" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE5" s="38" t="str">
         <f t="shared" si="1"/>
         <v>"Região"</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>6</v>
       </c>
@@ -14640,29 +15410,29 @@
         <v>379</v>
       </c>
       <c r="AY6" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ6" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA6" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB6" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC6" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD6" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE6" s="38" t="str">
         <f t="shared" si="1"/>
         <v>"Região"</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
         <v>7</v>
       </c>
@@ -14706,7 +15476,7 @@
         <v>78</v>
       </c>
       <c r="O7" s="28" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P7" s="37" t="s">
         <v>1</v>
@@ -14814,29 +15584,29 @@
         <v>379</v>
       </c>
       <c r="AY7" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ7" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA7" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB7" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC7" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD7" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE7" s="38" t="str">
         <f t="shared" si="1"/>
         <v>"Estado"</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>8</v>
       </c>
@@ -14980,38 +15750,38 @@
         <v>1</v>
       </c>
       <c r="AV8" s="30" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AW8" s="38" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AX8" s="30" t="s">
         <v>379</v>
       </c>
       <c r="AY8" s="38" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AZ8" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA8" s="38" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="BB8" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC8" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD8" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE8" s="38" t="str">
         <f t="shared" ref="BE8" si="2">_xlfn.CONCAT("""",C8,"""")</f>
         <v>"Capital"</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36">
         <v>9</v>
       </c>
@@ -15055,7 +15825,7 @@
         <v>78</v>
       </c>
       <c r="O9" s="28" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P9" s="37" t="s">
         <v>1</v>
@@ -15163,29 +15933,29 @@
         <v>379</v>
       </c>
       <c r="AY9" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ9" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA9" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB9" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC9" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD9" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE9" s="38" t="str">
         <f t="shared" si="1"/>
         <v>"UF"</v>
       </c>
     </row>
-    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>10</v>
       </c>
@@ -15229,7 +15999,7 @@
         <v>78</v>
       </c>
       <c r="O10" s="28" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P10" s="37" t="s">
         <v>1</v>
@@ -15337,22 +16107,22 @@
         <v>379</v>
       </c>
       <c r="AY10" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AZ10" s="30" t="s">
         <v>221</v>
       </c>
       <c r="BA10" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="BB10" s="30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BC10" s="38" t="s">
         <v>219</v>
       </c>
       <c r="BD10" s="30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BE10" s="38" t="str">
         <f t="shared" si="1"/>

--- a/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
+++ b/Versão5/BRASIL/Ontologia_Brasil_MG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60694CD2-78D9-4F39-A519-DC222AEFCB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271CA482-C936-4286-9DB9-274C7819EAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2866" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2901" uniqueCount="606">
   <si>
     <t>Key</t>
   </si>
@@ -1774,18 +1774,6 @@
     <t>Parãmetro Rvt</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>Função.Auxiliar</t>
   </si>
   <si>
@@ -1798,9 +1786,6 @@
     <t>Define a Helper Role in an application</t>
   </si>
   <si>
-    <t>Paisagística</t>
-  </si>
-  <si>
     <t>Função.Global</t>
   </si>
   <si>
@@ -1837,9 +1822,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -1862,6 +1844,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -2154,7 +2184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2368,23 +2398,65 @@
     <xf numFmtId="0" fontId="12" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="40">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2716,14 +2788,6 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3244,7 +3308,7 @@
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46268.69424675926</v>
+        <v>46273.674358796299</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>376</v>
@@ -3367,7 +3431,7 @@
     <col min="15" max="15" width="20.5703125" style="31" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="232.7109375" style="31" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="230.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="78" customWidth="1"/>
     <col min="20" max="20" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.140625" style="31" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
@@ -3436,7 +3500,7 @@
       <c r="R1" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="S1" s="77" t="s">
         <v>72</v>
       </c>
       <c r="T1" s="16" t="s">
@@ -3470,7 +3534,7 @@
         <v>372</v>
       </c>
       <c r="AD1" s="16" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3534,7 +3598,7 @@
       <c r="R2" s="64" t="s">
         <v>467</v>
       </c>
-      <c r="S2" s="64" t="s">
+      <c r="S2" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T2" s="64" t="str">
@@ -3634,7 +3698,7 @@
       <c r="R3" s="64" t="s">
         <v>468</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T3" s="64" t="str">
@@ -3734,7 +3798,7 @@
       <c r="R4" s="64" t="s">
         <v>469</v>
       </c>
-      <c r="S4" s="64" t="s">
+      <c r="S4" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T4" s="64" t="str">
@@ -3835,7 +3899,7 @@
       <c r="R5" s="64" t="s">
         <v>470</v>
       </c>
-      <c r="S5" s="64" t="s">
+      <c r="S5" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T5" s="64" t="str">
@@ -3935,7 +3999,7 @@
       <c r="R6" s="64" t="s">
         <v>471</v>
       </c>
-      <c r="S6" s="64" t="s">
+      <c r="S6" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="64" t="str">
@@ -4036,7 +4100,7 @@
       <c r="R7" s="64" t="s">
         <v>472</v>
       </c>
-      <c r="S7" s="64" t="s">
+      <c r="S7" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T7" s="64" t="str">
@@ -4137,7 +4201,7 @@
       <c r="R8" s="64" t="s">
         <v>473</v>
       </c>
-      <c r="S8" s="64" t="s">
+      <c r="S8" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T8" s="64" t="str">
@@ -4238,7 +4302,7 @@
       <c r="R9" s="64" t="s">
         <v>474</v>
       </c>
-      <c r="S9" s="64" t="s">
+      <c r="S9" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T9" s="64" t="str">
@@ -4339,7 +4403,7 @@
       <c r="R10" s="64" t="s">
         <v>475</v>
       </c>
-      <c r="S10" s="64" t="s">
+      <c r="S10" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="64" t="str">
@@ -4439,7 +4503,7 @@
       <c r="R11" s="64" t="s">
         <v>476</v>
       </c>
-      <c r="S11" s="64" t="s">
+      <c r="S11" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T11" s="64" t="str">
@@ -4540,7 +4604,7 @@
       <c r="R12" s="64" t="s">
         <v>477</v>
       </c>
-      <c r="S12" s="64" t="s">
+      <c r="S12" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T12" s="64" t="str">
@@ -4641,7 +4705,7 @@
       <c r="R13" s="64" t="s">
         <v>478</v>
       </c>
-      <c r="S13" s="64" t="s">
+      <c r="S13" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T13" s="64" t="str">
@@ -4743,7 +4807,7 @@
       <c r="R14" s="64" t="s">
         <v>479</v>
       </c>
-      <c r="S14" s="64" t="s">
+      <c r="S14" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T14" s="64" t="str">
@@ -4845,7 +4909,7 @@
       <c r="R15" s="64" t="s">
         <v>480</v>
       </c>
-      <c r="S15" s="64" t="s">
+      <c r="S15" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T15" s="64" t="str">
@@ -4947,7 +5011,7 @@
       <c r="R16" s="64" t="s">
         <v>481</v>
       </c>
-      <c r="S16" s="64" t="s">
+      <c r="S16" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T16" s="64" t="str">
@@ -5049,7 +5113,7 @@
       <c r="R17" s="64" t="s">
         <v>482</v>
       </c>
-      <c r="S17" s="64" t="s">
+      <c r="S17" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T17" s="64" t="str">
@@ -5151,7 +5215,7 @@
       <c r="R18" s="64" t="s">
         <v>483</v>
       </c>
-      <c r="S18" s="64" t="s">
+      <c r="S18" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T18" s="64" t="str">
@@ -5253,7 +5317,7 @@
       <c r="R19" s="64" t="s">
         <v>484</v>
       </c>
-      <c r="S19" s="64" t="s">
+      <c r="S19" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T19" s="64" t="str">
@@ -5355,7 +5419,7 @@
       <c r="R20" s="64" t="s">
         <v>485</v>
       </c>
-      <c r="S20" s="64" t="s">
+      <c r="S20" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T20" s="64" t="str">
@@ -5457,7 +5521,7 @@
       <c r="R21" s="64" t="s">
         <v>486</v>
       </c>
-      <c r="S21" s="64" t="s">
+      <c r="S21" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T21" s="64" t="str">
@@ -5559,7 +5623,7 @@
       <c r="R22" s="64" t="s">
         <v>487</v>
       </c>
-      <c r="S22" s="64" t="s">
+      <c r="S22" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T22" s="64" t="str">
@@ -5661,7 +5725,7 @@
       <c r="R23" s="64" t="s">
         <v>488</v>
       </c>
-      <c r="S23" s="64" t="s">
+      <c r="S23" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T23" s="64" t="str">
@@ -5763,7 +5827,7 @@
       <c r="R24" s="64" t="s">
         <v>489</v>
       </c>
-      <c r="S24" s="64" t="s">
+      <c r="S24" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T24" s="64" t="str">
@@ -5864,7 +5928,7 @@
       <c r="R25" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="S25" s="64" t="s">
+      <c r="S25" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T25" s="64" t="str">
@@ -5965,7 +6029,7 @@
       <c r="R26" s="64" t="s">
         <v>491</v>
       </c>
-      <c r="S26" s="64" t="s">
+      <c r="S26" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="64" t="str">
@@ -6066,7 +6130,7 @@
       <c r="R27" s="64" t="s">
         <v>492</v>
       </c>
-      <c r="S27" s="64" t="s">
+      <c r="S27" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T27" s="64" t="str">
@@ -6167,7 +6231,7 @@
       <c r="R28" s="64" t="s">
         <v>493</v>
       </c>
-      <c r="S28" s="64" t="s">
+      <c r="S28" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T28" s="64" t="str">
@@ -6268,7 +6332,7 @@
       <c r="R29" s="64" t="s">
         <v>494</v>
       </c>
-      <c r="S29" s="64" t="s">
+      <c r="S29" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T29" s="64" t="str">
@@ -6368,7 +6432,7 @@
       <c r="R30" s="64" t="s">
         <v>495</v>
       </c>
-      <c r="S30" s="64" t="s">
+      <c r="S30" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T30" s="64" t="str">
@@ -6468,7 +6532,7 @@
       <c r="R31" s="64" t="s">
         <v>496</v>
       </c>
-      <c r="S31" s="64" t="s">
+      <c r="S31" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T31" s="64" t="str">
@@ -6568,7 +6632,7 @@
       <c r="R32" s="64" t="s">
         <v>497</v>
       </c>
-      <c r="S32" s="64" t="s">
+      <c r="S32" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T32" s="64" t="str">
@@ -6668,7 +6732,7 @@
       <c r="R33" s="64" t="s">
         <v>498</v>
       </c>
-      <c r="S33" s="64" t="s">
+      <c r="S33" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T33" s="64" t="str">
@@ -6768,7 +6832,7 @@
       <c r="R34" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="S34" s="64" t="s">
+      <c r="S34" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T34" s="64" t="str">
@@ -6868,7 +6932,7 @@
       <c r="R35" s="64" t="s">
         <v>500</v>
       </c>
-      <c r="S35" s="64" t="s">
+      <c r="S35" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T35" s="64" t="str">
@@ -6968,7 +7032,7 @@
       <c r="R36" s="64" t="s">
         <v>501</v>
       </c>
-      <c r="S36" s="64" t="s">
+      <c r="S36" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T36" s="64" t="str">
@@ -7068,7 +7132,7 @@
       <c r="R37" s="64" t="s">
         <v>502</v>
       </c>
-      <c r="S37" s="64" t="s">
+      <c r="S37" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T37" s="64" t="str">
@@ -7168,7 +7232,7 @@
       <c r="R38" s="64" t="s">
         <v>503</v>
       </c>
-      <c r="S38" s="64" t="s">
+      <c r="S38" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T38" s="64" t="str">
@@ -7268,7 +7332,7 @@
       <c r="R39" s="64" t="s">
         <v>504</v>
       </c>
-      <c r="S39" s="64" t="s">
+      <c r="S39" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T39" s="64" t="str">
@@ -7368,7 +7432,7 @@
       <c r="R40" s="64" t="s">
         <v>505</v>
       </c>
-      <c r="S40" s="64" t="s">
+      <c r="S40" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T40" s="64" t="str">
@@ -7468,7 +7532,7 @@
       <c r="R41" s="64" t="s">
         <v>506</v>
       </c>
-      <c r="S41" s="64" t="s">
+      <c r="S41" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T41" s="64" t="str">
@@ -7568,7 +7632,7 @@
       <c r="R42" s="64" t="s">
         <v>507</v>
       </c>
-      <c r="S42" s="64" t="s">
+      <c r="S42" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T42" s="64" t="str">
@@ -7668,7 +7732,7 @@
       <c r="R43" s="64" t="s">
         <v>508</v>
       </c>
-      <c r="S43" s="64" t="s">
+      <c r="S43" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T43" s="64" t="str">
@@ -7768,7 +7832,7 @@
       <c r="R44" s="64" t="s">
         <v>509</v>
       </c>
-      <c r="S44" s="64" t="s">
+      <c r="S44" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T44" s="64" t="str">
@@ -7868,7 +7932,7 @@
       <c r="R45" s="64" t="s">
         <v>510</v>
       </c>
-      <c r="S45" s="64" t="s">
+      <c r="S45" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T45" s="64" t="str">
@@ -7968,7 +8032,7 @@
       <c r="R46" s="64" t="s">
         <v>511</v>
       </c>
-      <c r="S46" s="64" t="s">
+      <c r="S46" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T46" s="64" t="str">
@@ -8068,7 +8132,7 @@
       <c r="R47" s="64" t="s">
         <v>512</v>
       </c>
-      <c r="S47" s="64" t="s">
+      <c r="S47" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T47" s="64" t="str">
@@ -8168,7 +8232,7 @@
       <c r="R48" s="64" t="s">
         <v>513</v>
       </c>
-      <c r="S48" s="64" t="s">
+      <c r="S48" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T48" s="64" t="str">
@@ -8268,7 +8332,7 @@
       <c r="R49" s="64" t="s">
         <v>514</v>
       </c>
-      <c r="S49" s="64" t="s">
+      <c r="S49" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T49" s="64" t="str">
@@ -8368,7 +8432,7 @@
       <c r="R50" s="64" t="s">
         <v>515</v>
       </c>
-      <c r="S50" s="64" t="s">
+      <c r="S50" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T50" s="64" t="str">
@@ -8391,7 +8455,7 @@
         <v>Key-BRASIL_MG-50</v>
       </c>
       <c r="Y50" s="64" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="Z50" s="72" t="s">
         <v>1</v>
@@ -8468,7 +8532,7 @@
       <c r="R51" s="64" t="s">
         <v>516</v>
       </c>
-      <c r="S51" s="64" t="s">
+      <c r="S51" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T51" s="64" t="str">
@@ -8491,7 +8555,7 @@
         <v>Key-BRASIL_MG-51</v>
       </c>
       <c r="Y51" s="64" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="Z51" s="72" t="s">
         <v>1</v>
@@ -8568,7 +8632,7 @@
       <c r="R52" s="64" t="s">
         <v>517</v>
       </c>
-      <c r="S52" s="64" t="s">
+      <c r="S52" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T52" s="64" t="str">
@@ -8591,7 +8655,7 @@
         <v>Key-BRASIL_MG-52</v>
       </c>
       <c r="Y52" s="64" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="Z52" s="72" t="s">
         <v>1</v>
@@ -8668,7 +8732,7 @@
       <c r="R53" s="64" t="s">
         <v>518</v>
       </c>
-      <c r="S53" s="64" t="s">
+      <c r="S53" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T53" s="64" t="str">
@@ -8691,7 +8755,7 @@
         <v>Key-BRASIL_MG-53</v>
       </c>
       <c r="Y53" s="64" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="Z53" s="72" t="s">
         <v>1</v>
@@ -8768,7 +8832,7 @@
       <c r="R54" s="64" t="s">
         <v>519</v>
       </c>
-      <c r="S54" s="64" t="s">
+      <c r="S54" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T54" s="64" t="str">
@@ -8871,7 +8935,7 @@
       <c r="R55" s="64" t="s">
         <v>520</v>
       </c>
-      <c r="S55" s="64" t="s">
+      <c r="S55" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T55" s="64" t="str">
@@ -8973,7 +9037,7 @@
       <c r="R56" s="64" t="s">
         <v>521</v>
       </c>
-      <c r="S56" s="64" t="s">
+      <c r="S56" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T56" s="64" t="str">
@@ -9073,7 +9137,7 @@
       <c r="R57" s="64" t="s">
         <v>522</v>
       </c>
-      <c r="S57" s="64" t="s">
+      <c r="S57" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T57" s="64" t="str">
@@ -9173,7 +9237,7 @@
       <c r="R58" s="64" t="s">
         <v>523</v>
       </c>
-      <c r="S58" s="64" t="s">
+      <c r="S58" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T58" s="64" t="str">
@@ -9273,7 +9337,7 @@
       <c r="R59" s="64" t="s">
         <v>524</v>
       </c>
-      <c r="S59" s="64" t="s">
+      <c r="S59" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T59" s="64" t="str">
@@ -9373,7 +9437,7 @@
       <c r="R60" s="64" t="s">
         <v>525</v>
       </c>
-      <c r="S60" s="64" t="s">
+      <c r="S60" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T60" s="64" t="str">
@@ -9473,7 +9537,7 @@
       <c r="R61" s="64" t="s">
         <v>526</v>
       </c>
-      <c r="S61" s="64" t="s">
+      <c r="S61" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T61" s="64" t="str">
@@ -9573,7 +9637,7 @@
       <c r="R62" s="64" t="s">
         <v>525</v>
       </c>
-      <c r="S62" s="64" t="s">
+      <c r="S62" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T62" s="64" t="str">
@@ -9673,7 +9737,7 @@
       <c r="R63" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="S63" s="64" t="s">
+      <c r="S63" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T63" s="64" t="str">
@@ -9773,7 +9837,7 @@
       <c r="R64" s="64" t="s">
         <v>528</v>
       </c>
-      <c r="S64" s="64" t="s">
+      <c r="S64" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T64" s="64" t="str">
@@ -9873,7 +9937,7 @@
       <c r="R65" s="64" t="s">
         <v>529</v>
       </c>
-      <c r="S65" s="64" t="s">
+      <c r="S65" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T65" s="64" t="str">
@@ -9896,7 +9960,7 @@
         <v>Key-BRASIL_MG-65</v>
       </c>
       <c r="Y65" s="64" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="Z65" s="72" t="s">
         <v>1</v>
@@ -9973,7 +10037,7 @@
       <c r="R66" s="64" t="s">
         <v>530</v>
       </c>
-      <c r="S66" s="64" t="s">
+      <c r="S66" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T66" s="64" t="str">
@@ -9996,7 +10060,7 @@
         <v>Key-BRASIL_MG-66</v>
       </c>
       <c r="Y66" s="64" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="Z66" s="72" t="s">
         <v>1</v>
@@ -10073,7 +10137,7 @@
       <c r="R67" s="64" t="s">
         <v>531</v>
       </c>
-      <c r="S67" s="64" t="s">
+      <c r="S67" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T67" s="64" t="str">
@@ -10096,7 +10160,7 @@
         <v>Key-BRASIL_MG-67</v>
       </c>
       <c r="Y67" s="64" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="Z67" s="72" t="s">
         <v>1</v>
@@ -10174,7 +10238,7 @@
       <c r="R68" s="64" t="s">
         <v>532</v>
       </c>
-      <c r="S68" s="64" t="s">
+      <c r="S68" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T68" s="64" t="str">
@@ -10275,7 +10339,7 @@
       <c r="R69" s="64" t="s">
         <v>533</v>
       </c>
-      <c r="S69" s="64" t="s">
+      <c r="S69" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T69" s="64" t="str">
@@ -10376,7 +10440,7 @@
       <c r="R70" s="64" t="s">
         <v>532</v>
       </c>
-      <c r="S70" s="64" t="s">
+      <c r="S70" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T70" s="64" t="str">
@@ -10477,7 +10541,7 @@
       <c r="R71" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="S71" s="64" t="s">
+      <c r="S71" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T71" s="64" t="str">
@@ -10578,7 +10642,7 @@
       <c r="R72" s="64" t="s">
         <v>535</v>
       </c>
-      <c r="S72" s="64" t="s">
+      <c r="S72" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T72" s="64" t="str">
@@ -10678,7 +10742,7 @@
       <c r="R73" s="64" t="s">
         <v>536</v>
       </c>
-      <c r="S73" s="64" t="s">
+      <c r="S73" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T73" s="64" t="str">
@@ -10778,7 +10842,7 @@
       <c r="R74" s="64" t="s">
         <v>537</v>
       </c>
-      <c r="S74" s="64" t="s">
+      <c r="S74" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T74" s="64" t="str">
@@ -10879,7 +10943,7 @@
       <c r="R75" s="64" t="s">
         <v>538</v>
       </c>
-      <c r="S75" s="64" t="s">
+      <c r="S75" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T75" s="64" t="str">
@@ -10979,7 +11043,7 @@
       <c r="R76" s="64" t="s">
         <v>539</v>
       </c>
-      <c r="S76" s="64" t="s">
+      <c r="S76" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T76" s="64" t="str">
@@ -11002,7 +11066,7 @@
         <v>Key-BRASIL_MG-76</v>
       </c>
       <c r="Y76" s="64" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="Z76" s="72" t="s">
         <v>1</v>
@@ -11079,7 +11143,7 @@
       <c r="R77" s="64" t="s">
         <v>540</v>
       </c>
-      <c r="S77" s="64" t="s">
+      <c r="S77" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T77" s="64" t="str">
@@ -11102,7 +11166,7 @@
         <v>Key-BRASIL_MG-77</v>
       </c>
       <c r="Y77" s="64" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="Z77" s="72" t="s">
         <v>1</v>
@@ -11179,7 +11243,7 @@
       <c r="R78" s="64" t="s">
         <v>541</v>
       </c>
-      <c r="S78" s="64" t="s">
+      <c r="S78" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T78" s="64" t="str">
@@ -11202,7 +11266,7 @@
         <v>Key-BRASIL_MG-78</v>
       </c>
       <c r="Y78" s="64" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="Z78" s="72" t="s">
         <v>1</v>
@@ -11279,7 +11343,7 @@
       <c r="R79" s="64" t="s">
         <v>542</v>
       </c>
-      <c r="S79" s="64" t="s">
+      <c r="S79" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T79" s="64" t="str">
@@ -11379,7 +11443,7 @@
       <c r="R80" s="64" t="s">
         <v>543</v>
       </c>
-      <c r="S80" s="64" t="s">
+      <c r="S80" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T80" s="64" t="str">
@@ -11402,7 +11466,7 @@
         <v>Key-BRASIL_MG-80</v>
       </c>
       <c r="Y80" s="64" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="Z80" s="72" t="s">
         <v>1</v>
@@ -11479,7 +11543,7 @@
       <c r="R81" s="64" t="s">
         <v>544</v>
       </c>
-      <c r="S81" s="64" t="s">
+      <c r="S81" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T81" s="64" t="str">
@@ -11502,7 +11566,7 @@
         <v>Key-BRASIL_MG-81</v>
       </c>
       <c r="Y81" s="64" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="Z81" s="72" t="s">
         <v>1</v>
@@ -11579,7 +11643,7 @@
       <c r="R82" s="64" t="s">
         <v>545</v>
       </c>
-      <c r="S82" s="64" t="s">
+      <c r="S82" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T82" s="64" t="str">
@@ -11679,7 +11743,7 @@
       <c r="R83" s="64" t="s">
         <v>546</v>
       </c>
-      <c r="S83" s="64" t="s">
+      <c r="S83" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T83" s="64" t="str">
@@ -11779,7 +11843,7 @@
       <c r="R84" s="64" t="s">
         <v>547</v>
       </c>
-      <c r="S84" s="64" t="s">
+      <c r="S84" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T84" s="64" t="str">
@@ -11879,7 +11943,7 @@
       <c r="R85" s="64" t="s">
         <v>548</v>
       </c>
-      <c r="S85" s="64" t="s">
+      <c r="S85" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T85" s="64" t="str">
@@ -11979,7 +12043,7 @@
       <c r="R86" s="64" t="s">
         <v>549</v>
       </c>
-      <c r="S86" s="64" t="s">
+      <c r="S86" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T86" s="64" t="str">
@@ -12079,7 +12143,7 @@
       <c r="R87" s="64" t="s">
         <v>550</v>
       </c>
-      <c r="S87" s="64" t="s">
+      <c r="S87" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T87" s="64" t="str">
@@ -12179,7 +12243,7 @@
       <c r="R88" s="64" t="s">
         <v>551</v>
       </c>
-      <c r="S88" s="64" t="s">
+      <c r="S88" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T88" s="64" t="str">
@@ -12279,7 +12343,7 @@
       <c r="R89" s="64" t="s">
         <v>552</v>
       </c>
-      <c r="S89" s="64" t="s">
+      <c r="S89" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T89" s="64" t="str">
@@ -12379,7 +12443,7 @@
       <c r="R90" s="64" t="s">
         <v>553</v>
       </c>
-      <c r="S90" s="64" t="s">
+      <c r="S90" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T90" s="64" t="str">
@@ -12479,7 +12543,7 @@
       <c r="R91" s="64" t="s">
         <v>554</v>
       </c>
-      <c r="S91" s="64" t="s">
+      <c r="S91" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T91" s="64" t="str">
@@ -12579,7 +12643,7 @@
       <c r="R92" s="64" t="s">
         <v>555</v>
       </c>
-      <c r="S92" s="64" t="s">
+      <c r="S92" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T92" s="64" t="str">
@@ -12679,7 +12743,7 @@
       <c r="R93" s="64" t="s">
         <v>556</v>
       </c>
-      <c r="S93" s="64" t="s">
+      <c r="S93" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T93" s="64" t="str">
@@ -12779,7 +12843,7 @@
       <c r="R94" s="64" t="s">
         <v>557</v>
       </c>
-      <c r="S94" s="64" t="s">
+      <c r="S94" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T94" s="64" t="str">
@@ -12879,7 +12943,7 @@
       <c r="R95" s="64" t="s">
         <v>558</v>
       </c>
-      <c r="S95" s="64" t="s">
+      <c r="S95" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T95" s="64" t="str">
@@ -12979,7 +13043,7 @@
       <c r="R96" s="64" t="s">
         <v>559</v>
       </c>
-      <c r="S96" s="64" t="s">
+      <c r="S96" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T96" s="64" t="str">
@@ -13079,7 +13143,7 @@
       <c r="R97" s="64" t="s">
         <v>559</v>
       </c>
-      <c r="S97" s="64" t="s">
+      <c r="S97" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T97" s="64" t="str">
@@ -13179,7 +13243,7 @@
       <c r="R98" s="64" t="s">
         <v>560</v>
       </c>
-      <c r="S98" s="64" t="s">
+      <c r="S98" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T98" s="64" t="str">
@@ -13279,7 +13343,7 @@
       <c r="R99" s="64" t="s">
         <v>561</v>
       </c>
-      <c r="S99" s="64" t="s">
+      <c r="S99" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T99" s="64" t="str">
@@ -13379,7 +13443,7 @@
       <c r="R100" s="64" t="s">
         <v>562</v>
       </c>
-      <c r="S100" s="64" t="s">
+      <c r="S100" s="75" t="s">
         <v>1</v>
       </c>
       <c r="T100" s="64" t="str">
@@ -13420,86 +13484,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="60">
         <v>101</v>
       </c>
-      <c r="B101" s="74" t="s">
+      <c r="B101" s="73" t="s">
+        <v>590</v>
+      </c>
+      <c r="C101" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="D101" s="35" t="s">
+        <v>592</v>
+      </c>
+      <c r="E101" s="35" t="s">
+        <v>593</v>
+      </c>
+      <c r="F101" s="35" t="s">
         <v>566</v>
       </c>
-      <c r="C101" s="35" t="s">
+      <c r="G101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" s="70" t="s">
+        <v>591</v>
+      </c>
+      <c r="M101" s="70" t="s">
+        <v>592</v>
+      </c>
+      <c r="N101" s="70" t="s">
+        <v>594</v>
+      </c>
+      <c r="O101" s="70" t="s">
+        <v>595</v>
+      </c>
+      <c r="P101" s="71" t="s">
         <v>567</v>
       </c>
-      <c r="D101" s="35" t="s">
+      <c r="Q101" s="71" t="s">
+        <v>568</v>
+      </c>
+      <c r="R101" s="71" t="s">
         <v>569</v>
       </c>
-      <c r="E101" s="35" t="s">
-        <v>568</v>
-      </c>
-      <c r="F101" s="35" t="s">
-        <v>570</v>
-      </c>
-      <c r="G101" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="K101" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="L101" s="70" t="str">
-        <f t="shared" ref="L101:O105" si="18">SUBSTITUTE(CONCATENATE("", C101), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M101" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Macros</v>
-      </c>
-      <c r="N101" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O101" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P101" s="71" t="s">
-        <v>571</v>
-      </c>
-      <c r="Q101" s="71" t="s">
-        <v>572</v>
-      </c>
-      <c r="R101" s="71" t="s">
-        <v>573</v>
-      </c>
-      <c r="S101" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="T101" s="71" t="str">
-        <f t="shared" ref="T101:V105" si="19">SUBSTITUTE(C101, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U101" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>Macros</v>
-      </c>
-      <c r="V101" s="64" t="str">
-        <f t="shared" si="19"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W101" s="71" t="s">
-        <v>574</v>
-      </c>
-      <c r="X101" s="76" t="str">
-        <f t="shared" ref="X101:X105" si="20">CONCATENATE("Key-PAISA-",A101)</f>
-        <v>Key-PAISA-101</v>
+      <c r="S101" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T101" s="71" t="s">
+        <v>596</v>
+      </c>
+      <c r="U101" s="71" t="s">
+        <v>597</v>
+      </c>
+      <c r="V101" s="64" t="s">
+        <v>594</v>
+      </c>
+      <c r="W101" s="64" t="s">
+        <v>432</v>
+      </c>
+      <c r="X101" s="65" t="str">
+        <f t="shared" ref="X101:X105" si="18">CONCATENATE("Key-BRASIL_MG-",A101)</f>
+        <v>Key-BRASIL_MG-101</v>
       </c>
       <c r="Y101" s="72" t="s">
         <v>1</v>
@@ -13520,86 +13577,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="60">
         <v>102</v>
       </c>
-      <c r="B102" s="74" t="s">
-        <v>566</v>
+      <c r="B102" s="73" t="s">
+        <v>590</v>
       </c>
       <c r="C102" s="35" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="D102" s="35" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="E102" s="35" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="F102" s="35" t="s">
-        <v>575</v>
-      </c>
-      <c r="G102" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H102" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="I102" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="J102" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="K102" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="L102" s="70" t="str">
+        <v>570</v>
+      </c>
+      <c r="G102" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H102" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="I102" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="K102" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="L102" s="70" t="s">
+        <v>591</v>
+      </c>
+      <c r="M102" s="70" t="s">
+        <v>592</v>
+      </c>
+      <c r="N102" s="70" t="s">
+        <v>594</v>
+      </c>
+      <c r="O102" s="70" t="s">
+        <v>598</v>
+      </c>
+      <c r="P102" s="71" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q102" s="71" t="s">
+        <v>572</v>
+      </c>
+      <c r="R102" s="71" t="s">
+        <v>573</v>
+      </c>
+      <c r="S102" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T102" s="71" t="s">
+        <v>596</v>
+      </c>
+      <c r="U102" s="71" t="s">
+        <v>597</v>
+      </c>
+      <c r="V102" s="64" t="s">
+        <v>594</v>
+      </c>
+      <c r="W102" s="64" t="s">
+        <v>432</v>
+      </c>
+      <c r="X102" s="65" t="str">
         <f t="shared" si="18"/>
-        <v>De API</v>
-      </c>
-      <c r="M102" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Macros</v>
-      </c>
-      <c r="N102" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O102" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P102" s="71" t="s">
-        <v>576</v>
-      </c>
-      <c r="Q102" s="71" t="s">
-        <v>577</v>
-      </c>
-      <c r="R102" s="71" t="s">
-        <v>578</v>
-      </c>
-      <c r="S102" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="T102" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>De API</v>
-      </c>
-      <c r="U102" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>Macros</v>
-      </c>
-      <c r="V102" s="64" t="str">
-        <f t="shared" si="19"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W102" s="71" t="s">
-        <v>574</v>
-      </c>
-      <c r="X102" s="76" t="str">
-        <f t="shared" si="20"/>
-        <v>Key-PAISA-102</v>
+        <v>Key-BRASIL_MG-102</v>
       </c>
       <c r="Y102" s="72" t="s">
         <v>1</v>
@@ -13620,86 +13670,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="60">
         <v>103</v>
       </c>
-      <c r="B103" s="74" t="s">
-        <v>566</v>
+      <c r="B103" s="73" t="s">
+        <v>590</v>
       </c>
       <c r="C103" s="35" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="D103" s="35" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="E103" s="35" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="F103" s="35" t="s">
-        <v>579</v>
-      </c>
-      <c r="G103" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H103" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="I103" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="J103" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="K103" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="L103" s="70" t="str">
+        <v>574</v>
+      </c>
+      <c r="G103" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="I103" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="J103" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="K103" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="L103" s="70" t="s">
+        <v>591</v>
+      </c>
+      <c r="M103" s="70" t="s">
+        <v>592</v>
+      </c>
+      <c r="N103" s="70" t="s">
+        <v>594</v>
+      </c>
+      <c r="O103" s="70" t="s">
+        <v>599</v>
+      </c>
+      <c r="P103" s="71" t="s">
+        <v>575</v>
+      </c>
+      <c r="Q103" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="R103" s="71" t="s">
+        <v>577</v>
+      </c>
+      <c r="S103" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T103" s="71" t="s">
+        <v>596</v>
+      </c>
+      <c r="U103" s="71" t="s">
+        <v>597</v>
+      </c>
+      <c r="V103" s="64" t="s">
+        <v>594</v>
+      </c>
+      <c r="W103" s="64" t="s">
+        <v>432</v>
+      </c>
+      <c r="X103" s="65" t="str">
         <f t="shared" si="18"/>
-        <v>De API</v>
-      </c>
-      <c r="M103" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Macros</v>
-      </c>
-      <c r="N103" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O103" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P103" s="71" t="s">
-        <v>580</v>
-      </c>
-      <c r="Q103" s="71" t="s">
-        <v>581</v>
-      </c>
-      <c r="R103" s="71" t="s">
-        <v>582</v>
-      </c>
-      <c r="S103" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="T103" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>De API</v>
-      </c>
-      <c r="U103" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>Macros</v>
-      </c>
-      <c r="V103" s="64" t="str">
-        <f t="shared" si="19"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W103" s="71" t="s">
-        <v>574</v>
-      </c>
-      <c r="X103" s="76" t="str">
-        <f t="shared" si="20"/>
-        <v>Key-PAISA-103</v>
+        <v>Key-BRASIL_MG-103</v>
       </c>
       <c r="Y103" s="72" t="s">
         <v>1</v>
@@ -13720,86 +13763,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="60">
         <v>104</v>
       </c>
-      <c r="B104" s="74" t="s">
-        <v>566</v>
+      <c r="B104" s="73" t="s">
+        <v>590</v>
       </c>
       <c r="C104" s="35" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="D104" s="35" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="E104" s="35" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="F104" s="35" t="s">
-        <v>583</v>
-      </c>
-      <c r="G104" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H104" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="I104" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="J104" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="K104" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="L104" s="70" t="str">
+        <v>578</v>
+      </c>
+      <c r="G104" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H104" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="I104" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="J104" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="K104" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="L104" s="70" t="s">
+        <v>591</v>
+      </c>
+      <c r="M104" s="70" t="s">
+        <v>592</v>
+      </c>
+      <c r="N104" s="70" t="s">
+        <v>594</v>
+      </c>
+      <c r="O104" s="70" t="s">
+        <v>600</v>
+      </c>
+      <c r="P104" s="71" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q104" s="71" t="s">
+        <v>580</v>
+      </c>
+      <c r="R104" s="71" t="s">
+        <v>581</v>
+      </c>
+      <c r="S104" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T104" s="71" t="s">
+        <v>596</v>
+      </c>
+      <c r="U104" s="71" t="s">
+        <v>597</v>
+      </c>
+      <c r="V104" s="64" t="s">
+        <v>594</v>
+      </c>
+      <c r="W104" s="64" t="s">
+        <v>432</v>
+      </c>
+      <c r="X104" s="65" t="str">
         <f t="shared" si="18"/>
-        <v>De API</v>
-      </c>
-      <c r="M104" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Macros</v>
-      </c>
-      <c r="N104" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O104" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P104" s="71" t="s">
-        <v>584</v>
-      </c>
-      <c r="Q104" s="71" t="s">
-        <v>585</v>
-      </c>
-      <c r="R104" s="71" t="s">
-        <v>586</v>
-      </c>
-      <c r="S104" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="T104" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>De API</v>
-      </c>
-      <c r="U104" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>Macros</v>
-      </c>
-      <c r="V104" s="64" t="str">
-        <f t="shared" si="19"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W104" s="71" t="s">
-        <v>574</v>
-      </c>
-      <c r="X104" s="76" t="str">
-        <f t="shared" si="20"/>
-        <v>Key-PAISA-104</v>
+        <v>Key-BRASIL_MG-104</v>
       </c>
       <c r="Y104" s="72" t="s">
         <v>1</v>
@@ -13820,86 +13856,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="60">
         <v>105</v>
       </c>
-      <c r="B105" s="74" t="s">
-        <v>566</v>
+      <c r="B105" s="73" t="s">
+        <v>590</v>
       </c>
       <c r="C105" s="35" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="D105" s="35" t="s">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="E105" s="35" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="F105" s="35" t="s">
-        <v>588</v>
-      </c>
-      <c r="G105" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H105" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="I105" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="J105" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="K105" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="L105" s="70" t="str">
+        <v>582</v>
+      </c>
+      <c r="G105" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H105" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="I105" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="J105" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="K105" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="L105" s="70" t="s">
+        <v>591</v>
+      </c>
+      <c r="M105" s="70" t="s">
+        <v>601</v>
+      </c>
+      <c r="N105" s="70" t="s">
+        <v>603</v>
+      </c>
+      <c r="O105" s="70" t="s">
+        <v>604</v>
+      </c>
+      <c r="P105" s="71" t="s">
+        <v>583</v>
+      </c>
+      <c r="Q105" s="71" t="s">
+        <v>584</v>
+      </c>
+      <c r="R105" s="71" t="s">
+        <v>585</v>
+      </c>
+      <c r="S105" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T105" s="71" t="s">
+        <v>596</v>
+      </c>
+      <c r="U105" s="71" t="s">
+        <v>605</v>
+      </c>
+      <c r="V105" s="64" t="s">
+        <v>603</v>
+      </c>
+      <c r="W105" s="64" t="s">
+        <v>432</v>
+      </c>
+      <c r="X105" s="65" t="str">
         <f t="shared" si="18"/>
-        <v>De API</v>
-      </c>
-      <c r="M105" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Macros</v>
-      </c>
-      <c r="N105" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O105" s="70" t="str">
-        <f t="shared" si="18"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P105" s="71" t="s">
-        <v>589</v>
-      </c>
-      <c r="Q105" s="71" t="s">
-        <v>590</v>
-      </c>
-      <c r="R105" s="71" t="s">
-        <v>591</v>
-      </c>
-      <c r="S105" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="T105" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>De API</v>
-      </c>
-      <c r="U105" s="71" t="str">
-        <f t="shared" si="19"/>
-        <v>Macros</v>
-      </c>
-      <c r="V105" s="64" t="str">
-        <f t="shared" si="19"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="W105" s="71" t="s">
-        <v>574</v>
-      </c>
-      <c r="X105" s="76" t="str">
-        <f t="shared" si="20"/>
-        <v>Key-PAISA-105</v>
+        <v>Key-BRASIL_MG-105</v>
       </c>
       <c r="Y105" s="72" t="s">
         <v>1</v>
@@ -13922,86 +13951,84 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B105">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B100 A101:A105">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:D100 L41:Q100 T41:V100 AE41:XFD100 AE106:XFD1048576">
-    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E105:F105">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1 F106:F1048576 A1:D1 T1:X1 A106:D1048576 T106:X1048576">
-    <cfRule type="cellIs" dxfId="33" priority="454" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="457" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="32" priority="1492"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F29 F41:F93 F96:F100 L1:Q6 AE1:XFD29 T2:V28 L7:O9 Q7:Q9 L10:Q29 T29:U29 V29:V40 O30:O40">
-    <cfRule type="cellIs" dxfId="31" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F93 F96:F100">
-    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F40">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F40">
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
     <cfRule type="duplicateValues" dxfId="25" priority="27"/>
     <cfRule type="duplicateValues" dxfId="24" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F93 F2:F29 F96:F100">
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F100 F2:F93">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F101:F104">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="16" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="971"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="982"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="993"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L106:R1048576">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R100">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W100">
-    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
+  <conditionalFormatting sqref="W2:W105">
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F101:F105">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -14216,7 +14243,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14321,7 +14348,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A6">
-    <cfRule type="cellIs" dxfId="4" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16133,20 +16160,20 @@
   <autoFilter ref="F1:F6" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576 G2 G4:G5 H10:BB10 D10:F1048576 H11:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:BB9">
-    <cfRule type="cellIs" dxfId="1" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:XFD3 D1:F8 H4:BB8 BC4:XFD10">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
